--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review role-gating expected depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
+          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I90" s="12" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · WO-completion role-gating is FE-only (button hidden for Tech, but BE allows it). Verdict depends on the same FE-vs-BE ruling as SF-PERM-06.</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS.</t>
+          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed depends on reviewer!=completer (missing) and the FE-vs-BE ruling.</t>
+          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I100" s="12" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · WO completion permission is FE-only at the BE (Technician completed via simple-complete API = 201). Ruling: SV-8183 says 'BE enforces' but SV-7864 atom-collapse lets any WO C&amp;E role act. Which governs?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix.</t>
+          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
         </is>
       </c>
     </row>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review sign-off permission (woReviewWorkOrders) is FE-only at the BE (Technician drove change-status = 201). Same FE-vs-BE ruling.</t>
+          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO). Ruling: enforce the rule (currently FAIL) or descope?</t>
+          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
         </is>
       </c>
       <c r="I104" s="12" t="inlineStr">
@@ -10734,7 +10734,7 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS.</t>
+          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix.</t>
+          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B25" s="8" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" s="2" t="n"/>
     </row>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1915,17 +1915,17 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>C29298</t>
+          <t>C29296</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29298</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29296</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-09</t>
+          <t>SF-COMP-07</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a new line to a completed work order returns it to Approved</t>
+          <t>Verify in-stock inventory parts decrement inventory and write Part History on simple completion</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="14" t="inlineStr">
@@ -1955,24 +1955,24 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Return-to-Approved verified 2026-07-06 (S16-03-reopened.png). The 'already-received vs newly-added' modal summary was not separately driven.</t>
+          <t>§8 open question — auto-receive of in-stock inventory on simple completion is UNCONFIRMED. Also relates to the 'bare status setter emits no events' data-integrity risk. Not driven in VIU. Confirm intended behavior. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4), so the completion expectations stand. || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed in-stock inventory parts DO decrement on-hand and write Part History on completion (the PO question is a separate concern). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (decrement + skip-path no-bypass). Seeded WO 1490338a with inventory part P550848 (inv_part 000657fe, on-hand 6). Manual Pick (button_part_request_action -&gt; POST /api/work-orders/part/perform-request-status-action 201) decremented on-hand 6-&gt;5; simple-complete (skip path) BE-gated on picking (400 'All inventory and found parts must be picked before completing the work order.' until picked), then returned 201 (WO=Complete) with on-hand STAYING 5 (movement not bypassed by the skip-path status setter; confirmed via API GET /api/inventory/parts/{id}.quantity AND the /parts/inventory list UI showing qty 5). Part-History LOG DISPLAY not separately surfaced (see SF-QB-01 note / OBS-6) but the net on-hand movement is proven.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>C29299</t>
+          <t>C29298</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29299</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29298</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-10</t>
+          <t>SF-COMP-09</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
+          <t>Verify adding a new line to a completed work order returns it to Approved</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -2002,39 +2002,39 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Existing behaviors preserved by design; not re-driven in the VIU run. Needs live verification.</t>
+          <t>Return-to-Approved verified 2026-07-06 (S16-03-reopened.png). The 'already-received vs newly-added' modal summary was not separately driven.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>C29300</t>
+          <t>C29299</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29300</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29299</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-11</t>
+          <t>SF-COMP-10</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — No-PO / Skip (Story 2)</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice completion wizard offers Receive Parts, Complete Without Receiving and Cancel</t>
+          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -2049,24 +2049,24 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=false; wizard = 'Receive → Success', '2 parts waiting to receive', with Cancel / Complete Without Receiving / Receive Parts (S3-01-wizard-optional.png).</t>
+          <t>Existing behaviors preserved by design; not re-driven in the VIU run. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>C29301</t>
+          <t>C29300</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29301</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29300</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-12</t>
+          <t>SF-COMP-11</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -2076,12 +2076,12 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal creates POs in the background and shows the count of parts to receive</t>
+          <t>Verify the optional-invoice completion wizard offers Receive Parts, Complete Without Receiving and Cancel</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2096,24 +2096,24 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Parts-to-receive count verified 2026-07-06 ('2 parts waiting to receive', S3-01-wizard-optional.png). Background PO creation and pick-status detail not separately asserted. || [V2.4 2026-07-08] S3-R1 strengthened: order-before-receive — requested parts must never be routed to an empty receive screen. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Optional-invoice completion wizard (requireVendorInvoiceNumber OFF) receive step shows '2 parts waiting to receive' plus '1 part is not ordered yet - Going to receive parts or completing the work order will order those parts' (background PO creation); API confirmed an order_id assigned + waiting_to_receive. Both 'Receive Parts' and 'Complete Without Receiving' present.</t>
+          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=false; wizard = 'Receive → Success', '2 parts waiting to receive', with Cancel / Complete Without Receiving / Receive Parts (S3-01-wizard-optional.png).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>C29303</t>
+          <t>C29301</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29303</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29301</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-14</t>
+          <t>SF-COMP-12</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
+          <t>Verify the optional-invoice modal creates POs in the background and shows the count of parts to receive</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -2143,24 +2143,24 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14). | VIU-Verified 2026-07-08: optional-invoice (requireVendorInvoiceNumber=false) completion via simple-complete returned 201 and WO-&gt;Complete while both parts stayed status=waiting_to_receive (quantity_remaining preserved); UI Receive step shows the "Complete Without Receiving" button (VIU2-03-receive-step.png). Line-Receive-button sub-claim not separately asserted.</t>
+          <t>Parts-to-receive count verified 2026-07-06 ('2 parts waiting to receive', S3-01-wizard-optional.png). Background PO creation and pick-status detail not separately asserted. || [V2.4 2026-07-08] S3-R1 strengthened: order-before-receive — requested parts must never be routed to an empty receive screen. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Optional-invoice completion wizard (requireVendorInvoiceNumber OFF) receive step shows '2 parts waiting to receive' plus '1 part is not ordered yet - Going to receive parts or completing the work order will order those parts' (background PO creation); API confirmed an order_id assigned + waiting_to_receive. Both 'Receive Parts' and 'Complete Without Receiving' present.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29304</t>
+          <t>C29303</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29304</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29303</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-15</t>
+          <t>SF-COMP-14</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
+          <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G24" s="14" t="inlineStr">
@@ -2190,24 +2190,24 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Idempotency not driven in VIU. Needs live verification.</t>
+          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14). | VIU-Verified 2026-07-08: optional-invoice (requireVendorInvoiceNumber=false) completion via simple-complete returned 201 and WO-&gt;Complete while both parts stayed status=waiting_to_receive (quantity_remaining preserved); UI Receive step shows the "Complete Without Receiving" button (VIU2-03-receive-step.png). Line-Receive-button sub-claim not separately asserted.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29305</t>
+          <t>C29304</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29304</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-16</t>
+          <t>SF-COMP-15</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
+          <t>Idempotency not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29306</t>
+          <t>C29305</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-17</t>
+          <t>SF-COMP-16</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
+          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -2284,39 +2284,39 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
+          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29307</t>
+          <t>C29306</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-18</t>
+          <t>SF-COMP-17</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
+          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" s="14" t="inlineStr">
@@ -2331,24 +2331,24 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
+          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29309</t>
+          <t>C29307</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-COMP-18</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2378,39 +2378,39 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29310</t>
+          <t>C29309</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-21</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -2425,24 +2425,24 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29311</t>
+          <t>C29310</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-22</t>
+          <t>SF-COMP-21</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
+          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2472,34 +2472,34 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
+          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29312</t>
+          <t>C29311</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-COMP-22</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Completion — Line approval gate</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -2519,39 +2519,39 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29313</t>
+          <t>C29312</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -2566,39 +2566,39 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29322</t>
+          <t>C29313</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
+          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -2613,39 +2613,39 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
+          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29323</t>
+          <t>C29322</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-01</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
+          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -2660,24 +2660,24 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
+          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29324</t>
+          <t>C29323</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-02</t>
+          <t>SF-TECH-01</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
+          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
+          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29325</t>
+          <t>C29324</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-03</t>
+          <t>SF-TECH-02</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
+          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -2754,24 +2754,24 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
+          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29326</t>
+          <t>C29325</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-04</t>
+          <t>SF-TECH-03</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
+          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -2801,24 +2801,24 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
+          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29327</t>
+          <t>C29326</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-TECH-04</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -2848,24 +2848,24 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
+          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>C29328</t>
+          <t>C29327</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-TECH-05</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -2895,24 +2895,24 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
+          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>C29329</t>
+          <t>C29328</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-TECH-06</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -2942,24 +2942,24 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
+          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>C29330</t>
+          <t>C29329</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-08</t>
+          <t>SF-TECH-07</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
+          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -2984,44 +2984,44 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
+          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>C29331</t>
+          <t>C29330</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-TECH-08</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
+          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3031,29 +3031,29 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>C29332</t>
+          <t>C29331</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-VPART-01</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -3083,24 +3083,24 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>C29333</t>
+          <t>C29332</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-VPART-02</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3130,24 +3130,24 @@
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>C29334</t>
+          <t>C29333</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VPART-03</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -3177,24 +3177,24 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>C29335</t>
+          <t>C29334</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -3224,24 +3224,24 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>C29336</t>
+          <t>C29335</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VPART-05</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -3271,39 +3271,39 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>C29338</t>
+          <t>C29336</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-01</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>C29339</t>
+          <t>C29338</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-02</t>
+          <t>SF-VMIS-01</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
+          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -3365,24 +3365,24 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
+          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>C29341</t>
+          <t>C29339</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-02</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -3412,24 +3412,24 @@
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
+          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>C29342</t>
+          <t>C29341</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -3459,24 +3459,24 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>C29439</t>
+          <t>C29342</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-07</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -3506,34 +3506,34 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>C29344</t>
+          <t>C29439</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-VMIS-07</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -3553,24 +3553,24 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
+          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>C29345</t>
+          <t>C29344</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -3600,24 +3600,24 @@
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
+          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>C29346</t>
+          <t>C29345</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -3647,24 +3647,24 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
+          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>C29347</t>
+          <t>C29346</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -3694,24 +3694,24 @@
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
+          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>C29348</t>
+          <t>C29347</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -3741,24 +3741,24 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>C29349</t>
+          <t>C29348</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -3788,39 +3788,39 @@
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
+          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>C29350</t>
+          <t>C29349</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>C29351</t>
+          <t>C29350</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -3882,24 +3882,24 @@
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
+          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>C29352</t>
+          <t>C29351</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -3929,24 +3929,24 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>C29353</t>
+          <t>C29352</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -3976,24 +3976,24 @@
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>C29354</t>
+          <t>C29353</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -4023,24 +4023,24 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>C29355</t>
+          <t>C29354</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -4070,24 +4070,24 @@
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>C29356</t>
+          <t>C29355</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -4117,24 +4117,24 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
+          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>C29357</t>
+          <t>C29356</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -4164,24 +4164,24 @@
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
+          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>C29358</t>
+          <t>C29357</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -4211,34 +4211,34 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>C29360</t>
+          <t>C29358</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -4258,24 +4258,24 @@
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
+          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>C29361</t>
+          <t>C29360</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -4305,24 +4305,24 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
+          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>C29362</t>
+          <t>C29361</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G70" s="14" t="inlineStr">
@@ -4352,39 +4352,39 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>C29369</t>
+          <t>C29362</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -4399,24 +4399,24 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>C29370</t>
+          <t>C29369</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -4446,24 +4446,24 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
+          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>C29371</t>
+          <t>C29370</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-03</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -4473,12 +4473,12 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -4493,34 +4493,34 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>C29372</t>
+          <t>C29371</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-04</t>
+          <t>SF-RCV-03</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
+          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -4540,24 +4540,24 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>C29374</t>
+          <t>C29372</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-RCV-04</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -4567,12 +4567,12 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -4587,24 +4587,24 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
+          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>C29377</t>
+          <t>C29374</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -4634,24 +4634,24 @@
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>C29440</t>
+          <t>C29377</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-10</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -4681,39 +4681,39 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
+          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>C29378</t>
+          <t>C29440</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -4728,24 +4728,24 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
+          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>C29381</t>
+          <t>C29378</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
@@ -4775,39 +4775,39 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), and the PO left the Vendor-Missing group into the vendor's group (Receive enabled once PN+invoice supplied).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>C29383</t>
+          <t>C29381</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -4822,24 +4822,24 @@
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), and the PO left the Vendor-Missing group into the vendor's group (Receive enabled once PN+invoice supplied).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>C29384</t>
+          <t>C29383</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -4869,24 +4869,24 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
+          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>C29385</t>
+          <t>C29384</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -4916,39 +4916,39 @@
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
+          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>C29386</t>
+          <t>C29385</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-01</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Verify the Require Review setting drives the review flow when turned on</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
@@ -4963,24 +4963,24 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>C29387</t>
+          <t>C29386</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-02</t>
+          <t>SF-REV-01</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
@@ -5010,24 +5010,24 @@
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
+          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>C29388</t>
+          <t>C29387</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-02</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -5057,24 +5057,24 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
+          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>C29390</t>
+          <t>C29388</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-05</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
+          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>C29391</t>
+          <t>C29390</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-06</t>
+          <t>SF-REV-05</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
+          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>C29392</t>
+          <t>C29391</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-06</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -5198,24 +5198,24 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>Not separately asserted in VIU. Needs live verification.</t>
+          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>C29393</t>
+          <t>C29392</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-08</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -5240,29 +5240,29 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
+          <t>Not separately asserted in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>C29394</t>
+          <t>C29393</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-09</t>
+          <t>SF-REV-08</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
+          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
@@ -5287,29 +5287,29 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
         </is>
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
+          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>C29395</t>
+          <t>C29394</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-10</t>
+          <t>SF-REV-09</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -5334,29 +5334,29 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
+          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>C29397</t>
+          <t>C29395</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-REV-10</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
@@ -5381,29 +5381,29 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
         </is>
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
+          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>C29398</t>
+          <t>C29397</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -5433,34 +5433,34 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
+          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>C29401</t>
+          <t>C29398</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-01</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Verify the work order primary button reads 'Create Work Order'</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
@@ -5480,24 +5480,24 @@
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
+          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>C29402</t>
+          <t>C29401</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-02</t>
+          <t>SF-UX-01</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+          <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -5527,24 +5527,24 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
+          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>C29403</t>
+          <t>C29402</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-03</t>
+          <t>SF-UX-02</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
+          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
@@ -5574,39 +5574,39 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
+          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>C29405</t>
+          <t>C29403</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-01</t>
+          <t>SF-UX-03</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
+          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -5621,24 +5621,24 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
+          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>C29406</t>
+          <t>C29405</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-02</t>
+          <t>SF-PERM-01</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
+          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -5668,24 +5668,24 @@
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
+          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>C29407</t>
+          <t>C29406</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -5715,24 +5715,24 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
+          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>C29408</t>
+          <t>C29407</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -5757,29 +5757,29 @@
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
+          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>C29409</t>
+          <t>C29408</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
@@ -5804,29 +5804,29 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>C29410</t>
+          <t>C29409</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-PERM-05</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -5856,24 +5856,24 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>C29411</t>
+          <t>C29410</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-07</t>
+          <t>SF-PERM-06</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G103" s="14" t="inlineStr">
@@ -5898,29 +5898,29 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
+          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>C29412</t>
+          <t>C29411</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-08</t>
+          <t>SF-PERM-07</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -5945,29 +5945,29 @@
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
+          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
+          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>C29413</t>
+          <t>C29412</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-PERM-08</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -5992,29 +5992,29 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
+          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>C29414</t>
+          <t>C29413</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
@@ -6044,34 +6044,34 @@
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
+          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>C29415</t>
+          <t>C29414</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -6091,24 +6091,24 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
+          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>C29417</t>
+          <t>C29415</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -6138,24 +6138,24 @@
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
+          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>C29418</t>
+          <t>C29417</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-04</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -6165,7 +6165,7 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
@@ -6185,24 +6185,24 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>C29421</t>
+          <t>C29418</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-VAL-04</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
@@ -6232,24 +6232,24 @@
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
+          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>C29422</t>
+          <t>C29421</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -6279,24 +6279,24 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
+          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>C29424</t>
+          <t>C29422</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-VAL-08</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
@@ -6326,52 +6326,99 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
+          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
+          <t>C29424</t>
+        </is>
+      </c>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-10</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="inlineStr">
+        <is>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+        </is>
+      </c>
+      <c r="F113" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G113" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H113" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I113" s="12" t="inlineStr">
+        <is>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
           <t>C29425</t>
         </is>
       </c>
-      <c r="B113" s="13" t="inlineStr">
+      <c r="B114" s="13" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
         </is>
       </c>
-      <c r="C113" s="12" t="inlineStr">
+      <c r="C114" s="12" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="D113" s="12" t="inlineStr">
+      <c r="D114" s="12" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="E113" s="12" t="inlineStr">
+      <c r="E114" s="12" t="inlineStr">
         <is>
           <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
-      <c r="F113" s="12" t="inlineStr">
+      <c r="F114" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G113" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H113" s="12" t="inlineStr">
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H114" s="12" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="I113" s="12" t="inlineStr">
+      <c r="I114" s="12" t="inlineStr">
         <is>
           <t>PARTIAL in VIU — error not cleanly isolated (S17-02-approval-error.png). Needs a WO whose only blocker is the unapproved line. | VIU-Verified 2026-07-08: simple-complete with an unapproved (authorization_required) line returns 400 with text "All lines must be approved before completing the work order." (WO a71ec2f0).</t>
         </is>
@@ -6491,6 +6538,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B111" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId113"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6502,7 +6550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6660,17 +6708,17 @@
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>C29296</t>
+          <t>C29297</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29296</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29297</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-07</t>
+          <t>SF-COMP-08</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
@@ -6680,12 +6728,12 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Verify in-stock inventory parts decrement inventory and write Part History on simple completion</t>
+          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr">
@@ -6695,44 +6743,44 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q2 — Auto-receive of in-stock parts on simple completion — intended behaviour?</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>§8 open question — auto-receive of in-stock inventory on simple completion is UNCONFIRMED. Also relates to the 'bare status setter emits no events' data-integrity risk. Not driven in VIU. Confirm intended behavior. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4), so the completion expectations stand. || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed in-stock inventory parts DO decrement on-hand and write Part History on completion (the PO question is a separate concern). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive.</t>
+          <t>Auto-pick was ON in the VIU baseline, so the pick step was not exercised. Needs live verification with auto-pick OFF. || [FRESH VIU 2026-07-10 sv7301] PROGRESS: with autoPickInventoryParts=OFF (current org drift), adding inventory part P550848 left it status 'in_stock' (NOT auto-picked); simple-complete BE-BLOCKED 400 'All inventory and found parts must be picked before completing the work order.'; after line-level Pick (perform-request-status-action 201 -&gt; status picked) completion proceeded (201). Expected #2 (cannot complete until picked) and #3 (after pick, completes) PROVEN. Expected #1 (completion-MODAL Pick step offering 'Pick all from default bins'/'Review individually') NOT yet surfaced — pick was driven at line level, not via the completion wizard's pick step. Remains VIU-Pending on the modal pick-step UI.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>C29297</t>
+          <t>C29302</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29297</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29302</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-08</t>
+          <t>SF-COMP-13</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
+          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -6747,34 +6795,34 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Auto-pick was ON in the VIU baseline, so the pick step was not exercised. Needs live verification with auto-pick OFF.</t>
+          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>C29302</t>
+          <t>C29308</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29302</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-13</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -6794,39 +6842,39 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded).</t>
+          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>C29308</t>
+          <t>C29314</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -6836,29 +6884,29 @@
       </c>
       <c r="H7" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
         </is>
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip.</t>
+          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>C29314</t>
+          <t>C29315</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -6868,12 +6916,12 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -6888,34 +6936,34 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>C29315</t>
+          <t>C29316</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -6942,17 +6990,17 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>C29316</t>
+          <t>C29317</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -6962,12 +7010,12 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -6989,17 +7037,17 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>C29317</t>
+          <t>C29318</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -7009,12 +7057,12 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -7036,32 +7084,32 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>C29318</t>
+          <t>C29319</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -7083,32 +7131,32 @@
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>C29319</t>
+          <t>C29320</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -7123,24 +7171,24 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>C29320</t>
+          <t>C29321</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -7150,7 +7198,7 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -7170,39 +7218,39 @@
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>C29321</t>
+          <t>C29337</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -7212,7 +7260,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -7224,27 +7272,27 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>C29337</t>
+          <t>C29340</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -7259,29 +7307,29 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>C29340</t>
+          <t>C29343</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -7291,12 +7339,12 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -7311,39 +7359,39 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>C29343</t>
+          <t>C29359</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -7353,44 +7401,44 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>NOT BUILT. Needs dev complete. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a GENUINE special-order (vendor-source) cored part received on the Bulk Receive page to expose the Ok/Not-OK resolution. Confirmed again this pass: the only seedable core (catalog P550848) forces Source=Inventory (auto-picked, never routed through a receivable PO), and the manual part sub-form's Core Charge yields is_core=false. A vendor-source is_core part is not seedable in-app.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>C29359</t>
+          <t>C29363</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -7400,29 +7448,29 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a GENUINE special-order (vendor-source) cored part received on the Bulk Receive page to expose the Ok/Not-OK resolution. Confirmed again this pass: the only seedable core (catalog P550848) forces Source=Inventory (auto-picked, never routed through a receivable PO), and the manual part sub-form's Core Charge yields is_core=false. A vendor-source is_core part is not seedable in-app.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>C29363</t>
+          <t>C29364</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -7432,7 +7480,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -7452,24 +7500,24 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>C29364</t>
+          <t>C29365</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -7479,7 +7527,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -7499,24 +7547,24 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>C29365</t>
+          <t>C29366</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -7526,12 +7574,12 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -7546,24 +7594,24 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>C29366</t>
+          <t>C29367</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -7573,12 +7621,12 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -7593,24 +7641,24 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29367</t>
+          <t>C29368</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -7620,12 +7668,12 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -7640,39 +7688,39 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29368</t>
+          <t>C29373</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -7682,29 +7730,29 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
+          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29373</t>
+          <t>C29375</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -7714,12 +7762,12 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -7729,29 +7777,29 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
+          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29375</t>
+          <t>C29376</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -7761,12 +7809,12 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -7776,39 +7824,39 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29376</t>
+          <t>C29379</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -7823,29 +7871,29 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29379</t>
+          <t>C29380</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -7855,12 +7903,12 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
@@ -7875,24 +7923,24 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
+          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29380</t>
+          <t>C29382</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -7902,7 +7950,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -7922,34 +7970,34 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
+          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29382</t>
+          <t>C29389</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -7964,29 +8012,29 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29389</t>
+          <t>C29396</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -7996,12 +8044,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -8011,29 +8059,29 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29396</t>
+          <t>C29399</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -8043,12 +8091,12 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
@@ -8058,39 +8106,39 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29399</t>
+          <t>C29404</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-UX-04</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -8105,39 +8153,39 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29404</t>
+          <t>C29416</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-04</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -8152,29 +8200,29 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
+          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29416</t>
+          <t>C29419</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -8184,12 +8232,12 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -8204,24 +8252,24 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29419</t>
+          <t>C29420</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -8231,7 +8279,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -8258,17 +8306,17 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29420</t>
+          <t>C29423</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -8278,12 +8326,12 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
@@ -8298,39 +8346,39 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>C29423</t>
+          <t>C29426</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-QB-01</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G39" s="15" t="inlineStr">
@@ -8340,29 +8388,29 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
+          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>C29426</t>
+          <t>C29428</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-01</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -8372,7 +8420,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -8387,29 +8435,29 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q2 — Inventory decrement / Part History on skip-path completion.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>C29428</t>
+          <t>C29429</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -8419,12 +8467,12 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G41" s="15" t="inlineStr">
@@ -8439,24 +8487,24 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>C29429</t>
+          <t>C29430</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-04</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -8466,7 +8514,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -8493,17 +8541,17 @@
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>C29430</t>
+          <t>C29431</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -8513,7 +8561,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -8533,24 +8581,24 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>C29431</t>
+          <t>C29432</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-06</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -8560,7 +8608,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -8580,24 +8628,24 @@
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>C29432</t>
+          <t>C29433</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-07</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -8607,7 +8655,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -8626,53 +8674,6 @@
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>C29433</t>
-        </is>
-      </c>
-      <c r="B46" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
@@ -8724,7 +8725,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B46" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C34" s="2" t="n"/>
     </row>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I114"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2385,17 +2385,17 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29309</t>
+          <t>C29308</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -2425,39 +2425,39 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29310</t>
+          <t>C29309</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-21</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2472,24 +2472,24 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29311</t>
+          <t>C29310</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-22</t>
+          <t>SF-COMP-21</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
+          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
@@ -2519,34 +2519,34 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
+          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29312</t>
+          <t>C29311</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-COMP-22</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Completion — Line approval gate</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -2566,39 +2566,39 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29313</t>
+          <t>C29312</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -2613,39 +2613,39 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29322</t>
+          <t>C29313</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
+          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -2660,39 +2660,39 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
+          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29323</t>
+          <t>C29322</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-01</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
+          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
+          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29324</t>
+          <t>C29323</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-02</t>
+          <t>SF-TECH-01</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
+          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -2754,24 +2754,24 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
+          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29325</t>
+          <t>C29324</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-03</t>
+          <t>SF-TECH-02</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
+          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -2801,24 +2801,24 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
+          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29326</t>
+          <t>C29325</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-04</t>
+          <t>SF-TECH-03</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
+          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -2848,24 +2848,24 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
+          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>C29327</t>
+          <t>C29326</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-TECH-04</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -2895,24 +2895,24 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
+          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>C29328</t>
+          <t>C29327</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-TECH-05</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -2922,7 +2922,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -2942,24 +2942,24 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
+          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>C29329</t>
+          <t>C29328</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-TECH-06</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -2989,24 +2989,24 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
+          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>C29330</t>
+          <t>C29329</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-08</t>
+          <t>SF-TECH-07</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
+          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3031,44 +3031,44 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
+          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>C29331</t>
+          <t>C29330</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-TECH-08</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
+          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -3078,29 +3078,29 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>C29332</t>
+          <t>C29331</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-VPART-01</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -3130,24 +3130,24 @@
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>C29333</t>
+          <t>C29332</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-VPART-02</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -3177,24 +3177,24 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>C29334</t>
+          <t>C29333</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VPART-03</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -3224,24 +3224,24 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>C29335</t>
+          <t>C29334</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -3271,24 +3271,24 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>C29336</t>
+          <t>C29335</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VPART-05</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -3318,39 +3318,39 @@
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>C29338</t>
+          <t>C29336</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-01</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -3365,34 +3365,34 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>C29339</t>
+          <t>C29337</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-02</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -3412,24 +3412,24 @@
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>C29341</t>
+          <t>C29338</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-01</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -3459,24 +3459,24 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
+          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>C29342</t>
+          <t>C29339</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-VMIS-02</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
+          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>C29439</t>
+          <t>C29341</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-07</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -3553,34 +3553,34 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>C29344</t>
+          <t>C29342</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -3600,34 +3600,34 @@
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>C29345</t>
+          <t>C29439</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-VMIS-07</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -3647,24 +3647,24 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
+          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>C29346</t>
+          <t>C29344</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -3694,24 +3694,24 @@
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
+          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>C29347</t>
+          <t>C29345</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G57" s="14" t="inlineStr">
@@ -3741,24 +3741,24 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
+          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>C29348</t>
+          <t>C29346</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -3788,24 +3788,24 @@
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
+          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>C29349</t>
+          <t>C29347</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -3835,34 +3835,34 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>C29350</t>
+          <t>C29348</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -3882,39 +3882,39 @@
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
+          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>C29351</t>
+          <t>C29349</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -3929,24 +3929,24 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>C29352</t>
+          <t>C29350</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -3956,7 +3956,7 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -3976,24 +3976,24 @@
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
+          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>C29353</t>
+          <t>C29351</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -4023,24 +4023,24 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>C29354</t>
+          <t>C29352</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -4070,24 +4070,24 @@
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>C29355</t>
+          <t>C29353</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -4117,24 +4117,24 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>C29356</t>
+          <t>C29354</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -4164,24 +4164,24 @@
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>C29357</t>
+          <t>C29355</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -4211,24 +4211,24 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
+          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>C29358</t>
+          <t>C29356</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -4258,34 +4258,34 @@
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
+          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>C29360</t>
+          <t>C29357</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -4305,34 +4305,34 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>C29361</t>
+          <t>C29358</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -4352,24 +4352,24 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
+          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>C29362</t>
+          <t>C29360</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G71" s="14" t="inlineStr">
@@ -4399,34 +4399,34 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
+          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>C29369</t>
+          <t>C29361</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -4446,39 +4446,39 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>C29370</t>
+          <t>C29362</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -4493,39 +4493,39 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>C29371</t>
+          <t>C29363</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-03</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -4540,39 +4540,39 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED on the built Bulk Receive page (Story 8/10 inline PN-fix UI is shipped; the BATCH-6 'appears tied to Story 8, NOT built' note is SUPERSEDED). A no-number part shows 'Missing part number' (text visible); the inline input_part_number_{partId} Edit -&gt; enter PN -&gt; the 'Missing part number' text clears AND the PN persists immediately to the backend (order item.part_number=ZZPN-FIX01, PartRequest pn set) without a page reload.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>C29372</t>
+          <t>C29369</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-04</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -4587,34 +4587,34 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
+          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>C29374</t>
+          <t>C29370</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -4634,34 +4634,34 @@
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>C29377</t>
+          <t>C29371</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-RCV-03</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -4681,24 +4681,24 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>C29440</t>
+          <t>C29372</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-10</t>
+          <t>SF-RCV-04</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -4728,34 +4728,34 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
+          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>C29378</t>
+          <t>C29374</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -4775,34 +4775,34 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>C29381</t>
+          <t>C29377</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
@@ -4822,39 +4822,39 @@
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), and the PO left the Vendor-Missing group into the vendor's group (Receive enabled once PN+invoice supplied).</t>
+          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>C29383</t>
+          <t>C29440</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -4869,39 +4869,39 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
+          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>C29384</t>
+          <t>C29378</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -4916,39 +4916,39 @@
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>C29385</t>
+          <t>C29381</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
@@ -4963,34 +4963,34 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), and the PO left the Vendor-Missing group into the vendor's group (Receive enabled once PN+invoice supplied).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>C29386</t>
+          <t>C29383</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-01</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Verify the Require Review setting drives the review flow when turned on</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
+          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>C29387</t>
+          <t>C29384</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-02</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -5057,39 +5057,39 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
+          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>C29388</t>
+          <t>C29385</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>C29390</t>
+          <t>C29386</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-05</t>
+          <t>SF-REV-01</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+          <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
+          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>C29391</t>
+          <t>C29387</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-06</t>
+          <t>SF-REV-02</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -5198,24 +5198,24 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
+          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>C29392</t>
+          <t>C29388</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -5245,24 +5245,24 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>Not separately asserted in VIU. Needs live verification.</t>
+          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>C29393</t>
+          <t>C29390</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-08</t>
+          <t>SF-REV-05</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -5287,29 +5287,29 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
+          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>C29394</t>
+          <t>C29391</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-09</t>
+          <t>SF-REV-06</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
+          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -5334,29 +5334,29 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
+          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>C29395</t>
+          <t>C29392</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-10</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
@@ -5381,29 +5381,29 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
+          <t>Not separately asserted in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>C29397</t>
+          <t>C29393</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-REV-08</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G93" s="14" t="inlineStr">
@@ -5428,29 +5428,29 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
+          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>C29398</t>
+          <t>C29394</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-REV-09</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -5475,39 +5475,39 @@
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>C29401</t>
+          <t>C29395</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-01</t>
+          <t>SF-REV-10</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Verify the work order primary button reads 'Create Work Order'</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -5522,39 +5522,39 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
+          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>C29402</t>
+          <t>C29397</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-02</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
@@ -5574,34 +5574,34 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
+          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>C29403</t>
+          <t>C29398</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-03</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -5621,39 +5621,39 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
+          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>C29405</t>
+          <t>C29401</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-01</t>
+          <t>SF-UX-01</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
+          <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -5668,34 +5668,34 @@
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
+          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>C29406</t>
+          <t>C29402</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-02</t>
+          <t>SF-UX-02</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
+          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -5715,34 +5715,34 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
+          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>C29407</t>
+          <t>C29403</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-UX-03</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -5762,24 +5762,24 @@
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
+          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>C29408</t>
+          <t>C29405</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-PERM-01</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
@@ -5804,29 +5804,29 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
+          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>C29409</t>
+          <t>C29406</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -5856,24 +5856,24 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
+          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>C29410</t>
+          <t>C29407</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
@@ -5903,24 +5903,24 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
+          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>C29411</t>
+          <t>C29408</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-07</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -5945,29 +5945,29 @@
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>C29412</t>
+          <t>C29409</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-08</t>
+          <t>SF-PERM-05</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -5977,12 +5977,12 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G105" s="14" t="inlineStr">
@@ -5992,29 +5992,29 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>C29413</t>
+          <t>C29410</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-PERM-06</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6024,12 +6024,12 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -6044,24 +6044,24 @@
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>C29414</t>
+          <t>C29411</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-PERM-07</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
@@ -6086,39 +6086,39 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
+          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>C29415</t>
+          <t>C29412</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-PERM-08</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
@@ -6133,44 +6133,44 @@
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
         </is>
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
+          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>C29417</t>
+          <t>C29413</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -6185,39 +6185,39 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
+          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>C29418</t>
+          <t>C29414</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-04</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
@@ -6232,24 +6232,24 @@
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
+          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>C29421</t>
+          <t>C29415</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G111" s="14" t="inlineStr">
@@ -6279,24 +6279,24 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
+          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>C29422</t>
+          <t>C29417</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
@@ -6326,24 +6326,24 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>C29424</t>
+          <t>C29418</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-VAL-04</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G113" s="14" t="inlineStr">
@@ -6373,52 +6373,287 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
+          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
+          <t>C29419</t>
+        </is>
+      </c>
+      <c r="B114" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-05</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="inlineStr">
+        <is>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+        </is>
+      </c>
+      <c r="F114" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G114" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H114" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I114" s="12" t="inlineStr">
+        <is>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>C29420</t>
+        </is>
+      </c>
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-06</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present. Cannot receive without BOTH a vendor and a part number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>C29421</t>
+        </is>
+      </c>
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-07</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I116" s="12" t="inlineStr">
+        <is>
+          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>C29422</t>
+        </is>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-08</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G117" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>C29424</t>
+        </is>
+      </c>
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-10</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
           <t>C29425</t>
         </is>
       </c>
-      <c r="B114" s="13" t="inlineStr">
+      <c r="B119" s="13" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
         </is>
       </c>
-      <c r="C114" s="12" t="inlineStr">
+      <c r="C119" s="12" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="D114" s="12" t="inlineStr">
+      <c r="D119" s="12" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="E114" s="12" t="inlineStr">
+      <c r="E119" s="12" t="inlineStr">
         <is>
           <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
-      <c r="F114" s="12" t="inlineStr">
+      <c r="F119" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G114" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H114" s="12" t="inlineStr">
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="I114" s="12" t="inlineStr">
+      <c r="I119" s="12" t="inlineStr">
         <is>
           <t>PARTIAL in VIU — error not cleanly isolated (S17-02-approval-error.png). Needs a WO whose only blocker is the unapproved line. | VIU-Verified 2026-07-08: simple-complete with an unapproved (authorization_required) line returns 400 with text "All lines must be approved before completing the work order." (WO a71ec2f0).</t>
         </is>
@@ -6539,6 +6774,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B112" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId118"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6550,7 +6790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6802,32 +7042,32 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>C29308</t>
+          <t>C29314</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -6837,29 +7077,29 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
         </is>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip.</t>
+          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>C29314</t>
+          <t>C29315</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -6869,12 +7109,12 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -6889,34 +7129,34 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>C29315</t>
+          <t>C29316</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -6943,17 +7183,17 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>C29316</t>
+          <t>C29317</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -6963,12 +7203,12 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -6990,17 +7230,17 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>C29317</t>
+          <t>C29318</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -7010,12 +7250,12 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -7037,32 +7277,32 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>C29318</t>
+          <t>C29319</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -7084,32 +7324,32 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>C29319</t>
+          <t>C29320</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -7124,24 +7364,24 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>C29320</t>
+          <t>C29321</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -7151,7 +7391,7 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -7171,39 +7411,39 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>C29321</t>
+          <t>C29340</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -7213,44 +7453,44 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>C29337</t>
+          <t>C29343</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -7260,7 +7500,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed + drive the vendorless / no-PN part add flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
@@ -7272,32 +7512,32 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>C29340</t>
+          <t>C29359</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -7307,44 +7547,44 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
+          <t>NOT BUILT. Needs dev complete. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a GENUINE special-order (vendor-source) cored part received on the Bulk Receive page to expose the Ok/Not-OK resolution. Confirmed again this pass: the only seedable core (catalog P550848) forces Source=Inventory (auto-picked, never routed through a receivable PO), and the manual part sub-form's Core Charge yields is_core=false. A vendor-source is_core part is not seedable in-app.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>C29343</t>
+          <t>C29364</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -7354,44 +7594,44 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>C29359</t>
+          <t>C29365</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -7401,29 +7641,29 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a GENUINE special-order (vendor-source) cored part received on the Bulk Receive page to expose the Ok/Not-OK resolution. Confirmed again this pass: the only seedable core (catalog P550848) forces Source=Inventory (auto-picked, never routed through a receivable PO), and the manual part sub-form's Core Charge yields is_core=false. A vendor-source is_core part is not seedable in-app.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>C29363</t>
+          <t>C29366</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -7433,12 +7673,12 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -7453,24 +7693,24 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>C29364</t>
+          <t>C29367</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -7480,7 +7720,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -7500,24 +7740,24 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>C29365</t>
+          <t>C29368</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -7527,12 +7767,12 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -7547,39 +7787,39 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>C29366</t>
+          <t>C29373</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -7589,44 +7829,44 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
+          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>C29367</t>
+          <t>C29375</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -7636,44 +7876,44 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29368</t>
+          <t>C29376</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -7683,39 +7923,39 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29373</t>
+          <t>C29379</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -7730,44 +7970,44 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29375</t>
+          <t>C29380</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -7777,44 +8017,44 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
+          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29376</t>
+          <t>C29382</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -7824,44 +8064,44 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29379</t>
+          <t>C29389</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
@@ -7871,44 +8111,44 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29380</t>
+          <t>C29396</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
@@ -7918,39 +8158,39 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
+          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29382</t>
+          <t>C29399</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -7965,39 +8205,39 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29389</t>
+          <t>C29404</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-UX-04</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -8012,44 +8252,44 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29396</t>
+          <t>C29416</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -8059,39 +8299,39 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
+          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29399</t>
+          <t>C29423</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -8106,44 +8346,44 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29404</t>
+          <t>C29426</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-04</t>
+          <t>SF-QB-01</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
+          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -8153,44 +8393,44 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
+          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29416</t>
+          <t>C29428</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr">
@@ -8200,44 +8440,44 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29419</t>
+          <t>C29429</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G36" s="15" t="inlineStr">
@@ -8247,7 +8487,7 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -8259,32 +8499,32 @@
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29420</t>
+          <t>C29430</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
@@ -8294,7 +8534,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
@@ -8306,27 +8546,27 @@
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29423</t>
+          <t>C29431</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -8341,29 +8581,29 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
+          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>C29426</t>
+          <t>C29432</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-01</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -8373,12 +8613,12 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G39" s="15" t="inlineStr">
@@ -8393,24 +8633,24 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>C29428</t>
+          <t>C29433</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -8420,12 +8660,12 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
@@ -8439,241 +8679,6 @@
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>C29429</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
-        </is>
-      </c>
-      <c r="C41" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-04</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E41" s="12" t="inlineStr">
-        <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
-        </is>
-      </c>
-      <c r="F41" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G41" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>C29430</t>
-        </is>
-      </c>
-      <c r="B42" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-05</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G42" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>C29431</t>
-        </is>
-      </c>
-      <c r="B43" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-06</t>
-        </is>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I43" s="12" t="inlineStr">
-        <is>
-          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>C29432</t>
-        </is>
-      </c>
-      <c r="B44" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G44" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>C29433</t>
-        </is>
-      </c>
-      <c r="B45" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
@@ -8720,11 +8725,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B43" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B44" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B45" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9453,9 +9453,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G10" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip.</t>
+          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
         </is>
       </c>
     </row>
@@ -10064,9 +10064,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G23" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G23" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
         </is>
       </c>
     </row>
@@ -11098,9 +11098,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G45" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G45" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
         </is>
       </c>
     </row>
@@ -11145,9 +11145,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G46" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G46" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present. Cannot receive without BOTH a vendor and a part number.</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="B32" s="7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C34" s="2" t="n"/>
     </row>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I119"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2150,17 +2150,17 @@
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29303</t>
+          <t>C29302</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29303</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29302</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-14</t>
+          <t>SF-COMP-13</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
+          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -2190,24 +2190,24 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14). | VIU-Verified 2026-07-08: optional-invoice (requireVendorInvoiceNumber=false) completion via simple-complete returned 201 and WO-&gt;Complete while both parts stayed status=waiting_to_receive (quantity_remaining preserved); UI Receive step shows the "Complete Without Receiving" button (VIU2-03-receive-step.png). Line-Receive-button sub-claim not separately asserted.</t>
+          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded). || [FRESH VIU 2026-07-10 sv7301] VERIFIED (OBS-5 consolidation; supersedes BATCH-6 BUG-11 block). With requireVendorInvoiceNumber=OFF, the optional-invoice completion wizard shows 'N parts waiting to receive' + 'Clicking Receive Parts will take you to the purchase order page' + a background-order note; clicking Receive Parts navigated to the consolidated shared receive page /bulk-receive?workOrderId=...&amp;returnTo=WorkOrder ('Receive Vendor Parts', receive all vendors at once) — the shipped shared receive surface (replaces the legacy Accept Delivery named in the case, per OBS-5). Setting restored.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29304</t>
+          <t>C29303</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29304</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29303</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-15</t>
+          <t>SF-COMP-14</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
+          <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" s="14" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Idempotency not driven in VIU. Needs live verification.</t>
+          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14). | VIU-Verified 2026-07-08: optional-invoice (requireVendorInvoiceNumber=false) completion via simple-complete returned 201 and WO-&gt;Complete while both parts stayed status=waiting_to_receive (quantity_remaining preserved); UI Receive step shows the "Complete Without Receiving" button (VIU2-03-receive-step.png). Line-Receive-button sub-claim not separately asserted.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29305</t>
+          <t>C29304</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29304</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-16</t>
+          <t>SF-COMP-15</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -2284,24 +2284,24 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
+          <t>Idempotency not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29306</t>
+          <t>C29305</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-17</t>
+          <t>SF-COMP-16</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
+          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -2331,39 +2331,39 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
+          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29307</t>
+          <t>C29306</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-18</t>
+          <t>SF-COMP-17</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
+          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
@@ -2378,24 +2378,24 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
+          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29308</t>
+          <t>C29307</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-COMP-18</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -2425,24 +2425,24 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
+          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29309</t>
+          <t>C29308</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2472,39 +2472,39 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29310</t>
+          <t>C29309</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-21</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
@@ -2519,24 +2519,24 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29311</t>
+          <t>C29310</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-22</t>
+          <t>SF-COMP-21</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
+          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -2566,34 +2566,34 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
+          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29312</t>
+          <t>C29311</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-COMP-22</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Completion — Line approval gate</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -2613,39 +2613,39 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29313</t>
+          <t>C29312</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -2660,39 +2660,39 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29322</t>
+          <t>C29313</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
+          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -2707,39 +2707,39 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
+          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29323</t>
+          <t>C29322</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-01</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
+          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -2754,24 +2754,24 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
+          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29324</t>
+          <t>C29323</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-02</t>
+          <t>SF-TECH-01</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
+          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -2801,24 +2801,24 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
+          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29325</t>
+          <t>C29324</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-03</t>
+          <t>SF-TECH-02</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
+          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -2848,24 +2848,24 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
+          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>C29326</t>
+          <t>C29325</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-04</t>
+          <t>SF-TECH-03</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
+          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -2895,24 +2895,24 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
+          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>C29327</t>
+          <t>C29326</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-TECH-04</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -2942,24 +2942,24 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
+          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>C29328</t>
+          <t>C29327</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-TECH-05</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -2989,24 +2989,24 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
+          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>C29329</t>
+          <t>C29328</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-TECH-06</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3016,12 +3016,12 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3036,24 +3036,24 @@
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
+          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>C29330</t>
+          <t>C29329</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-08</t>
+          <t>SF-TECH-07</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
+          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -3078,44 +3078,44 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
+          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>C29331</t>
+          <t>C29330</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-TECH-08</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
+          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3125,29 +3125,29 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>C29332</t>
+          <t>C29331</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-VPART-01</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -3177,24 +3177,24 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>C29333</t>
+          <t>C29332</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-VPART-02</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -3224,24 +3224,24 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>C29334</t>
+          <t>C29333</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VPART-03</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -3271,24 +3271,24 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>C29335</t>
+          <t>C29334</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>C29336</t>
+          <t>C29335</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VPART-05</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -3365,24 +3365,24 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>C29337</t>
+          <t>C29336</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -3412,34 +3412,34 @@
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>C29338</t>
+          <t>C29337</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-01</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -3459,24 +3459,24 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>C29339</t>
+          <t>C29338</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-02</t>
+          <t>SF-VMIS-01</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
+          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
+          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>C29341</t>
+          <t>C29339</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-02</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3533,12 +3533,12 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G53" s="14" t="inlineStr">
@@ -3553,24 +3553,24 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
+          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>C29342</t>
+          <t>C29341</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -3600,24 +3600,24 @@
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>C29439</t>
+          <t>C29342</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-07</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -3647,34 +3647,34 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>C29344</t>
+          <t>C29439</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-VMIS-07</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -3694,24 +3694,24 @@
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
+          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>C29345</t>
+          <t>C29344</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -3741,24 +3741,24 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
+          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>C29346</t>
+          <t>C29345</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -3788,24 +3788,24 @@
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
+          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>C29347</t>
+          <t>C29346</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
+          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>C29348</t>
+          <t>C29347</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
@@ -3882,24 +3882,24 @@
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>C29349</t>
+          <t>C29348</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -3929,39 +3929,39 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
+          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>C29350</t>
+          <t>C29349</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -3976,24 +3976,24 @@
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>C29351</t>
+          <t>C29350</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -4023,24 +4023,24 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
+          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>C29352</t>
+          <t>C29351</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -4070,24 +4070,24 @@
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>C29353</t>
+          <t>C29352</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -4117,24 +4117,24 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>C29354</t>
+          <t>C29353</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -4164,24 +4164,24 @@
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>C29355</t>
+          <t>C29354</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -4211,24 +4211,24 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>C29356</t>
+          <t>C29355</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -4258,24 +4258,24 @@
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
+          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>C29357</t>
+          <t>C29356</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -4305,24 +4305,24 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
+          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>C29358</t>
+          <t>C29357</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -4352,34 +4352,34 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>C29360</t>
+          <t>C29358</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -4399,24 +4399,24 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
+          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>C29361</t>
+          <t>C29360</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -4446,24 +4446,24 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
+          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>C29362</t>
+          <t>C29361</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -4473,12 +4473,12 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G73" s="14" t="inlineStr">
@@ -4493,39 +4493,39 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>C29363</t>
+          <t>C29362</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -4540,34 +4540,34 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED on the built Bulk Receive page (Story 8/10 inline PN-fix UI is shipped; the BATCH-6 'appears tied to Story 8, NOT built' note is SUPERSEDED). A no-number part shows 'Missing part number' (text visible); the inline input_part_number_{partId} Edit -&gt; enter PN -&gt; the 'Missing part number' text clears AND the PN persists immediately to the backend (order item.part_number=ZZPN-FIX01, PartRequest pn set) without a page reload.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>C29369</t>
+          <t>C29363</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -4587,24 +4587,24 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED on the built Bulk Receive page (Story 8/10 inline PN-fix UI is shipped; the BATCH-6 'appears tied to Story 8, NOT built' note is SUPERSEDED). A no-number part shows 'Missing part number' (text visible); the inline input_part_number_{partId} Edit -&gt; enter PN -&gt; the 'Missing part number' text clears AND the PN persists immediately to the backend (order item.part_number=ZZPN-FIX01, PartRequest pn set) without a page reload.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>C29370</t>
+          <t>C29369</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -4634,24 +4634,24 @@
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
+          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>C29371</t>
+          <t>C29370</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-03</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
@@ -4681,34 +4681,34 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>C29372</t>
+          <t>C29371</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-04</t>
+          <t>SF-RCV-03</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
+          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -4728,24 +4728,24 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>C29374</t>
+          <t>C29372</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-RCV-04</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
@@ -4775,24 +4775,24 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
+          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>C29377</t>
+          <t>C29374</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -4822,24 +4822,24 @@
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>C29440</t>
+          <t>C29377</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-10</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -4869,39 +4869,39 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
+          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>C29378</t>
+          <t>C29440</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -4916,24 +4916,24 @@
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
+          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>C29381</t>
+          <t>C29378</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -4943,12 +4943,12 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
@@ -4963,39 +4963,39 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), and the PO left the Vendor-Missing group into the vendor's group (Receive enabled once PN+invoice supplied).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>C29383</t>
+          <t>C29381</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -5010,24 +5010,24 @@
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), and the PO left the Vendor-Missing group into the vendor's group (Receive enabled once PN+invoice supplied).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>C29384</t>
+          <t>C29383</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -5057,24 +5057,24 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
+          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>C29385</t>
+          <t>C29384</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -5104,39 +5104,39 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
+          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>C29386</t>
+          <t>C29385</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-01</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Verify the Require Review setting drives the review flow when turned on</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>C29387</t>
+          <t>C29386</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-02</t>
+          <t>SF-REV-01</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
@@ -5198,24 +5198,24 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
+          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>C29388</t>
+          <t>C29387</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-02</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -5245,24 +5245,24 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
+          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>C29390</t>
+          <t>C29388</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-05</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -5292,24 +5292,24 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
+          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>C29391</t>
+          <t>C29389</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-06</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -5339,24 +5339,24 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (supersedes BATCH-6 BUG-11 block). With requireReview=ON, the completion CTA = 'Send To Review' (wizard 'Complete &amp; Send to Review'); the receive step contains NO inline receive fields (0 qty/invoice inputs inside the dialog) and 'Receive Parts' routes to the shared receive page /bulk-receive (returnTo=WorkOrder), not an inline modal. Setting restored.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>C29392</t>
+          <t>C29390</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-05</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -5386,24 +5386,24 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>Not separately asserted in VIU. Needs live verification.</t>
+          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>C29393</t>
+          <t>C29391</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-08</t>
+          <t>SF-REV-06</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5413,12 +5413,12 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
+          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G93" s="14" t="inlineStr">
@@ -5428,29 +5428,29 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
+          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>C29394</t>
+          <t>C29392</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-09</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -5475,29 +5475,29 @@
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
+          <t>Not separately asserted in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>C29395</t>
+          <t>C29393</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-10</t>
+          <t>SF-REV-08</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
+          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
@@ -5522,29 +5522,29 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
+          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>C29397</t>
+          <t>C29394</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-REV-09</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -5569,29 +5569,29 @@
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>C29398</t>
+          <t>C29395</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-REV-10</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -5616,39 +5616,39 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
+          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>C29401</t>
+          <t>C29397</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-01</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Verify the work order primary button reads 'Create Work Order'</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
@@ -5668,34 +5668,34 @@
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
+          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>C29402</t>
+          <t>C29398</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-02</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -5715,24 +5715,24 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
+          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>C29403</t>
+          <t>C29401</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-03</t>
+          <t>SF-UX-01</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
+          <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -5762,39 +5762,39 @@
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
+          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>C29405</t>
+          <t>C29402</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-01</t>
+          <t>SF-UX-02</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
+          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
@@ -5809,34 +5809,34 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
+          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>C29406</t>
+          <t>C29403</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-02</t>
+          <t>SF-UX-03</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
+          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -5856,24 +5856,24 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
+          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>C29407</t>
+          <t>C29405</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-PERM-01</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G103" s="14" t="inlineStr">
@@ -5903,24 +5903,24 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
+          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>C29408</t>
+          <t>C29406</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
@@ -5945,29 +5945,29 @@
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
+          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>C29409</t>
+          <t>C29407</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -5997,24 +5997,24 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
+          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>C29410</t>
+          <t>C29408</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
@@ -6039,29 +6039,29 @@
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>C29411</t>
+          <t>C29409</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-07</t>
+          <t>SF-PERM-05</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -6071,12 +6071,12 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
@@ -6086,29 +6086,29 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>C29412</t>
+          <t>C29410</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-08</t>
+          <t>SF-PERM-06</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -6133,29 +6133,29 @@
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
+          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>C29413</t>
+          <t>C29411</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-PERM-07</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
+          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>C29414</t>
+          <t>C29412</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-PERM-08</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
@@ -6227,39 +6227,39 @@
       </c>
       <c r="H110" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
         </is>
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
+          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>C29415</t>
+          <t>C29413</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -6279,39 +6279,39 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
+          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>C29417</t>
+          <t>C29414</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
@@ -6326,24 +6326,24 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
+          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>C29418</t>
+          <t>C29415</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-04</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G113" s="14" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
+          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>C29419</t>
+          <t>C29417</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G114" s="14" t="inlineStr">
@@ -6420,24 +6420,24 @@
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
         <is>
-          <t>C29420</t>
+          <t>C29418</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-VAL-04</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -6447,12 +6447,12 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G115" s="14" t="inlineStr">
@@ -6467,24 +6467,24 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present. Cannot receive without BOTH a vendor and a part number.</t>
+          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>C29421</t>
+          <t>C29419</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
@@ -6514,24 +6514,24 @@
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
-          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
-          <t>C29422</t>
+          <t>C29420</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G117" s="14" t="inlineStr">
@@ -6561,24 +6561,24 @@
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present. Cannot receive without BOTH a vendor and a part number.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t>C29424</t>
+          <t>C29421</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G118" s="14" t="inlineStr">
@@ -6608,52 +6608,146 @@
       </c>
       <c r="I118" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
+          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
         <is>
+          <t>C29422</t>
+        </is>
+      </c>
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-08</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="inlineStr">
+        <is>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+        </is>
+      </c>
+      <c r="F119" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>C29424</t>
+        </is>
+      </c>
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-10</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="inlineStr">
+        <is>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+        </is>
+      </c>
+      <c r="F120" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H120" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I120" s="12" t="inlineStr">
+        <is>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
           <t>C29425</t>
         </is>
       </c>
-      <c r="B119" s="13" t="inlineStr">
+      <c r="B121" s="13" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
         </is>
       </c>
-      <c r="C119" s="12" t="inlineStr">
+      <c r="C121" s="12" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="D119" s="12" t="inlineStr">
+      <c r="D121" s="12" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="E119" s="12" t="inlineStr">
+      <c r="E121" s="12" t="inlineStr">
         <is>
           <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
-      <c r="F119" s="12" t="inlineStr">
+      <c r="F121" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G119" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H119" s="12" t="inlineStr">
+      <c r="G121" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="I119" s="12" t="inlineStr">
+      <c r="I121" s="12" t="inlineStr">
         <is>
           <t>PARTIAL in VIU — error not cleanly isolated (S17-02-approval-error.png). Needs a WO whose only blocker is the unapproved line. | VIU-Verified 2026-07-08: simple-complete with an unapproved (authorization_required) line returns 400 with text "All lines must be approved before completing the work order." (WO a71ec2f0).</t>
         </is>
@@ -6779,6 +6873,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId120"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6790,7 +6886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6995,32 +7091,32 @@
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>C29302</t>
+          <t>C29314</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29302</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-13</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
+          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -7030,29 +7126,29 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
         </is>
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded).</t>
+          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>C29314</t>
+          <t>C29315</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -7062,12 +7158,12 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G6" s="15" t="inlineStr">
@@ -7082,34 +7178,34 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>C29315</t>
+          <t>C29316</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -7136,17 +7232,17 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>C29316</t>
+          <t>C29317</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -7156,12 +7252,12 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -7183,17 +7279,17 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>C29317</t>
+          <t>C29318</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -7203,12 +7299,12 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -7230,32 +7326,32 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>C29318</t>
+          <t>C29319</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -7277,32 +7373,32 @@
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>C29319</t>
+          <t>C29320</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -7317,24 +7413,24 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>C29320</t>
+          <t>C29321</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -7344,7 +7440,7 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -7364,39 +7460,39 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>C29321</t>
+          <t>C29340</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -7406,29 +7502,29 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>C29340</t>
+          <t>C29343</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -7438,12 +7534,12 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -7458,39 +7554,39 @@
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>C29343</t>
+          <t>C29359</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -7500,44 +7596,44 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>NOT BUILT. Needs dev complete. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a GENUINE special-order (vendor-source) cored part received on the Bulk Receive page to expose the Ok/Not-OK resolution. Confirmed again this pass: the only seedable core (catalog P550848) forces Source=Inventory (auto-picked, never routed through a receivable PO), and the manual part sub-form's Core Charge yields is_core=false. A vendor-source is_core part is not seedable in-app.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>C29359</t>
+          <t>C29364</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -7547,29 +7643,29 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
         </is>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a GENUINE special-order (vendor-source) cored part received on the Bulk Receive page to expose the Ok/Not-OK resolution. Confirmed again this pass: the only seedable core (catalog P550848) forces Source=Inventory (auto-picked, never routed through a receivable PO), and the manual part sub-form's Core Charge yields is_core=false. A vendor-source is_core part is not seedable in-app.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED. Received a WO-PO vendor part carrying a NEW free-text part number (ZZPN-FIX01) via /bulk-receive (POST /api/orders/receive-requested-parts 200). NO new inventory part was created (GET /api/inventory/parts?search=ZZPN-FIX01 = 0 before AND after) — consistent with vendor-source parts being direct-to-WO consumption, not inventory-tracked (cf. SF-VPART-05); /api/catalogue/parts search 404. Whether a new PN should create a catalog/inventory item + Part History on receive needs the inventory-integrity/Part-History surface, which is BLOCKED-ENV (OBS-6). Applies equally to SF-PNFIX-03/06.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>C29364</t>
+          <t>C29365</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -7579,7 +7675,7 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -7599,24 +7695,24 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>C29365</t>
+          <t>C29366</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -7626,12 +7722,12 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -7646,24 +7742,24 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>C29366</t>
+          <t>C29367</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -7673,12 +7769,12 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -7693,24 +7789,24 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>C29367</t>
+          <t>C29368</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -7720,12 +7816,12 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -7740,39 +7836,39 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>C29368</t>
+          <t>C29373</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -7782,29 +7878,29 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
+          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>C29373</t>
+          <t>C29375</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -7814,12 +7910,12 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -7829,29 +7925,29 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
+          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>C29375</t>
+          <t>C29376</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -7861,12 +7957,12 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -7876,39 +7972,39 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29376</t>
+          <t>C29379</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -7923,29 +8019,29 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29379</t>
+          <t>C29380</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -7955,12 +8051,12 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -7975,24 +8071,24 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
+          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29380</t>
+          <t>C29382</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -8002,7 +8098,7 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -8022,39 +8118,39 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
+          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29382</t>
+          <t>C29396</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -8064,29 +8160,29 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
+          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29389</t>
+          <t>C29399</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -8096,7 +8192,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -8123,32 +8219,32 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29396</t>
+          <t>C29404</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-UX-04</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
@@ -8158,39 +8254,39 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
+          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29399</t>
+          <t>C29416</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -8205,39 +8301,39 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29404</t>
+          <t>C29423</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-04</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -8252,44 +8348,44 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29416</t>
+          <t>C29426</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-QB-01</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -8299,44 +8395,44 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
+          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29423</t>
+          <t>C29428</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
@@ -8346,29 +8442,29 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29426</t>
+          <t>C29429</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-01</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -8378,12 +8474,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -8398,24 +8494,24 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29428</t>
+          <t>C29430</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -8425,12 +8521,12 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr">
@@ -8445,24 +8541,24 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29429</t>
+          <t>C29431</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-04</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -8472,7 +8568,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -8492,24 +8588,24 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29430</t>
+          <t>C29432</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -8519,7 +8615,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -8539,24 +8635,24 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29431</t>
+          <t>C29433</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-06</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -8566,7 +8662,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -8585,100 +8681,6 @@
         </is>
       </c>
       <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>C29432</t>
-        </is>
-      </c>
-      <c r="B39" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="F39" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G39" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I39" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="12" t="inlineStr">
-        <is>
-          <t>C29433</t>
-        </is>
-      </c>
-      <c r="B40" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E40" s="12" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="F40" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G40" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I40" s="12" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
@@ -8723,8 +8725,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B39" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B40" r:id="rId39"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9359,9 +9359,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G8" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H8" s="12" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded).</t>
+          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded). || [FRESH VIU 2026-07-10 sv7301] VERIFIED (OBS-5 consolidation; supersedes BATCH-6 BUG-11 block). With requireVendorInvoiceNumber=OFF, the optional-invoice completion wizard shows 'N parts waiting to receive' + 'Clicking Receive Parts will take you to the purchase order page' + a background-order note; clicking Receive Parts navigated to the consolidated shared receive page /bulk-receive?workOrderId=...&amp;returnTo=WorkOrder ('Receive Vendor Parts', receive all vendors at once) — the shipped shared receive surface (replaces the legacy Accept Delivery named in the case, per OBS-5). Setting restored.</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED. Received a WO-PO vendor part carrying a NEW free-text part number (ZZPN-FIX01) via /bulk-receive (POST /api/orders/receive-requested-parts 200). NO new inventory part was created (GET /api/inventory/parts?search=ZZPN-FIX01 = 0 before AND after) — consistent with vendor-source parts being direct-to-WO consumption, not inventory-tracked (cf. SF-VPART-05); /api/catalogue/parts search 404. Whether a new PN should create a catalog/inventory item + Part History on receive needs the inventory-integrity/Part-History surface, which is BLOCKED-ENV (OBS-6). Applies equally to SF-PNFIX-03/06.</t>
         </is>
       </c>
     </row>
@@ -10440,9 +10440,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G31" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G31" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (supersedes BATCH-6 BUG-11 block). With requireReview=ON, the completion CTA = 'Send To Review' (wizard 'Complete &amp; Send to Review'); the receive step contains NO inline receive fields (0 qty/invoice inputs inside the dialog) and 'Receive Parts' routes to the shared receive page /bulk-receive (returnTo=WorkOrder), not an inline modal. Setting restored.</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -623,7 +623,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" s="2" t="n"/>
     </row>
@@ -1052,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1962,17 +1962,17 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>C29298</t>
+          <t>C29297</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29298</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29297</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-09</t>
+          <t>SF-COMP-08</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a new line to a completed work order returns it to Approved</t>
+          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -2002,24 +2002,24 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Return-to-Approved verified 2026-07-06 (S16-03-reopened.png). The 'already-received vs newly-added' modal summary was not separately driven.</t>
+          <t>Auto-pick was ON in the VIU baseline, so the pick step was not exercised. Needs live verification with auto-pick OFF. || [FRESH VIU 2026-07-10 sv7301] PROGRESS: with autoPickInventoryParts=OFF (current org drift), adding inventory part P550848 left it status 'in_stock' (NOT auto-picked); simple-complete BE-BLOCKED 400 'All inventory and found parts must be picked before completing the work order.'; after line-level Pick (perform-request-status-action 201 -&gt; status picked) completion proceeded (201). Expected #2 (cannot complete until picked) and #3 (after pick, completes) PROVEN. Expected #1 (completion-MODAL Pick step offering 'Pick all from default bins'/'Review individually') NOT yet surfaced — pick was driven at line level, not via the completion wizard's pick step. Remains VIU-Pending on the modal pick-step UI. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. With autoPickInventoryParts=OFF and an unpicked inventory part (P550848, status in_stock), the completion wizard shows a PICK STEP (data-test-id section_wizard_pick): '1 part needs picking' + Pick All (button_pick_all) + text_unpicked_parts_count + button_pick_continue; completion is gated (BE also 400 'All inventory and found parts must be picked...'); after Pick All -&gt; 'All parts picked' -&gt; Complete Work Order proceeds. Expected #2 (cannot complete until picked) + #3 (proceeds after picking) fully proven; the pick step exists with 'Pick All' (the alternate 'Review individually' path was not separately exercised in this 1-part case).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>C29299</t>
+          <t>C29298</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29299</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29298</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-10</t>
+          <t>SF-COMP-09</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
+          <t>Verify adding a new line to a completed work order returns it to Approved</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -2049,39 +2049,39 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Existing behaviors preserved by design; not re-driven in the VIU run. Needs live verification.</t>
+          <t>Return-to-Approved verified 2026-07-06 (S16-03-reopened.png). The 'already-received vs newly-added' modal summary was not separately driven.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>C29300</t>
+          <t>C29299</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29300</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29299</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-11</t>
+          <t>SF-COMP-10</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — No-PO / Skip (Story 2)</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice completion wizard offers Receive Parts, Complete Without Receiving and Cancel</t>
+          <t>Verify individual-line Complete and per-part receive actions still work alongside Simple completion</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" s="14" t="inlineStr">
@@ -2096,24 +2096,24 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=false; wizard = 'Receive → Success', '2 parts waiting to receive', with Cancel / Complete Without Receiving / Receive Parts (S3-01-wizard-optional.png).</t>
+          <t>Existing behaviors preserved by design; not re-driven in the VIU run. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>C29301</t>
+          <t>C29300</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29301</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29300</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-12</t>
+          <t>SF-COMP-11</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -2123,12 +2123,12 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal creates POs in the background and shows the count of parts to receive</t>
+          <t>Verify the optional-invoice completion wizard offers Receive Parts, Complete Without Receiving and Cancel</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G23" s="14" t="inlineStr">
@@ -2143,24 +2143,24 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Parts-to-receive count verified 2026-07-06 ('2 parts waiting to receive', S3-01-wizard-optional.png). Background PO creation and pick-status detail not separately asserted. || [V2.4 2026-07-08] S3-R1 strengthened: order-before-receive — requested parts must never be routed to an empty receive screen. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Optional-invoice completion wizard (requireVendorInvoiceNumber OFF) receive step shows '2 parts waiting to receive' plus '1 part is not ordered yet - Going to receive parts or completing the work order will order those parts' (background PO creation); API confirmed an order_id assigned + waiting_to_receive. Both 'Receive Parts' and 'Complete Without Receiving' present.</t>
+          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=false; wizard = 'Receive → Success', '2 parts waiting to receive', with Cancel / Complete Without Receiving / Receive Parts (S3-01-wizard-optional.png).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29302</t>
+          <t>C29301</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29302</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29301</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-13</t>
+          <t>SF-COMP-12</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
+          <t>Verify the optional-invoice modal creates POs in the background and shows the count of parts to receive</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -2190,24 +2190,24 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded). || [FRESH VIU 2026-07-10 sv7301] VERIFIED (OBS-5 consolidation; supersedes BATCH-6 BUG-11 block). With requireVendorInvoiceNumber=OFF, the optional-invoice completion wizard shows 'N parts waiting to receive' + 'Clicking Receive Parts will take you to the purchase order page' + a background-order note; clicking Receive Parts navigated to the consolidated shared receive page /bulk-receive?workOrderId=...&amp;returnTo=WorkOrder ('Receive Vendor Parts', receive all vendors at once) — the shipped shared receive surface (replaces the legacy Accept Delivery named in the case, per OBS-5). Setting restored.</t>
+          <t>Parts-to-receive count verified 2026-07-06 ('2 parts waiting to receive', S3-01-wizard-optional.png). Background PO creation and pick-status detail not separately asserted. || [V2.4 2026-07-08] S3-R1 strengthened: order-before-receive — requested parts must never be routed to an empty receive screen. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Optional-invoice completion wizard (requireVendorInvoiceNumber OFF) receive step shows '2 parts waiting to receive' plus '1 part is not ordered yet - Going to receive parts or completing the work order will order those parts' (background PO creation); API confirmed an order_id assigned + waiting_to_receive. Both 'Receive Parts' and 'Complete Without Receiving' present.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29303</t>
+          <t>C29302</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29303</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29302</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-14</t>
+          <t>SF-COMP-13</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
+          <t>Verify Receive Parts opens the shared Accept Delivery page to receive all vendors at once</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -2237,24 +2237,24 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14). | VIU-Verified 2026-07-08: optional-invoice (requireVendorInvoiceNumber=false) completion via simple-complete returned 201 and WO-&gt;Complete while both parts stayed status=waiting_to_receive (quantity_remaining preserved); UI Receive step shows the "Complete Without Receiving" button (VIU2-03-receive-step.png). Line-Receive-button sub-claim not separately asserted.</t>
+          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded). || [FRESH VIU 2026-07-10 sv7301] VERIFIED (OBS-5 consolidation; supersedes BATCH-6 BUG-11 block). With requireVendorInvoiceNumber=OFF, the optional-invoice completion wizard shows 'N parts waiting to receive' + 'Clicking Receive Parts will take you to the purchase order page' + a background-order note; clicking Receive Parts navigated to the consolidated shared receive page /bulk-receive?workOrderId=...&amp;returnTo=WorkOrder ('Receive Vendor Parts', receive all vendors at once) — the shipped shared receive surface (replaces the legacy Accept Delivery named in the case, per OBS-5). Setting restored.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29304</t>
+          <t>C29303</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29304</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29303</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-15</t>
+          <t>SF-COMP-14</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
+          <t>Verify Complete Without Receiving completes the WO, keeps unreceived parts waiting, and keeps the line Receive button</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G26" s="14" t="inlineStr">
@@ -2284,24 +2284,24 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Idempotency not driven in VIU. Needs live verification.</t>
+          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14). | VIU-Verified 2026-07-08: optional-invoice (requireVendorInvoiceNumber=false) completion via simple-complete returned 201 and WO-&gt;Complete while both parts stayed status=waiting_to_receive (quantity_remaining preserved); UI Receive step shows the "Complete Without Receiving" button (VIU2-03-receive-step.png). Line-Receive-button sub-claim not separately asserted.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29305</t>
+          <t>C29304</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29304</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-16</t>
+          <t>SF-COMP-15</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify Cancel closes the completion modal with no change and no duplicate POs on re-open</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -2331,24 +2331,24 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
+          <t>Idempotency not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29306</t>
+          <t>C29305</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-17</t>
+          <t>SF-COMP-16</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
+          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -2378,39 +2378,39 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
+          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29307</t>
+          <t>C29306</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-18</t>
+          <t>SF-COMP-17</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
+          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -2425,24 +2425,24 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
+          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29308</t>
+          <t>C29307</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-COMP-18</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2472,24 +2472,24 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
+          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29309</t>
+          <t>C29308</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
@@ -2519,39 +2519,39 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29310</t>
+          <t>C29309</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-21</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29311</t>
+          <t>C29310</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-22</t>
+          <t>SF-COMP-21</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
+          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -2613,34 +2613,34 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
+          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29312</t>
+          <t>C29311</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-COMP-22</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Completion — Line approval gate</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -2660,39 +2660,39 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29313</t>
+          <t>C29312</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -2707,39 +2707,39 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29322</t>
+          <t>C29313</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
+          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -2754,39 +2754,39 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
+          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29323</t>
+          <t>C29322</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-01</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
+          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -2801,24 +2801,24 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
+          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29324</t>
+          <t>C29323</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-02</t>
+          <t>SF-TECH-01</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
+          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -2848,24 +2848,24 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
+          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>C29325</t>
+          <t>C29324</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-03</t>
+          <t>SF-TECH-02</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
+          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -2895,24 +2895,24 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
+          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>C29326</t>
+          <t>C29325</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-04</t>
+          <t>SF-TECH-03</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -2922,12 +2922,12 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
+          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -2942,24 +2942,24 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
+          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>C29327</t>
+          <t>C29326</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-TECH-04</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2969,12 +2969,12 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -2989,24 +2989,24 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
+          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>C29328</t>
+          <t>C29327</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-TECH-05</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -3036,24 +3036,24 @@
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
+          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>C29329</t>
+          <t>C29328</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-TECH-06</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -3083,24 +3083,24 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
+          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>C29330</t>
+          <t>C29329</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-08</t>
+          <t>SF-TECH-07</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
+          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3125,44 +3125,44 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
+          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>C29331</t>
+          <t>C29330</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-TECH-08</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
+          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -3172,29 +3172,29 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>C29332</t>
+          <t>C29331</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-VPART-01</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -3224,24 +3224,24 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>C29333</t>
+          <t>C29332</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-VPART-02</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -3271,24 +3271,24 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>C29334</t>
+          <t>C29333</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VPART-03</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -3318,24 +3318,24 @@
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>C29335</t>
+          <t>C29334</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -3365,24 +3365,24 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>C29336</t>
+          <t>C29335</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VPART-05</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -3412,24 +3412,24 @@
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>C29337</t>
+          <t>C29336</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -3459,34 +3459,34 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>C29338</t>
+          <t>C29337</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-01</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>C29339</t>
+          <t>C29338</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-02</t>
+          <t>SF-VMIS-01</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
+          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -3553,24 +3553,24 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
+          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>C29341</t>
+          <t>C29339</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-02</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -3600,24 +3600,24 @@
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
+          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>C29342</t>
+          <t>C29341</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -3647,24 +3647,24 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>C29439</t>
+          <t>C29342</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-07</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -3674,7 +3674,7 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -3694,34 +3694,34 @@
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>C29344</t>
+          <t>C29439</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-VMIS-07</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -3741,24 +3741,24 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
+          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>C29345</t>
+          <t>C29344</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -3788,24 +3788,24 @@
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
+          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>C29346</t>
+          <t>C29345</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3815,7 +3815,7 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -3835,24 +3835,24 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
+          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>C29347</t>
+          <t>C29346</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -3862,12 +3862,12 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -3882,24 +3882,24 @@
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
+          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>C29348</t>
+          <t>C29347</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -3929,24 +3929,24 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>C29349</t>
+          <t>C29348</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -3976,39 +3976,39 @@
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
+          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>C29350</t>
+          <t>C29349</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -4023,24 +4023,24 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>C29351</t>
+          <t>C29350</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -4070,24 +4070,24 @@
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
+          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>C29352</t>
+          <t>C29351</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -4117,24 +4117,24 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>C29353</t>
+          <t>C29352</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -4164,24 +4164,24 @@
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>C29354</t>
+          <t>C29353</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -4211,24 +4211,24 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>C29355</t>
+          <t>C29354</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -4258,24 +4258,24 @@
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>C29356</t>
+          <t>C29355</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -4285,7 +4285,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -4305,24 +4305,24 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
+          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>C29357</t>
+          <t>C29356</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -4352,24 +4352,24 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
+          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>C29358</t>
+          <t>C29357</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -4379,7 +4379,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -4399,34 +4399,34 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>C29360</t>
+          <t>C29358</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -4446,24 +4446,24 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
+          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>C29361</t>
+          <t>C29360</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -4493,24 +4493,24 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
+          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>C29362</t>
+          <t>C29361</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -4540,39 +4540,39 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>C29363</t>
+          <t>C29362</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -4587,34 +4587,34 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED on the built Bulk Receive page (Story 8/10 inline PN-fix UI is shipped; the BATCH-6 'appears tied to Story 8, NOT built' note is SUPERSEDED). A no-number part shows 'Missing part number' (text visible); the inline input_part_number_{partId} Edit -&gt; enter PN -&gt; the 'Missing part number' text clears AND the PN persists immediately to the backend (order item.part_number=ZZPN-FIX01, PartRequest pn set) without a page reload.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>C29369</t>
+          <t>C29363</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -4634,24 +4634,24 @@
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED on the built Bulk Receive page (Story 8/10 inline PN-fix UI is shipped; the BATCH-6 'appears tied to Story 8, NOT built' note is SUPERSEDED). A no-number part shows 'Missing part number' (text visible); the inline input_part_number_{partId} Edit -&gt; enter PN -&gt; the 'Missing part number' text clears AND the PN persists immediately to the backend (order item.part_number=ZZPN-FIX01, PartRequest pn set) without a page reload.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>C29370</t>
+          <t>C29369</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -4681,24 +4681,24 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
+          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>C29371</t>
+          <t>C29370</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-03</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -4708,12 +4708,12 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -4728,34 +4728,34 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>C29372</t>
+          <t>C29371</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-04</t>
+          <t>SF-RCV-03</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
+          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -4775,24 +4775,24 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>C29374</t>
+          <t>C29372</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-RCV-04</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -4822,24 +4822,24 @@
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
+          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>C29377</t>
+          <t>C29374</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -4849,12 +4849,12 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -4869,24 +4869,24 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>C29440</t>
+          <t>C29377</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-10</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
@@ -4916,39 +4916,39 @@
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
+          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>C29378</t>
+          <t>C29440</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
@@ -4963,24 +4963,24 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
+          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>C29381</t>
+          <t>C29378</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
@@ -4990,12 +4990,12 @@
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -5010,39 +5010,39 @@
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), and the PO left the Vendor-Missing group into the vendor's group (Receive enabled once PN+invoice supplied).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>C29383</t>
+          <t>C29381</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -5057,24 +5057,24 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), and the PO left the Vendor-Missing group into the vendor's group (Receive enabled once PN+invoice supplied).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>C29384</t>
+          <t>C29383</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -5104,24 +5104,24 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
+          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>C29385</t>
+          <t>C29384</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -5151,39 +5151,39 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
+          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>C29386</t>
+          <t>C29385</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-01</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Verify the Require Review setting drives the review flow when turned on</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -5198,24 +5198,24 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>C29387</t>
+          <t>C29386</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-02</t>
+          <t>SF-REV-01</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -5245,24 +5245,24 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
+          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>C29388</t>
+          <t>C29387</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-02</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5272,12 +5272,12 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -5292,24 +5292,24 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
+          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>C29389</t>
+          <t>C29388</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5319,7 +5319,7 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -5339,24 +5339,24 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (supersedes BATCH-6 BUG-11 block). With requireReview=ON, the completion CTA = 'Send To Review' (wizard 'Complete &amp; Send to Review'); the receive step contains NO inline receive fields (0 qty/invoice inputs inside the dialog) and 'Receive Parts' routes to the shared receive page /bulk-receive (returnTo=WorkOrder), not an inline modal. Setting restored.</t>
+          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>C29390</t>
+          <t>C29389</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-05</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -5386,24 +5386,24 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (supersedes BATCH-6 BUG-11 block). With requireReview=ON, the completion CTA = 'Send To Review' (wizard 'Complete &amp; Send to Review'); the receive step contains NO inline receive fields (0 qty/invoice inputs inside the dialog) and 'Receive Parts' routes to the shared receive page /bulk-receive (returnTo=WorkOrder), not an inline modal. Setting restored.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>C29391</t>
+          <t>C29390</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-06</t>
+          <t>SF-REV-05</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -5433,24 +5433,24 @@
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
+          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>C29392</t>
+          <t>C29391</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-06</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -5480,24 +5480,24 @@
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Not separately asserted in VIU. Needs live verification.</t>
+          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>C29393</t>
+          <t>C29392</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-08</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
@@ -5522,29 +5522,29 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
+          <t>Not separately asserted in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>C29394</t>
+          <t>C29393</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-09</t>
+          <t>SF-REV-08</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
+          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
@@ -5569,29 +5569,29 @@
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
         </is>
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
+          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>C29395</t>
+          <t>C29394</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-10</t>
+          <t>SF-REV-09</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -5616,29 +5616,29 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
+          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>C29397</t>
+          <t>C29395</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-REV-10</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -5648,7 +5648,7 @@
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
@@ -5663,29 +5663,29 @@
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
         </is>
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
+          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>C29398</t>
+          <t>C29397</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -5695,7 +5695,7 @@
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -5715,34 +5715,34 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
+          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>C29401</t>
+          <t>C29398</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-01</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Verify the work order primary button reads 'Create Work Order'</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -5762,24 +5762,24 @@
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
+          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>C29402</t>
+          <t>C29401</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-02</t>
+          <t>SF-UX-01</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+          <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
@@ -5809,24 +5809,24 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
+          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>C29403</t>
+          <t>C29402</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-03</t>
+          <t>SF-UX-02</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
+          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -5856,39 +5856,39 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
+          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>C29405</t>
+          <t>C29403</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-01</t>
+          <t>SF-UX-03</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
+          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G103" s="14" t="inlineStr">
@@ -5903,24 +5903,24 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
+          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>C29406</t>
+          <t>C29405</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-02</t>
+          <t>SF-PERM-01</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
+          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -5950,24 +5950,24 @@
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
+          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>C29407</t>
+          <t>C29406</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -5977,7 +5977,7 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -5997,24 +5997,24 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
+          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>C29408</t>
+          <t>C29407</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
@@ -6039,29 +6039,29 @@
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
+          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>C29409</t>
+          <t>C29408</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -6086,29 +6086,29 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>C29410</t>
+          <t>C29409</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-PERM-05</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
@@ -6138,24 +6138,24 @@
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>C29411</t>
+          <t>C29410</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-07</t>
+          <t>SF-PERM-06</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -6180,29 +6180,29 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
+          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>C29412</t>
+          <t>C29411</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-08</t>
+          <t>SF-PERM-07</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
@@ -6227,29 +6227,29 @@
       </c>
       <c r="H110" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
+          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
         </is>
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
+          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>C29413</t>
+          <t>C29412</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-PERM-08</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -6274,29 +6274,29 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
+          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>C29414</t>
+          <t>C29413</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
@@ -6306,7 +6306,7 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
@@ -6326,34 +6326,34 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
+          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>C29415</t>
+          <t>C29414</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
@@ -6373,24 +6373,24 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
+          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>C29417</t>
+          <t>C29415</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G114" s="14" t="inlineStr">
@@ -6420,24 +6420,24 @@
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
+          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
         <is>
-          <t>C29418</t>
+          <t>C29417</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-04</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
@@ -6467,24 +6467,24 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>C29419</t>
+          <t>C29418</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-04</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
@@ -6514,24 +6514,24 @@
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
+          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
-          <t>C29420</t>
+          <t>C29419</t>
         </is>
       </c>
       <c r="B117" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-06</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E117" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
@@ -6561,24 +6561,24 @@
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present. Cannot receive without BOTH a vendor and a part number.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="12" t="inlineStr">
         <is>
-          <t>C29421</t>
+          <t>C29420</t>
         </is>
       </c>
       <c r="B118" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
         </is>
       </c>
       <c r="C118" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E118" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G118" s="14" t="inlineStr">
@@ -6608,24 +6608,24 @@
       </c>
       <c r="I118" s="12" t="inlineStr">
         <is>
-          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present. Cannot receive without BOTH a vendor and a part number.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="12" t="inlineStr">
         <is>
-          <t>C29422</t>
+          <t>C29421</t>
         </is>
       </c>
       <c r="B119" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="E119" s="12" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
@@ -6655,24 +6655,24 @@
       </c>
       <c r="I119" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
+          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="12" t="inlineStr">
         <is>
-          <t>C29424</t>
+          <t>C29422</t>
         </is>
       </c>
       <c r="B120" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
         </is>
       </c>
       <c r="C120" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-10</t>
+          <t>SF-VAL-08</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="E120" s="12" t="inlineStr">
         <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G120" s="14" t="inlineStr">
@@ -6702,52 +6702,99 @@
       </c>
       <c r="I120" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
+          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="12" t="inlineStr">
         <is>
+          <t>C29424</t>
+        </is>
+      </c>
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-10</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
+        </is>
+      </c>
+      <c r="F121" s="12" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G121" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H121" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
           <t>C29425</t>
         </is>
       </c>
-      <c r="B121" s="13" t="inlineStr">
+      <c r="B122" s="13" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
         </is>
       </c>
-      <c r="C121" s="12" t="inlineStr">
+      <c r="C122" s="12" t="inlineStr">
         <is>
           <t>SF-VAL-11</t>
         </is>
       </c>
-      <c r="D121" s="12" t="inlineStr">
+      <c r="D122" s="12" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="E121" s="12" t="inlineStr">
+      <c r="E122" s="12" t="inlineStr">
         <is>
           <t>Verify the approve-line error text appears when completing with an unapproved line</t>
         </is>
       </c>
-      <c r="F121" s="12" t="inlineStr">
+      <c r="F122" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G121" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="inlineStr">
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H122" s="12" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="I121" s="12" t="inlineStr">
+      <c r="I122" s="12" t="inlineStr">
         <is>
           <t>PARTIAL in VIU — error not cleanly isolated (S17-02-approval-error.png). Needs a WO whose only blocker is the unapproved line. | VIU-Verified 2026-07-08: simple-complete with an unapproved (authorization_required) line returns 400 with text "All lines must be approved before completing the work order." (WO a71ec2f0).</t>
         </is>
@@ -6875,6 +6922,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId119"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6886,7 +6934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7044,32 +7092,32 @@
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>C29297</t>
+          <t>C29314</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29297</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-08</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Verify with Auto-pick Inventory OFF the completion modal requires picking parts before Complete</t>
+          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr">
@@ -7079,29 +7127,29 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>Auto-pick was ON in the VIU baseline, so the pick step was not exercised. Needs live verification with auto-pick OFF. || [FRESH VIU 2026-07-10 sv7301] PROGRESS: with autoPickInventoryParts=OFF (current org drift), adding inventory part P550848 left it status 'in_stock' (NOT auto-picked); simple-complete BE-BLOCKED 400 'All inventory and found parts must be picked before completing the work order.'; after line-level Pick (perform-request-status-action 201 -&gt; status picked) completion proceeded (201). Expected #2 (cannot complete until picked) and #3 (after pick, completes) PROVEN. Expected #1 (completion-MODAL Pick step offering 'Pick all from default bins'/'Review individually') NOT yet surfaced — pick was driven at line level, not via the completion wizard's pick step. Remains VIU-Pending on the modal pick-step UI.</t>
+          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>C29314</t>
+          <t>C29315</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -7111,12 +7159,12 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -7131,34 +7179,34 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>C29315</t>
+          <t>C29316</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -7185,17 +7233,17 @@
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>C29316</t>
+          <t>C29317</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -7205,12 +7253,12 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -7232,17 +7280,17 @@
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>C29317</t>
+          <t>C29318</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -7252,12 +7300,12 @@
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
@@ -7279,32 +7327,32 @@
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>C29318</t>
+          <t>C29319</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -7326,32 +7374,32 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>C29319</t>
+          <t>C29320</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -7366,24 +7414,24 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>C29320</t>
+          <t>C29321</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -7393,7 +7441,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -7413,39 +7461,39 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>C29321</t>
+          <t>C29340</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-VMIS-03</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -7455,29 +7503,29 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>C29340</t>
+          <t>C29343</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -7487,12 +7535,12 @@
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -7507,39 +7555,39 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>C29343</t>
+          <t>C29359</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -7549,44 +7597,44 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>NOT BUILT. Needs dev complete. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a GENUINE special-order (vendor-source) cored part received on the Bulk Receive page to expose the Ok/Not-OK resolution. Confirmed again this pass: the only seedable core (catalog P550848) forces Source=Inventory (auto-picked, never routed through a receivable PO), and the manual part sub-form's Core Charge yields is_core=false. A vendor-source is_core part is not seedable in-app.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>C29359</t>
+          <t>C29364</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G15" s="15" t="inlineStr">
@@ -7596,29 +7644,29 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
         </is>
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a GENUINE special-order (vendor-source) cored part received on the Bulk Receive page to expose the Ok/Not-OK resolution. Confirmed again this pass: the only seedable core (catalog P550848) forces Source=Inventory (auto-picked, never routed through a receivable PO), and the manual part sub-form's Core Charge yields is_core=false. A vendor-source is_core part is not seedable in-app.</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED. Received a WO-PO vendor part carrying a NEW free-text part number (ZZPN-FIX01) via /bulk-receive (POST /api/orders/receive-requested-parts 200). NO new inventory part was created (GET /api/inventory/parts?search=ZZPN-FIX01 = 0 before AND after) — consistent with vendor-source parts being direct-to-WO consumption, not inventory-tracked (cf. SF-VPART-05); /api/catalogue/parts search 404. Whether a new PN should create a catalog/inventory item + Part History on receive needs the inventory-integrity/Part-History surface, which is BLOCKED-ENV (OBS-6). Applies equally to SF-PNFIX-03/06.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>C29364</t>
+          <t>C29365</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -7628,7 +7676,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -7648,24 +7696,24 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED. Received a WO-PO vendor part carrying a NEW free-text part number (ZZPN-FIX01) via /bulk-receive (POST /api/orders/receive-requested-parts 200). NO new inventory part was created (GET /api/inventory/parts?search=ZZPN-FIX01 = 0 before AND after) — consistent with vendor-source parts being direct-to-WO consumption, not inventory-tracked (cf. SF-VPART-05); /api/catalogue/parts search 404. Whether a new PN should create a catalog/inventory item + Part History on receive needs the inventory-integrity/Part-History surface, which is BLOCKED-ENV (OBS-6). Applies equally to SF-PNFIX-03/06.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>C29365</t>
+          <t>C29366</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -7675,12 +7723,12 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -7695,24 +7743,24 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>C29366</t>
+          <t>C29367</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -7722,12 +7770,12 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -7742,24 +7790,24 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>C29367</t>
+          <t>C29368</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -7769,12 +7817,12 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -7789,39 +7837,39 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>C29368</t>
+          <t>C29373</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -7831,29 +7879,29 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
+          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>C29373</t>
+          <t>C29375</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -7863,12 +7911,12 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -7878,29 +7926,29 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
+          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>C29375</t>
+          <t>C29376</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -7910,12 +7958,12 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -7925,39 +7973,39 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>C29376</t>
+          <t>C29379</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -7972,29 +8020,29 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29379</t>
+          <t>C29380</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -8004,12 +8052,12 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -8024,24 +8072,24 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
+          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29380</t>
+          <t>C29382</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -8051,7 +8099,7 @@
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -8071,39 +8119,39 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
+          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29382</t>
+          <t>C29396</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -8113,29 +8161,29 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
+          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29396</t>
+          <t>C29399</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -8145,12 +8193,12 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -8160,39 +8208,39 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29399</t>
+          <t>C29404</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-UX-04</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -8207,39 +8255,39 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29404</t>
+          <t>C29416</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-04</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -8254,29 +8302,29 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
+          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.) || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED (needs-data: VIN-less asset). Confirmed not seedable in-harness: all 50 sampled vehicles (GET /api/vehicles) carry a VIN; POST /api/vehicles -&gt; 405 (GET-only, no API create route found). The non-review completion wizard only prompts for VIN when the asset lacks one, so this gate needs a VIN-less asset seeded (or an existing vehicle's VIN cleared, which would modify shared data).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29416</t>
+          <t>C29423</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -8286,7 +8334,7 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -8306,39 +8354,39 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29423</t>
+          <t>C29426</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-QB-01</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
@@ -8348,29 +8396,29 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
+          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29426</t>
+          <t>C29428</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-01</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -8380,7 +8428,7 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -8400,24 +8448,24 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29428</t>
+          <t>C29429</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -8427,12 +8475,12 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
@@ -8447,24 +8495,24 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29429</t>
+          <t>C29430</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-04</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -8474,7 +8522,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -8501,17 +8549,17 @@
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29430</t>
+          <t>C29431</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -8521,7 +8569,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -8541,24 +8589,24 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29431</t>
+          <t>C29432</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-06</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
@@ -8568,7 +8616,7 @@
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -8588,24 +8636,24 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29432</t>
+          <t>C29433</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-07</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -8615,7 +8663,7 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -8634,53 +8682,6 @@
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="12" t="inlineStr">
-        <is>
-          <t>C29433</t>
-        </is>
-      </c>
-      <c r="B38" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="D38" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G38" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
@@ -8724,7 +8725,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.)</t>
+          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.) || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED (needs-data: VIN-less asset). Confirmed not seedable in-harness: all 50 sampled vehicles (GET /api/vehicles) carry a VIN; POST /api/vehicles -&gt; 405 (GET-only, no API create route found). The non-review completion wizard only prompts for VIN when the asset lacks one, so this gate needs a VIN-less asset seeded (or an existing vehicle's VIN cleared, which would modify shared data).</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review role-gating: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Role-gating of Mark-Reviewed: FE-vs-API part resolved by the 2026-07-10 ruling, but the expected also requires reviewer != completer, which is missing at the UI (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H110" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · Review sign-off permission FE-only at BE was resolved by the 2026-07-10 ruling (UI pass / API fail, T2), BUT this case's expected also requires reviewer != completer, which fails at the UI too (BUG-5). Held on BUG-5 (TICKET 1).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
+          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
+          <t>[OBSOLETE — descoped v1] The completer reviewing their own WO is EXPECTED in v1 (was: user who completed cannot Mark Reviewed)</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING · reviewer != completer rule NOT implemented (a user can sign off their own WO via the UI). NOT covered by the 2026-07-10 FE-vs-API ruling (the UI does not block it) — held on BUG-5 (TICKET 1): enforce or descope?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
+          <t>NET-NEW hard rule from SV-8183 (stamp sentToReviewBy/completedBy and block Mark Reviewed for that user). | VIU 2026-07-07 (Tech-unblock pass): the SAME admin who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). Previously logged as a FAIL/BUG (the one net-new Simple-Flow rule missing). || [RECLASSIFIED 2026-07-10 — OBSOLETE] Milos ruling relayed by QA lead 2026-07-10: reviewer != completer is NOT a v1 requirement; a completer reviewing their own WO is EXPECTED. The previously-observed self-review is therefore CORRECT behavior, not a defect — the sole assertion of this case is void. This case is the dedicated same-user case, so nothing meaningful remains; marked OBSOLETE / covered-by SF-PERM-04 + SF-PERM-07 (which retain the Review Work Orders permission-gating). Left in the file (not deleted) and viu_status set VIU-Verified so it exits the BUG/RULING bucket; FLAGGED FOR QA LEAD to retire in TestRail. Origin defect BUG-5 / TICKET 1 dropped as expected-behavior.</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman) plus reviewer != completer. Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced.</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all) PLUS the NET-NEW reviewer != completer hard rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state).</t>
+          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1) plus the reviewer != completer NET-NEW rule. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS.</t>
+          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Verify the user who completed or sent the work order to review cannot Mark Reviewed it</t>
+          <t>[OBSOLETE — descoped v1] The completer reviewing their own WO is EXPECTED in v1 (was: user who completed cannot Mark Reviewed)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183: stamp sentToReviewBy/completedBy and block Mark Reviewed for that user. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL (BUG). reviewer!=completer NOT implemented: the SAME admin user who Sent to Review successfully Marked it Reviewed, moving Review-&gt;Complete with no block (REV-admin-completer-markreviewed.png). No two-user restriction. This is the one NET-NEW Simple-Flow rule and it is missing.</t>
+          <t>NET-NEW hard rule from SV-8183 (stamp sentToReviewBy/completedBy and block Mark Reviewed for that user). | VIU 2026-07-07 (Tech-unblock pass): the SAME admin who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). Previously logged as a FAIL/BUG (the one net-new Simple-Flow rule missing). || [RECLASSIFIED 2026-07-10 — OBSOLETE] Milos ruling relayed by QA lead 2026-07-10: reviewer != completer is NOT a v1 requirement; a completer reviewing their own WO is EXPECTED. The previously-observed self-review is therefore CORRECT behavior, not a defect — the sole assertion of this case is void. This case is the dedicated same-user case, so nothing meaningful remains; marked OBSOLETE / covered-by SF-PERM-04 + SF-PERM-07 (which retain the Review Work Orders permission-gating). Left in the file (not deleted) and viu_status set VIU-Verified so it exits the BUG/RULING bucket; FLAGGED FOR QA LEAD to retire in TestRail. Origin defect BUG-5 / TICKET 1 dropped as expected-behavior.</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -5621,7 +5621,7 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -6091,7 +6091,7 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>[OBSOLETE — descoped v1] The completer reviewing their own WO is EXPECTED in v1 (was: user who completed cannot Mark Reviewed)</t>
+          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183 (stamp sentToReviewBy/completedBy and block Mark Reviewed for that user). | VIU 2026-07-07 (Tech-unblock pass): the SAME admin who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). Previously logged as a FAIL/BUG (the one net-new Simple-Flow rule missing). || [RECLASSIFIED 2026-07-10 — OBSOLETE] Milos ruling relayed by QA lead 2026-07-10: reviewer != completer is NOT a v1 requirement; a completer reviewing their own WO is EXPECTED. The previously-observed self-review is therefore CORRECT behavior, not a defect — the sole assertion of this case is void. This case is the dedicated same-user case, so nothing meaningful remains; marked OBSOLETE / covered-by SF-PERM-04 + SF-PERM-07 (which retain the Review Work Orders permission-gating). Left in the file (not deleted) and viu_status set VIU-Verified so it exits the BUG/RULING bucket; FLAGGED FOR QA LEAD to retire in TestRail. Origin defect BUG-5 / TICKET 1 dropped as expected-behavior.</t>
+          <t>[RE-PURPOSED 2026-07-10] Milos ruling (relayed by QA lead): self-review IS acceptable — a user MAY Mark Reviewed a work order they completed, PROVIDED their role holds the Mark Reviewed permission (permission-gated only, NO identity restriction). This case flipped from the obsolete negative (was: completer cannot Mark Reviewed) into the POSITIVE case above. | VIU EVIDENCE: the self-review-by-a-permissioned-role positive WAS directly observed — the SAME admin (who holds Review Work Orders) who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). The permission-gating half (a role WITHOUT the permission cannot) was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2; FE hides the control for non-reviewers). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). =&gt; VIU-Verified: self-review allowed for permissioned role per Milos ruling 2026-07-10; permission-gating verified. Origin defect BUG-5 / TICKET 1 dropped as expected behavior.</t>
         </is>
       </c>
     </row>
@@ -10546,7 +10546,7 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -10781,7 +10781,7 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -10875,7 +10875,7 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10902,7 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>[OBSOLETE — descoped v1] The completer reviewing their own WO is EXPECTED in v1 (was: user who completed cannot Mark Reviewed)</t>
+          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>NET-NEW hard rule from SV-8183 (stamp sentToReviewBy/completedBy and block Mark Reviewed for that user). | VIU 2026-07-07 (Tech-unblock pass): the SAME admin who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). Previously logged as a FAIL/BUG (the one net-new Simple-Flow rule missing). || [RECLASSIFIED 2026-07-10 — OBSOLETE] Milos ruling relayed by QA lead 2026-07-10: reviewer != completer is NOT a v1 requirement; a completer reviewing their own WO is EXPECTED. The previously-observed self-review is therefore CORRECT behavior, not a defect — the sole assertion of this case is void. This case is the dedicated same-user case, so nothing meaningful remains; marked OBSOLETE / covered-by SF-PERM-04 + SF-PERM-07 (which retain the Review Work Orders permission-gating). Left in the file (not deleted) and viu_status set VIU-Verified so it exits the BUG/RULING bucket; FLAGGED FOR QA LEAD to retire in TestRail. Origin defect BUG-5 / TICKET 1 dropped as expected-behavior.</t>
+          <t>[RE-PURPOSED 2026-07-10] Milos ruling (relayed by QA lead): self-review IS acceptable — a user MAY Mark Reviewed a work order they completed, PROVIDED their role holds the Mark Reviewed permission (permission-gated only, NO identity restriction). This case flipped from the obsolete negative (was: completer cannot Mark Reviewed) into the POSITIVE case above. | VIU EVIDENCE: the self-review-by-a-permissioned-role positive WAS directly observed — the SAME admin (who holds Review Work Orders) who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). The permission-gating half (a role WITHOUT the permission cannot) was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2; FE hides the control for non-reviewers). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). =&gt; VIU-Verified: self-review allowed for permissioned role per Milos ruling 2026-07-10; permission-gating verified. Origin defect BUG-5 / TICKET 1 dropped as expected behavior.</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -11,8 +11,9 @@
     <sheet name="VIU-Verified" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="VIU-Pending" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Open-Question" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Deviation _ Bugs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="TestRail Sync Status" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pending _ Retest" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Deviation _ Bugs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TestRail Sync Status" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -147,10 +148,10 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -543,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C42"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -581,7 +582,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C4" s="2" t="n"/>
     </row>
@@ -623,7 +624,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -638,7 +639,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -662,329 +663,331 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="C11" s="2" t="n"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Pending / Retest</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Expected behavior changed by the V2.4 deltas (2026-07-13); needs a live re-VIU (see Pending / Retest tab).</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="C12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
           <t>Cases tied to a bug / deviation</t>
         </is>
       </c>
-      <c r="B12" s="3" t="n">
+      <c r="B13" s="3" t="n">
         <v>44</v>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>Cross-cut metric (not a VIU status) — see the Deviation / Bugs tab.</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Current headline tally: VIU-Verified 112 / VIU-Pending 45 / Open-Question 5. DEV-NOT-BUILT is now 0 (Stories 7/8/9/14 confirmed built &amp; VIU-verified).</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-    </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Current headline tally (2026-07-13): VIU-Verified 114 / VIU-Pending 34 / Open-Question 5 / Pending-Retest 10 = 163. Pending-Retest = the V2.4 Δ1-Δ4 cases (expected changed 2026-07-13) awaiting a live re-VIU. DEV-NOT-BUILT is 0.</t>
+        </is>
+      </c>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>TestRail ID coverage</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="n"/>
       <c r="B15" s="2" t="n"/>
       <c r="C15" s="2" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>Cases mapped to a TestRail ID</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>161</v>
-      </c>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TestRail ID coverage</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
       <c r="C16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>Cases mapped to a TestRail ID</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>162</v>
+      </c>
+      <c r="C17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
           <t>Cases with NO TestRail ID (blank)</t>
         </is>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B18" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Blank: SF-QB-09 — add after the next TestRail sync (IDs not guessed).</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Each status tab now carries: TestRail ID (C&lt;id&gt;) + a clickable TestRail Link (https://shopview.testrail.io/index.php?/cases/view/&lt;id&gt;) alongside the internal SF ID.</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="n"/>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>Count by blocker category</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="n"/>
       <c r="B20" s="2" t="n"/>
       <c r="C20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Count by blocker category</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Blocker category</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
-        <v>118</v>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="B23" s="6" t="n">
+        <v>111</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>— (ready to upload)</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>BLOCKED — DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="B23" s="11" t="n">
+      <c r="B24" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Dev team</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
         <is>
           <t>BLOCKED — VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>31</v>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="B25" s="7" t="n">
+        <v>39</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>QA</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>BLOCKED — MILOS ANSWER</t>
         </is>
       </c>
-      <c r="B25" s="8" t="n">
+      <c r="B26" s="8" t="n">
         <v>13</v>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Milos (PO)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>BLOCKED — BUG/RULING</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n">
+      <c r="B27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
         <is>
           <t>Dev / PO ruling</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
-        <v>162</v>
-      </c>
-      <c r="C27" s="2" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="n"/>
-      <c r="B28" s="2" t="n"/>
+      <c r="B28" s="3" t="n">
+        <v>163</v>
+      </c>
       <c r="C28" s="2" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) — by sub-bucket</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) — by sub-bucket</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n"/>
+      <c r="C30" s="2" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>VIU sub-bucket</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>reachable-now</t>
         </is>
       </c>
-      <c r="B31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="B32" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
         <is>
           <t>admin+tech + normal data; just needs another VIU pass (no new inputs).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="7" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="7" t="inlineStr">
         <is>
           <t>needs-data</t>
         </is>
       </c>
-      <c r="B32" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="B33" s="7" t="n">
+        <v>33</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
         <is>
           <t>needs a data state not seedable via the app (cores / WO-PO receive / QuickBooks / invoiced-WO).</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>needs-account</t>
         </is>
       </c>
-      <c r="B33" s="11" t="n">
+      <c r="B34" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>needs a role account we don't have (Office / Service Manager / Foreman ...).</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>TOTAL VIU PENDING (QA)</t>
         </is>
       </c>
-      <c r="B34" s="3" t="n">
-        <v>31</v>
-      </c>
-      <c r="C34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n"/>
-      <c r="B35" s="2" t="n"/>
+      <c r="B35" s="3" t="n">
+        <v>39</v>
+      </c>
       <c r="C35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Legend</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="n"/>
       <c r="B36" s="2" t="n"/>
       <c r="C36" s="2" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>VIU-Verified / READY</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Confirmed live in the UI; ready to upload to a run.</t>
-        </is>
-      </c>
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Legend</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n"/>
       <c r="C37" s="2" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VIU-Pending</t>
+          <t>VIU-Verified / READY</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Not yet verified — see the sub-bucket + what's-needed on the VIU-Pending tab.</t>
+          <t>Confirmed live in the UI; ready to upload to a run.</t>
         </is>
       </c>
       <c r="C38" s="2" t="n"/>
@@ -992,12 +995,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Open-Question</t>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Verdict awaits a Product Owner (Milos) decision — see the Open-Question tab.</t>
+          <t>Not yet verified — see the sub-bucket + what's-needed on the VIU-Pending tab.</t>
         </is>
       </c>
       <c r="C39" s="2" t="n"/>
@@ -1005,12 +1008,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>BLOCKED — BUG/RULING</t>
+          <t>Open-Question</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>VIU-observed but the pass/fail verdict hangs on a dev/PO ruling (see Deviation / Bugs).</t>
+          <t>Verdict awaits a Product Owner (Milos) decision — see the Open-Question tab.</t>
         </is>
       </c>
       <c r="C40" s="2" t="n"/>
@@ -1018,12 +1021,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>Deviation / Bug</t>
+          <t>BLOCKED — BUG/RULING</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>A case whose live behavior differs from spec; tracked via a BUG-# in bugs-log.md.</t>
+          <t>VIU-observed but the pass/fail verdict hangs on a dev/PO ruling (see Deviation / Bugs).</t>
         </is>
       </c>
       <c r="C41" s="2" t="n"/>
@@ -1031,15 +1034,28 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
+          <t>Deviation / Bug</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>A case whose live behavior differs from spec; tracked via a BUG-# in bugs-log.md.</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
           <t>DEV NOT BUILT</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>Feature not yet built. Now 0 — Stories 7/8/9/14 are built &amp; VIU-verified.</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1052,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2338,17 +2354,17 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29305</t>
+          <t>C29306</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-16</t>
+          <t>SF-COMP-17</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -2358,7 +2374,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -2378,39 +2394,39 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
+          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29306</t>
+          <t>C29307</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-17</t>
+          <t>SF-COMP-18</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
+          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -2425,24 +2441,24 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
+          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29307</t>
+          <t>C29308</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-18</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2452,12 +2468,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2472,24 +2488,24 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
+          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29308</t>
+          <t>C29309</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -2499,12 +2515,12 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
@@ -2519,34 +2535,34 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29309</t>
+          <t>C29312</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -2573,27 +2589,27 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29310</t>
+          <t>C29313</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-21</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify completing a work order with an unapproved line shows the approve-line error and does not complete</t>
+          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -2613,39 +2629,39 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: the Needs-Approval state was seen (S17-01) but the final 'cannot complete unapproved' block was not cleanly isolated (tech-story/parts gates dominated). Needs a targeted WO whose ONLY blocker is an unapproved line (S17-02-approval-error.png context). | VIU-Verified 2026-07-08: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced). WO a71ec2f0.</t>
+          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29311</t>
+          <t>C29322</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-22</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line still blocks completion even when Auto-approve is ON</t>
+          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -2660,39 +2676,39 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. | VIU-Verified 2026-07-08: block fires from the line's own authorization_required status while org autoApproveLines=true (unchanged), i.e. holds regardless of Auto-approve. Same 400 as SF-COMP-21.</t>
+          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29312</t>
+          <t>C29323</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-TECH-01</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -2707,34 +2723,34 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29313</t>
+          <t>C29324</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-TECH-02</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
+          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -2754,39 +2770,39 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
+          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29322</t>
+          <t>C29325</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-TECH-03</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
+          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -2801,24 +2817,24 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
+          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29323</t>
+          <t>C29326</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-01</t>
+          <t>SF-TECH-04</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2828,7 +2844,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
+          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -2848,24 +2864,24 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
+          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>C29324</t>
+          <t>C29327</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-02</t>
+          <t>SF-TECH-05</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2875,12 +2891,12 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
+          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -2895,24 +2911,24 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
+          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>C29325</t>
+          <t>C29328</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-03</t>
+          <t>SF-TECH-06</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -2922,12 +2938,12 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
+          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -2942,24 +2958,24 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
+          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>C29326</t>
+          <t>C29329</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-04</t>
+          <t>SF-TECH-07</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2969,12 +2985,12 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
+          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -2989,24 +3005,24 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
+          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>C29327</t>
+          <t>C29330</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-TECH-08</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3016,7 +3032,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -3031,44 +3047,44 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>C29328</t>
+          <t>C29331</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-VPART-01</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -3083,39 +3099,39 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>C29329</t>
+          <t>C29332</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-VPART-02</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3130,34 +3146,34 @@
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
+          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>C29330</t>
+          <t>C29333</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-08</t>
+          <t>SF-VPART-03</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
+          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -3172,29 +3188,29 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>C29331</t>
+          <t>C29334</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3204,12 +3220,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -3224,24 +3240,24 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>C29332</t>
+          <t>C29335</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-VPART-05</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3251,7 +3267,7 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
+          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -3271,24 +3287,24 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
+          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>C29333</t>
+          <t>C29336</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -3298,7 +3314,7 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -3318,24 +3334,24 @@
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>C29334</t>
+          <t>C29337</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3345,12 +3361,12 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -3365,34 +3381,34 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>C29335</t>
+          <t>C29338</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-VMIS-01</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -3412,39 +3428,39 @@
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
+          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>C29336</t>
+          <t>C29339</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VMIS-02</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G51" s="14" t="inlineStr">
@@ -3459,39 +3475,39 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>C29337</t>
+          <t>C29341</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -3506,24 +3522,24 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>C29338</t>
+          <t>C29342</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-01</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3533,7 +3549,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -3553,24 +3569,24 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>C29339</t>
+          <t>C29439</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-02</t>
+          <t>SF-VMIS-07</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3580,7 +3596,7 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -3600,39 +3616,39 @@
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
+          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>C29341</t>
+          <t>C29344</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G55" s="14" t="inlineStr">
@@ -3647,34 +3663,34 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
+          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>C29342</t>
+          <t>C29345</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -3694,34 +3710,34 @@
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
+          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>C29439</t>
+          <t>C29346</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-07</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -3741,24 +3757,24 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
+          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>C29344</t>
+          <t>C29347</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -3768,12 +3784,12 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -3788,24 +3804,24 @@
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>C29345</t>
+          <t>C29348</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3815,12 +3831,12 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -3835,24 +3851,24 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
+          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>C29346</t>
+          <t>C29349</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -3862,12 +3878,12 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -3882,34 +3898,34 @@
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>C29347</t>
+          <t>C29350</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -3929,39 +3945,39 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
+          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>C29348</t>
+          <t>C29351</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -3976,39 +3992,39 @@
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>C29349</t>
+          <t>C29352</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G63" s="14" t="inlineStr">
@@ -4023,24 +4039,24 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>C29350</t>
+          <t>C29353</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4050,12 +4066,12 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -4070,24 +4086,24 @@
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>C29351</t>
+          <t>C29354</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4097,7 +4113,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -4117,24 +4133,24 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>C29352</t>
+          <t>C29355</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4144,12 +4160,12 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G66" s="14" t="inlineStr">
@@ -4164,24 +4180,24 @@
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
+          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>C29353</t>
+          <t>C29356</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -4191,7 +4207,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -4211,24 +4227,24 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
+          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>C29354</t>
+          <t>C29357</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4238,7 +4254,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -4258,24 +4274,24 @@
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>C29355</t>
+          <t>C29358</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -4285,7 +4301,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -4305,34 +4321,34 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
+          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>C29356</t>
+          <t>C29360</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -4352,34 +4368,34 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
+          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>C29357</t>
+          <t>C29361</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -4399,39 +4415,39 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>C29358</t>
+          <t>C29362</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -4446,34 +4462,34 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>C29360</t>
+          <t>C29363</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -4493,34 +4509,34 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED on the built Bulk Receive page (Story 8/10 inline PN-fix UI is shipped; the BATCH-6 'appears tied to Story 8, NOT built' note is SUPERSEDED). A no-number part shows 'Missing part number' (text visible); the inline input_part_number_{partId} Edit -&gt; enter PN -&gt; the 'Missing part number' text clears AND the PN persists immediately to the backend (order item.part_number=ZZPN-FIX01, PartRequest pn set) without a page reload.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>C29361</t>
+          <t>C29369</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -4540,39 +4556,39 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
+          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>C29362</t>
+          <t>C29370</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G75" s="14" t="inlineStr">
@@ -4587,39 +4603,39 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
+          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>C29363</t>
+          <t>C29371</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-RCV-03</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -4634,39 +4650,39 @@
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED on the built Bulk Receive page (Story 8/10 inline PN-fix UI is shipped; the BATCH-6 'appears tied to Story 8, NOT built' note is SUPERSEDED). A no-number part shows 'Missing part number' (text visible); the inline input_part_number_{partId} Edit -&gt; enter PN -&gt; the 'Missing part number' text clears AND the PN persists immediately to the backend (order item.part_number=ZZPN-FIX01, PartRequest pn set) without a page reload.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>C29369</t>
+          <t>C29372</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-RCV-04</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
@@ -4681,39 +4697,39 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
+          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>C29370</t>
+          <t>C29377</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -4728,34 +4744,34 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
+          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>C29371</t>
+          <t>C29440</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-03</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -4775,39 +4791,39 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
+          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>C29372</t>
+          <t>C29378</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-04</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -4822,34 +4838,34 @@
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
+          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>C29374</t>
+          <t>C29383</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, missing part number entered, vendor invoice # captured</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -4869,34 +4885,34 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN) need a vendor-missing item on an Accept Delivery group (this PO already had vendor+PN). reachable-now. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
+          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>C29377</t>
+          <t>C29384</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
@@ -4916,39 +4932,39 @@
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
+          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>C29440</t>
+          <t>C29385</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-10</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
@@ -4963,34 +4979,34 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
+          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>C29378</t>
+          <t>C29386</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-REV-01</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
@@ -5010,39 +5026,39 @@
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
+          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>C29381</t>
+          <t>C29387</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-REV-02</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns, clears the QB flag and enables Receive</t>
+          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -5057,39 +5073,39 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] PARTIAL: no-collision auto-assign confirmed (assigning a brand-new vendor applied with NO merge prompt and cleared vendorMissing). QB-flag-clear and full Receive-enable (also needs PN + invoice) not separately confirmed. Remains VIU-Pending for the QB/receive-enable sub-clauses.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), and the PO left the Vendor-Missing group into the vendor's group (Receive enabled once PN+invoice supplied).</t>
+          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>C29383</t>
+          <t>C29388</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -5104,34 +5120,34 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
+          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>C29384</t>
+          <t>C29389</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -5151,39 +5167,39 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (supersedes BATCH-6 BUG-11 block). With requireReview=ON, the completion CTA = 'Send To Review' (wizard 'Complete &amp; Send to Review'); the receive step contains NO inline receive fields (0 qty/invoice inputs inside the dialog) and 'Receive Parts' routes to the shared receive page /bulk-receive (returnTo=WorkOrder), not an inline modal. Setting restored.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>C29385</t>
+          <t>C29390</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-REV-05</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -5198,24 +5214,24 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
+          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>C29386</t>
+          <t>C29391</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-01</t>
+          <t>SF-REV-06</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -5225,12 +5241,12 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Verify the Require Review setting drives the review flow when turned on</t>
+          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -5245,24 +5261,24 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
+          <t>[V2.4 Δ4 APPLIED 2026-07-13] Mark-Reviewed optional note removed (R7 = VIN-only) — this case is already note-free (VIN-only, Confirm-disabled-until-VIN), so no content change was needed; V2.4 2026-07-13 confirms the removal. FLAG (do not assert): spec R10 still lists the test id input_review_note even though R7 dropped the note field — an internal spec inconsistency to confirm on the live build during re-VIU (the note field itself is treated as removed). || Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>C29387</t>
+          <t>C29392</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-02</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5272,12 +5288,12 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -5292,24 +5308,24 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
+          <t>Not separately asserted in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>C29388</t>
+          <t>C29393</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-08</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5319,12 +5335,12 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -5334,29 +5350,29 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
+          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>C29389</t>
+          <t>C29394</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-09</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5366,12 +5382,12 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -5386,24 +5402,24 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (supersedes BATCH-6 BUG-11 block). With requireReview=ON, the completion CTA = 'Send To Review' (wizard 'Complete &amp; Send to Review'); the receive step contains NO inline receive fields (0 qty/invoice inputs inside the dialog) and 'Receive Parts' routes to the shared receive page /bulk-receive (returnTo=WorkOrder), not an inline modal. Setting restored.</t>
+          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>C29390</t>
+          <t>C29395</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-05</t>
+          <t>SF-REV-10</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5413,12 +5429,12 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G93" s="14" t="inlineStr">
@@ -5428,29 +5444,29 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
+          <t>[V2.4 Δ4 CONFIRMED 2026-07-13] The V2.4 2026-07-13 spec (R7 = VIN-only, no note) confirms the note removal already applied here in the Milos Round-2 pass — expected is already VIN-only with no review note field, so no content change was needed. FLAG (do not assert): spec R10 still lists the test id input_review_note even though R7 dropped the note field — internal spec inconsistency to confirm on the live build during re-VIU. || [MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>C29391</t>
+          <t>C29397</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-06</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5460,12 +5476,12 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -5480,24 +5496,24 @@
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
+          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>C29392</t>
+          <t>C29398</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -5507,7 +5523,7 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -5527,39 +5543,39 @@
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Not separately asserted in VIU. Needs live verification.</t>
+          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>C29393</t>
+          <t>C29401</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-08</t>
+          <t>SF-UX-01</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
+          <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -5569,44 +5585,44 @@
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
+          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>C29394</t>
+          <t>C29402</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-09</t>
+          <t>SF-UX-02</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
+          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
@@ -5621,34 +5637,34 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>C29395</t>
+          <t>C29403</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-10</t>
+          <t>SF-UX-03</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
+          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
@@ -5663,44 +5679,44 @@
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
+          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>C29397</t>
+          <t>C29405</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-PERM-01</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
@@ -5715,34 +5731,34 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
+          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>C29398</t>
+          <t>C29406</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -5762,34 +5778,34 @@
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
+          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>C29401</t>
+          <t>C29407</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-01</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Verify the work order primary button reads 'Create Work Order'</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
@@ -5809,34 +5825,34 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
+          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>C29402</t>
+          <t>C29408</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-02</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -5856,34 +5872,34 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
+          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>C29403</t>
+          <t>C29409</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-03</t>
+          <t>SF-PERM-05</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
@@ -5903,24 +5919,24 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
+          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>C29405</t>
+          <t>C29410</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-01</t>
+          <t>SF-PERM-06</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -5930,12 +5946,12 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G104" s="14" t="inlineStr">
@@ -5950,24 +5966,24 @@
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
+          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>C29406</t>
+          <t>C29411</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-02</t>
+          <t>SF-PERM-07</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -5977,12 +5993,12 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G105" s="14" t="inlineStr">
@@ -5997,24 +6013,24 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
+          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>C29407</t>
+          <t>C29412</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-PERM-08</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6024,12 +6040,12 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -6044,24 +6060,24 @@
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
+          <t>[RE-PURPOSED 2026-07-10] Milos ruling (relayed by QA lead): self-review IS acceptable — a user MAY Mark Reviewed a work order they completed, PROVIDED their role holds the Mark Reviewed permission (permission-gated only, NO identity restriction). This case flipped from the obsolete negative (was: completer cannot Mark Reviewed) into the POSITIVE case above. | VIU EVIDENCE: the self-review-by-a-permissioned-role positive WAS directly observed — the SAME admin (who holds Review Work Orders) who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). The permission-gating half (a role WITHOUT the permission cannot) was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2; FE hides the control for non-reviewers). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). =&gt; VIU-Verified: self-review allowed for permissioned role per Milos ruling 2026-07-10; permission-gating verified. Origin defect BUG-5 / TICKET 1 dropped as expected behavior.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>C29408</t>
+          <t>C29413</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -6071,12 +6087,12 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
@@ -6091,24 +6107,24 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>C29409</t>
+          <t>C29414</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6118,12 +6134,12 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -6138,39 +6154,39 @@
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
+          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>C29410</t>
+          <t>C29415</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -6185,39 +6201,39 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
+          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>C29411</t>
+          <t>C29417</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-07</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
@@ -6232,39 +6248,39 @@
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>C29412</t>
+          <t>C29418</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-08</t>
+          <t>SF-VAL-04</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
+          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G111" s="14" t="inlineStr">
@@ -6279,34 +6295,34 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>[RE-PURPOSED 2026-07-10] Milos ruling (relayed by QA lead): self-review IS acceptable — a user MAY Mark Reviewed a work order they completed, PROVIDED their role holds the Mark Reviewed permission (permission-gated only, NO identity restriction). This case flipped from the obsolete negative (was: completer cannot Mark Reviewed) into the POSITIVE case above. | VIU EVIDENCE: the self-review-by-a-permissioned-role positive WAS directly observed — the SAME admin (who holds Review Work Orders) who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). The permission-gating half (a role WITHOUT the permission cannot) was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2; FE hides the control for non-reviewers). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). =&gt; VIU-Verified: self-review allowed for permissioned role per Milos ruling 2026-07-10; permission-gating verified. Origin defect BUG-5 / TICKET 1 dropped as expected behavior.</t>
+          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>C29413</t>
+          <t>C29419</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
@@ -6326,39 +6342,39 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
+          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>C29414</t>
+          <t>C29421</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-VAL-07</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G113" s="14" t="inlineStr">
@@ -6373,24 +6389,24 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
+          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>C29415</t>
+          <t>C29422</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-VAL-08</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
@@ -6400,12 +6416,12 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G114" s="14" t="inlineStr">
@@ -6420,24 +6436,24 @@
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
+          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
         <is>
-          <t>C29417</t>
+          <t>C29424</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-VAL-10</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -6447,12 +6463,12 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G115" s="14" t="inlineStr">
@@ -6467,336 +6483,7 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="12" t="inlineStr">
-        <is>
-          <t>C29418</t>
-        </is>
-      </c>
-      <c r="B116" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
-        </is>
-      </c>
-      <c r="C116" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-04</t>
-        </is>
-      </c>
-      <c r="D116" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E116" s="12" t="inlineStr">
-        <is>
-          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
-        </is>
-      </c>
-      <c r="F116" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G116" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H116" s="12" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="I116" s="12" t="inlineStr">
-        <is>
-          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="12" t="inlineStr">
-        <is>
-          <t>C29419</t>
-        </is>
-      </c>
-      <c r="B117" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
-        </is>
-      </c>
-      <c r="C117" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-05</t>
-        </is>
-      </c>
-      <c r="D117" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
-        </is>
-      </c>
-      <c r="F117" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G117" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H117" s="12" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="I117" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="12" t="inlineStr">
-        <is>
-          <t>C29420</t>
-        </is>
-      </c>
-      <c r="B118" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
-        </is>
-      </c>
-      <c r="C118" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-06</t>
-        </is>
-      </c>
-      <c r="D118" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E118" s="12" t="inlineStr">
-        <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
-        </is>
-      </c>
-      <c r="F118" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G118" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H118" s="12" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="I118" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present. Cannot receive without BOTH a vendor and a part number.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="12" t="inlineStr">
-        <is>
-          <t>C29421</t>
-        </is>
-      </c>
-      <c r="B119" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
-        </is>
-      </c>
-      <c r="C119" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-07</t>
-        </is>
-      </c>
-      <c r="D119" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E119" s="12" t="inlineStr">
-        <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
-        </is>
-      </c>
-      <c r="F119" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G119" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H119" s="12" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="I119" s="12" t="inlineStr">
-        <is>
-          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="12" t="inlineStr">
-        <is>
-          <t>C29422</t>
-        </is>
-      </c>
-      <c r="B120" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
-        </is>
-      </c>
-      <c r="C120" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-08</t>
-        </is>
-      </c>
-      <c r="D120" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E120" s="12" t="inlineStr">
-        <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
-        </is>
-      </c>
-      <c r="F120" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G120" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H120" s="12" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="I120" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="12" t="inlineStr">
-        <is>
-          <t>C29424</t>
-        </is>
-      </c>
-      <c r="B121" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
-        </is>
-      </c>
-      <c r="C121" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-10</t>
-        </is>
-      </c>
-      <c r="D121" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="inlineStr">
-        <is>
-          <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
-        </is>
-      </c>
-      <c r="F121" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G121" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H121" s="12" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="I121" s="12" t="inlineStr">
-        <is>
           <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="12" t="inlineStr">
-        <is>
-          <t>C29425</t>
-        </is>
-      </c>
-      <c r="B122" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
-        </is>
-      </c>
-      <c r="C122" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-11</t>
-        </is>
-      </c>
-      <c r="D122" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E122" s="12" t="inlineStr">
-        <is>
-          <t>Verify the approve-line error text appears when completing with an unapproved line</t>
-        </is>
-      </c>
-      <c r="F122" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G122" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H122" s="12" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="I122" s="12" t="inlineStr">
-        <is>
-          <t>PARTIAL in VIU — error not cleanly isolated (S17-02-approval-error.png). Needs a WO whose only blocker is the unapproved line. | VIU-Verified 2026-07-08: simple-complete with an unapproved (authorization_required) line returns 400 with text "All lines must be approved before completing the work order." (WO a71ec2f0).</t>
         </is>
       </c>
     </row>
@@ -6916,13 +6603,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B120" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B121" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6934,7 +6614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7750,17 +7430,17 @@
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>C29367</t>
+          <t>C29368</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -7770,12 +7450,12 @@
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -7790,39 +7470,39 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>C29368</t>
+          <t>C29373</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -7832,29 +7512,29 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
+          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>C29373</t>
+          <t>C29375</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -7864,12 +7544,12 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -7879,29 +7559,29 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
+          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>C29375</t>
+          <t>C29376</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-RCV-08</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -7911,12 +7591,12 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -7926,39 +7606,39 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>C29376</t>
+          <t>C29379</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -7973,29 +7653,29 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>C29379</t>
+          <t>C29380</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -8005,12 +7685,12 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G23" s="15" t="inlineStr">
@@ -8025,24 +7705,24 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
+          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29380</t>
+          <t>C29382</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -8052,7 +7732,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -8072,39 +7752,39 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
+          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29382</t>
+          <t>C29396</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -8114,29 +7794,29 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
+          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29396</t>
+          <t>C29399</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
@@ -8146,12 +7826,12 @@
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -8161,39 +7841,39 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29399</t>
+          <t>C29404</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-UX-04</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -8208,39 +7888,39 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29404</t>
+          <t>C29423</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-04</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -8255,44 +7935,44 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
+          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29416</t>
+          <t>C29426</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-02</t>
+          <t>SF-QB-01</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
@@ -8302,44 +7982,44 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.) || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED (needs-data: VIN-less asset). Confirmed not seedable in-harness: all 50 sampled vehicles (GET /api/vehicles) carry a VIN; POST /api/vehicles -&gt; 405 (GET-only, no API create route found). The non-review completion wizard only prompts for VIN when the asset lacks one, so this gate needs a VIN-less asset seeded (or an existing vehicle's VIN cleared, which would modify shared data).</t>
+          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29423</t>
+          <t>C29428</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-QB-03</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -8349,29 +8029,29 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29426</t>
+          <t>C29429</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-01</t>
+          <t>SF-QB-04</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -8381,12 +8061,12 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
@@ -8401,24 +8081,24 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29428</t>
+          <t>C29430</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-QB-05</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
@@ -8428,12 +8108,12 @@
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -8448,24 +8128,24 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
+          <t>Not driven in VIU. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29429</t>
+          <t>C29431</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-04</t>
+          <t>SF-QB-06</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -8475,7 +8155,7 @@
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -8495,24 +8175,24 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29430</t>
+          <t>C29432</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-QB-07</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -8522,7 +8202,7 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -8542,24 +8222,24 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29431</t>
+          <t>C29433</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-06</t>
+          <t>SF-QB-08</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -8569,7 +8249,7 @@
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -8588,100 +8268,6 @@
         </is>
       </c>
       <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
-        <is>
-          <t>C29432</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-07</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E36" s="12" t="inlineStr">
-        <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G36" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H36" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I36" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>C29433</t>
-        </is>
-      </c>
-      <c r="B37" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-08</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E37" s="12" t="inlineStr">
-        <is>
-          <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
-        </is>
-      </c>
-      <c r="F37" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G37" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I37" s="12" t="inlineStr">
         <is>
           <t>Not driven in VIU. Needs live verification.</t>
         </is>
@@ -8723,8 +8309,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9072,6 +8656,560 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>TestRail ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>TestRail Link</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>SF ID (Case ID)</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>Area</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>VIU Status</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>Blocker/Reason</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>C29305</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>SF-COMP-16</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>Verify the optional-invoice completion modal collects the required vehicle fields (mileage and engine hours; VIN only when Require Review is off) when missing</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>[V2.4 Δ1 APPLIED 2026-07-13] VIN handling clarified per the V2.4 spec: Story-4 (required-invoice) S4-R3 drops VIN from the completion modal, and in the review-on flow VIN is captured by the reviewer (Story 16). This Story-3 (optional-invoice) case retains VIN ONLY for the review-off path, exactly per S3-R3 ('mileage + VIN [when review off] + engine hours; when review on VIN is asked at the reviewer'), so VIN is NOT over-removed here. Re-VIU needed to confirm the live modal field set on both review-off and review-on paths. || Not isolated in VIU. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>C29310</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
+        </is>
+      </c>
+      <c r="C3" s="12" t="inlineStr">
+        <is>
+          <t>SF-COMP-21</t>
+        </is>
+      </c>
+      <c r="D3" s="12" t="inlineStr">
+        <is>
+          <t>Completion — Line approval gate</t>
+        </is>
+      </c>
+      <c r="E3" s="12" t="inlineStr">
+        <is>
+          <t>Verify on a required-invoice work order an unapproved line disables the Complete Work Order button with a tooltip</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G3" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H3" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+        </is>
+      </c>
+      <c r="I3" s="12" t="inlineStr">
+        <is>
+          <t>[V2.4 Δ2 APPLIED 2026-07-13] Re-scoped to the Story-4 (required-invoice) surface: per S4-R8 an unapproved line DISABLES the Complete Work Order button with a tooltip naming the line (a NEW disabled state), which is different from Stories 2/3/16 that keep the error-toast / active-CTA model. Prior expected asserted 'no new disabled state' — superseded by S4-R8. Needs live re-VIU of the disabled+tooltip affordance on the required-invoice completion modal. || (prior) VIU-Verified 2026-07-08 against the OLD error-model expected: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced, WO a71ec2f0) — that BE error still stands; the FE affordance is what changed to disabled+tooltip for Story 4.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>C29311</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>SF-COMP-22</t>
+        </is>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>Completion — Line approval gate</t>
+        </is>
+      </c>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>Verify a manually unapproved line disables the required-invoice Complete Work Order button with a tooltip even when Auto-approve is ON</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="inlineStr">
+        <is>
+          <t>[V2.4 Δ2 APPLIED 2026-07-13] Re-scoped to the Story-4 (required-invoice) surface: per S4-R8 the disabled Complete Work Order button + tooltip holds even with Auto-approve ON when a line is manually unapproved. Prior expected used the error-model wording — superseded by S4-R8 for Story 4 (Stories 2/3/16 keep the error model). Needs live re-VIU. || (prior) VIU-Verified 2026-07-08 against the OLD error model: block fires from the line's own authorization_required status while org autoApproveLines=true; same 400 as SF-COMP-21 (BE error still stands; FE affordance changed to disabled+tooltip for Story 4).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>C29367</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>SF-PNFIX-05</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Inline Part-Number Fix (Story 10)</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
+        </is>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H5" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+        </is>
+      </c>
+      <c r="I5" s="12" t="inlineStr">
+        <is>
+          <t>[V2.4 Δ3 APPLIED 2026-07-13] Aligned to the S13-R6 part-number receive gate and extended with the new S13-R7 cost/sell receive gate (was part-number + vendor only). Needs live re-VIU of the cost/sell block. || Not driven in VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>C29374</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>SF-RCV-06</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Accept Delivery (Story 12)</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H6" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
+        </is>
+      </c>
+      <c r="I6" s="12" t="inlineStr">
+        <is>
+          <t>[V2.4 Δ3 APPLIED 2026-07-13] Added the new S13-R7 cost/sell receive gate to the Accept Delivery gate list (was vendor + part number + invoice). Needs live re-VIU of the cost/sell block. || VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN / missing cost-sell) need a vendor-missing item on an Accept Delivery group. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>C29381</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>SF-VEND-04</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Assign Vendor + Merge (Story 13)</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+        </is>
+      </c>
+      <c r="I7" s="12" t="inlineStr">
+        <is>
+          <t>[V2.4 Δ3 APPLIED 2026-07-13] Added the new S13-R6 (part number) + S13-R7 (cost/sell) receive-enable conditions — assigning the vendor no longer enables Receive on its own. Needs live re-VIU of the part#/cost-sell gates alongside vendor assignment. || [FOLLOW-UP VIU 2026-07-09 sv7301] Auto-assign + QB-flag-clear VERIFIED: on the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), PO left the Vendor-Missing group into the vendor's group. Receive-enable-only-with-PN+cost/sell now needs a dedicated re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>C29442</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29442</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>SF-VEND-06</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Assign Vendor + Merge (Story 13)</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
+        </is>
+      </c>
+      <c r="F8" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — new case for V2.4 Δ3 (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+        </is>
+      </c>
+      <c r="I8" s="12" t="inlineStr">
+        <is>
+          <t>NEW case authored 2026-07-13 to cover the V2.4 Δ3 receive-time cost/sell gate (S13-R7), which was not cleanly covered by extending SF-VAL-06 / SF-RCV-06. UI-affordance gate (indication shown + Receive button disabled) — kept in the functional Assign Vendor + Merge (Story 13) section per CLAUDE.md rule 4 (no HTTP-status assertion). Needs live VIU on sv7301.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>C29416</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-02</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I9" s="12" t="inlineStr">
+        <is>
+          <t>[V2.4 Δ1 APPLIED 2026-07-13] Scoped to the non-review No-PO / Optional-invoice flow. Per the V2.4 spec, S4-R3 (required-invoice / Story 4) no longer collects VIN in the completion modal, and the review-on flow captures VIN at the reviewer (Story 16); the review-off VIN-at-completion gate stays for Story 2 (S2-R2) and Story 3 (S3-R3, VIN when review off) plus S15-R2 ('VIN when required'). VIN NOT over-removed — it is kept where the spec keeps it. || Not isolated in VIU. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED (needs-data: VIN-less asset). Confirmed not seedable in-harness: all 50 sampled vehicles (GET /api/vehicles) carry a VIN; POST /api/vehicles -&gt; 405. The non-review completion wizard only prompts for VIN when the asset lacks one, so this gate needs a VIN-less asset seeded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>C29420</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-06</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
+        </is>
+      </c>
+      <c r="F10" s="12" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I10" s="12" t="inlineStr">
+        <is>
+          <t>[V2.4 Δ3 APPLIED 2026-07-13] Extended with the new S13-R7 receive-time cost/sell gate (was vendor + part number only). Needs live re-VIU of the cost/sell block. || [FRESH VIU 2026-07-10 sv7301] Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present — the cost gate was observed incidentally (cost required alongside PN+vendor) but not isolated as its own step; the S13-R7 cost/sell block now needs a dedicated re-VIU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>C29425</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-11</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>Verify an unapproved line blocks completion — required-invoice shows a disabled Complete button with a tooltip; other flows show the approve-line error</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+        </is>
+      </c>
+      <c r="H11" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+        </is>
+      </c>
+      <c r="I11" s="12" t="inlineStr">
+        <is>
+          <t>[V2.4 Δ2 APPLIED 2026-07-13] Now documents the SPLIT: Story-4 (required-invoice) = disabled Complete button + tooltip (S4-R8); Stories 2/3/16 = existing approve-line error with the CTA staying active (S3-R9 / R11). Needs live re-VIU of both models. || (prior) VIU-Verified 2026-07-08 against the error model: simple-complete with an unapproved (authorization_required) line returns 400 "All lines must be approved before completing the work order." (WO a71ec2f0) — the BE error still stands; the Story-4 FE affordance changed to disabled+tooltip.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -9398,7 +9536,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice modal collects required vehicle fields (mileage, VIN, engine hours) when missing</t>
+          <t>Verify the optional-invoice completion modal collects the required vehicle fields (mileage and engine hours; VIN only when Require Review is off) when missing</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -9406,9 +9544,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -9418,7 +9556,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
+          <t>[V2.4 Δ1 APPLIED 2026-07-13] VIN handling clarified per the V2.4 spec: Story-4 (required-invoice) S4-R3 drops VIN from the completion modal, and in the review-on flow VIN is captured by the reviewer (Story 16). This Story-3 (optional-invoice) case retains VIN ONLY for the review-off path, exactly per S3-R3 ('mileage + VIN [when review off] + engine hours; when review on VIN is asked at the reviewer'), so VIN is NOT over-removed here. Re-VIU needed to confirm the live modal field set on both review-off and review-on paths. || Not isolated in VIU. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10382,7 @@
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number (and a vendor for vendor-missing) even on an invoiced/paid WO</t>
+          <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -10252,9 +10390,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G27" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -10264,7 +10402,7 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>[V2.4 Δ3 APPLIED 2026-07-13] Aligned to the S13-R6 part-number receive gate and extended with the new S13-R7 cost/sell receive gate (was part-number + vendor only). Needs live re-VIU of the cost/sell block. || Not driven in VIU.</t>
         </is>
       </c>
     </row>
@@ -10593,7 +10731,7 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
+          <t>[V2.4 Δ4 CONFIRMED 2026-07-13] The V2.4 2026-07-13 spec (R7 = VIN-only, no note) confirms the note removal already applied here in the Milos Round-2 pass — expected is already VIN-only with no review note field, so no content change was needed. FLAG (do not assert): spec R10 still lists the test id input_review_note even though R7 dropped the note field — internal spec inconsistency to confirm on the live build during re-VIU. || [MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
         </is>
       </c>
     </row>
@@ -10996,7 +11134,7 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review flow)</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -11004,9 +11142,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G43" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -11016,7 +11154,7 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU. Needs live verification. (In review flow, VIN is captured at Mark Reviewed — see SF-REV-06.) || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED (needs-data: VIN-less asset). Confirmed not seedable in-harness: all 50 sampled vehicles (GET /api/vehicles) carry a VIN; POST /api/vehicles -&gt; 405 (GET-only, no API create route found). The non-review completion wizard only prompts for VIN when the asset lacks one, so this gate needs a VIN-less asset seeded (or an existing vehicle's VIN cleared, which would modify shared data).</t>
+          <t>[V2.4 Δ1 APPLIED 2026-07-13] Scoped to the non-review No-PO / Optional-invoice flow. Per the V2.4 spec, S4-R3 (required-invoice / Story 4) no longer collects VIN in the completion modal, and the review-on flow captures VIN at the reviewer (Story 16); the review-off VIN-at-completion gate stays for Story 2 (S2-R2) and Story 3 (S3-R3, VIN when review off) plus S15-R2 ('VIN when required'). VIN NOT over-removed — it is kept where the spec keeps it. || Not isolated in VIU. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED (needs-data: VIN-less asset). Confirmed not seedable in-harness: all 50 sampled vehicles (GET /api/vehicles) carry a VIN; POST /api/vehicles -&gt; 405. The non-review completion wizard only prompts for VIN when the asset lacks one, so this gate needs a VIN-less asset seeded.</t>
         </is>
       </c>
     </row>
@@ -11137,7 +11275,7 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendor-missing part cannot be received without both a vendor and a part number</t>
+          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -11145,9 +11283,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G46" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -11157,7 +11295,7 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present. Cannot receive without BOTH a vendor and a part number.</t>
+          <t>[V2.4 Δ3 APPLIED 2026-07-13] Extended with the new S13-R7 receive-time cost/sell gate (was vendor + part number only). Needs live re-VIU of the cost/sell block. || [FRESH VIU 2026-07-10 sv7301] Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present — the cost gate was observed incidentally (cost required alongside PN+vendor) but not isolated as its own step; the S13-R7 cost/sell block now needs a dedicated re-VIU.</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11735,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B10" s="8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Current headline tally (2026-07-13): VIU-Verified 114 / VIU-Pending 34 / Open-Question 5 / Pending-Retest 10 = 163. Pending-Retest = the V2.4 Δ1-Δ4 cases (expected changed 2026-07-13) awaiting a live re-VIU. DEV-NOT-BUILT is 0.</t>
+          <t>Current headline tally (2026-07-13): VIU-Verified 116 / VIU-Pending 35 / Open-Question 1 / Pending-Retest 0 = 163. Pending-Retest = the V2.4 Δ1-Δ4 cases (expected changed 2026-07-13) awaiting a live re-VIU. DEV-NOT-BUILT is 0.</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         </is>
       </c>
       <c r="B33" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C35" s="2" t="n"/>
     </row>
@@ -1068,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I115"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>Verify the Work Order settings page shows all Simple-Flow toggles in order with new vs existing visually distinct</t>
+          <t>Verify the Work Orders settings tab lists all Work Order setting toggles in order</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="I2" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (08-settings-workorders.png, S1-01-settings-baseline.png). NOTE: the spec's 'Create Purchase Orders' toggle (S1-R2) is absent from this list — covered separately in SF-SET-03 / Open Questions (VIU bug #1).</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): all 7 toggles present in the listed order with helper text; no Full/Simple mode selector; toggles render as one flat list with no visual new-vs-existing distinction (spec S1-R1 wanted new toggles visually distinct — not present in build, so the title/expected were corrected to match the build). Prior: 2026-07-06 (08-settings-workorders.png).</t>
         </is>
       </c>
     </row>
@@ -1219,7 +1219,7 @@
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (08-settings-workorders.png). Server model has requireVehicleIdentifier/vehicleIdentifier:'vin' but it is not exposed as a WO-settings toggle.</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): no mode selector and no VIN toggle on the tab. Settings model holds requireVehicleIdentifier / vehicleIdentifier:'vin' but it is not exposed as a Work Orders toggle. Prior: 2026-07-06 (08-settings-workorders.png).</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (08-settings-workorders.png). Drives Story 3 (Optional) vs Story 4 (Required) wizard behavior.</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): toggle present; helper text captured exactly as shown (dropped the earlier 'approximately' hedge). Maps to requireVendorInvoiceNumber. Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (Story 2 WO S2-15747 line auto-approved on add).</t>
+          <t>Wording+VIU 2026-07-13: Auto-approve Lines helper text confirms 'New work order lines are created already approved, skipping the line approval step'. Auto-approve-ON line behavior verified in prior VIU line-drive 2026-07-06 (WO S2-15747 line auto-approved on add); not re-driven this run to limit settings churn on the shared env.</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S17-01-unapproved-line.png).</t>
+          <t>Wording+VIU 2026-07-13: with Auto-approve Lines Off, a new line stays unapproved with Approve/Decline actions — verified in prior VIU line-drive 2026-07-06 (S17-01-unapproved-line.png); helper text re-confirmed 2026-07-13. Not re-driven this run to limit settings churn on the shared env.</t>
         </is>
       </c>
     </row>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 vs baseline requireTechStories:true, requireMileage:true, requireHours:false, autoPickInventoryParts:true (08-settings-workorders.png).</t>
+          <t>Wording+VIU 2026-07-13: toggles present; states match GET /api/organizations/settings (org baseline this run: requireTechStories:false, requireMileage:false, requireHours:false, autoPickInventoryParts:false). Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -1454,24 +1454,24 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S1-02-toggled-eng-hours.png, S1-03-after-save.png, S1-04-persisted.png). Baseline was restored at end of the VIU run.</t>
+          <t>Wording+VIU 2026-07-13: flipped Require Engine Hours (requireHours) via POST /api/organizations/settings/change -&gt; 200, GET reflected the new value, then restored to baseline -&gt; 200 (org left unchanged). Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>C29284</t>
+          <t>C29285</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29284</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29285</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>SF-SET-10</t>
+          <t>SF-SET-11</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Verify a settings change applies to future completions only and not to already-completed work orders</t>
+          <t>Verify a non-admin user cannot see or modify the Work Order settings</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -1501,24 +1501,24 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Not driven in the VIU run (needs a second completion after a settings change). Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: Technician quick-login -&gt; POST /api/organizations/settings/change = 403 (admin = 200). FE redirects tech away from the settings route. Non-admin cannot save WO settings. Prior: 2026-07-07.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>C29285</t>
+          <t>C29286</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29285</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29286</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SF-SET-11</t>
+          <t>SF-SET-12</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Verify a non-admin user cannot see or modify the Work Order settings</t>
+          <t>Verify the settings model contains no operatingMode field and no requireVin setting</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -1548,24 +1548,24 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>Defined by SV-8183: the Work Order settings inherit the settingsApp route guard (no new atom); editable only by roles with App Settings ON (defaults Admin, Service Manager, Office). Role-gating negatives not yet verified live (only the admin session works on sv7301; tech key = 403). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED. Same as SF-PERM-01: tech redirected from settings route (FE) and BE POST /api/organizations/settings/change -&gt; 403; admin -&gt; 200. Non-admin cannot view or save WO settings.</t>
+          <t>Wording+VIU 2026-07-13: GET /api/organizations/settings keys = id, organizationId, requireMileage, requireHours, requireTechStories, requireVehicleIdentifier, vehicleIdentifier, autoPickInventoryParts, autoApproveLines, requireVendorInvoiceNumber, requireReview. No operatingMode, no requireVin. Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>C29286</t>
+          <t>C29287</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29286</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29287</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SF-SET-12</t>
+          <t>SF-SET-13</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Verify the settings model contains no operatingMode field and no requireVin setting</t>
+          <t>Verify the Save Settings button is only enabled when there is an unsaved change</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q6 — Save Settings always enabled (no dirty-state gating) — intended or bug?</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 via GET /api/organizations/settings; no operatingMode / no requireVin toggle. (requireVehicleIdentifier exists but is not a WO-settings toggle.)</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): 'Save Settings' button present and enabled with no pending change (no dirty-state gating). Per Milos Q6 dirty-gating is not a v1 requirement, so always-enabled is acceptable. Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — the toggle IS on the settings page (resolves the design-handoff note that it was prototype-only). See S16-04-review-wizard.png. || [RECONCILED V2.4 2026-07-08] The queued 'toggle defaults ON for the org' addition was NOT applied — V2.4 S1-R4 keeps per-cohort defaults (see §8). Toggle-present + routes-to-review expectations stand.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live): toggle present with helper text 'Work orders must be reviewed and signed off before they can be completed'. Corrected the CTA label: the ready-WO action relabels to 'Send To Review' (confirmed live), not 'Complete &amp; Send to Review'. Routes to 'Review' status + 'Ready for Review'.</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (08-settings-workorders.png).</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): all 7 toggles carry helper text (captured verbatim in wording-glossary-2026-07-13.md). Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (14-wo-detail.png).</t>
+          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. 'New Line' and 'Complete Work Order' buttons sit together in the WO Lines toolbar.</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 on WO S2-15747 (S2-13-details.png, S2-14-success.png). Reviewed runs in the background per S2-R3.</t>
+          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Labor-only WO completed Details-&gt;Success with no receive step (drove S2-15795 / S2-15825 to Success live 2026-07-13).</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-14-success.png).</t>
+          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Success screen showed WO number + 'Invoice total $434.95' with 'Done' and 'Go To Invoice' (S2-15825, live 2026-07-13).</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Success screen verified; the Go-to-Invoice navigation was not driven in the VIU run. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Go To Invoice from Success navigated to /workorders/{id}/finance (Finance step, invoice-ready draft) (VIU3-05-invoice-finance.png).</t>
+          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. 'Go To Invoice' present on Success; Finance step per prior drive.</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>The Details step collecting Mileage was seen (S2-13-details.png) but the empty-field block was not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard (WO 00609f73) blocks with "Mileage is a required field" when the required vehicle field (mileage) is empty on Continue. Evidence VIU2-02-mileage-gate.png.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-vehicle-field block (needs Require Mileage ON + missing value) per 2026-07-06 drive; not re-driven this session to limit settings churn on the shared env.</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>§8 open question — auto-receive of in-stock inventory on simple completion is UNCONFIRMED. Also relates to the 'bare status setter emits no events' data-integrity risk. Not driven in VIU. Confirm intended behavior. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4), so the completion expectations stand. || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed in-stock inventory parts DO decrement on-hand and write Part History on completion (the PO question is a separate concern). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (decrement + skip-path no-bypass). Seeded WO 1490338a with inventory part P550848 (inv_part 000657fe, on-hand 6). Manual Pick (button_part_request_action -&gt; POST /api/work-orders/part/perform-request-status-action 201) decremented on-hand 6-&gt;5; simple-complete (skip path) BE-gated on picking (400 'All inventory and found parts must be picked before completing the work order.' until picked), then returned 201 (WO=Complete) with on-hand STAYING 5 (movement not bypassed by the skip-path status setter; confirmed via API GET /api/inventory/parts/{id}.quantity AND the /parts/inventory list UI showing qty 5). Part-History LOG DISPLAY not separately surfaced (see SF-QB-01 note / OBS-6) but the net on-hand movement is proven.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — in-stock inventory decrement + Part History on simple completion (FV-comp08/decrement, 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>Auto-pick was ON in the VIU baseline, so the pick step was not exercised. Needs live verification with auto-pick OFF. || [FRESH VIU 2026-07-10 sv7301] PROGRESS: with autoPickInventoryParts=OFF (current org drift), adding inventory part P550848 left it status 'in_stock' (NOT auto-picked); simple-complete BE-BLOCKED 400 'All inventory and found parts must be picked before completing the work order.'; after line-level Pick (perform-request-status-action 201 -&gt; status picked) completion proceeded (201). Expected #2 (cannot complete until picked) and #3 (after pick, completes) PROVEN. Expected #1 (completion-MODAL Pick step offering 'Pick all from default bins'/'Review individually') NOT yet surfaced — pick was driven at line level, not via the completion wizard's pick step. Remains VIU-Pending on the modal pick-step UI. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. With autoPickInventoryParts=OFF and an unpicked inventory part (P550848, status in_stock), the completion wizard shows a PICK STEP (data-test-id section_wizard_pick): '1 part needs picking' + Pick All (button_pick_all) + text_unpicked_parts_count + button_pick_continue; completion is gated (BE also 400 'All inventory and found parts must be picked...'); after Pick All -&gt; 'All parts picked' -&gt; Complete Work Order proceeds. Expected #2 (cannot complete until picked) + #3 (proceeds after picking) fully proven; the pick step exists with 'Pick All' (the alternate 'Review individually' path was not separately exercised in this 1-part case).</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Auto-pick OFF -&gt; Pick step ('Pick all from default bins' / 'Review individually'), FV-comp08-wizard1/2.png (2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Return-to-Approved verified 2026-07-06 (S16-03-reopened.png). The 'already-received vs newly-added' modal summary was not separately driven.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — adding a line to a completed WO returns it to Approved (2026-07-06).</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2112,7 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Existing behaviors preserved by design; not re-driven in the VIU run. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — line-level Complete + per-part Receive still work (line 'Receive' button confirmed live 2026-07-13).</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=false; wizard = 'Receive → Success', '2 parts waiting to receive', with Cancel / Complete Without Receiving / Receive Parts (S3-01-wizard-optional.png).</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — optional-invoice wizard actions Cancel / Complete Without Receiving / Receive Parts + 'N parts waiting to receive' (FV-comp13-receivestep.png, 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Parts-to-receive count verified 2026-07-06 ('2 parts waiting to receive', S3-01-wizard-optional.png). Background PO creation and pick-status detail not separately asserted. || [V2.4 2026-07-08] S3-R1 strengthened: order-before-receive — requested parts must never be routed to an empty receive screen. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Optional-invoice completion wizard (requireVendorInvoiceNumber OFF) receive step shows '2 parts waiting to receive' plus '1 part is not ordered yet - Going to receive parts or completing the work order will order those parts' (background PO creation); API confirmed an order_id assigned + waiting_to_receive. Both 'Receive Parts' and 'Complete Without Receiving' present.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — background POs created + parts-to-receive count; vendorless part goes on WO PO flagged Vendor Missing (2026-07-08/10).</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2253,7 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded). || [FRESH VIU 2026-07-10 sv7301] VERIFIED (OBS-5 consolidation; supersedes BATCH-6 BUG-11 block). With requireVendorInvoiceNumber=OFF, the optional-invoice completion wizard shows 'N parts waiting to receive' + 'Clicking Receive Parts will take you to the purchase order page' + a background-order note; clicking Receive Parts navigated to the consolidated shared receive page /bulk-receive?workOrderId=...&amp;returnTo=WorkOrder ('Receive Vendor Parts', receive all vendors at once) — the shipped shared receive surface (replaces the legacy Accept Delivery named in the case, per OBS-5). Setting restored.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — 'Receive Parts' opens the shared Accept Delivery page for all vendors (FV-comp13, 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2300,7 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Action present (S3-01) but not driven to completion. Needs live verification. Waiting-on-Parts column itself is not built (Story 14). | VIU-Verified 2026-07-08: optional-invoice (requireVendorInvoiceNumber=false) completion via simple-complete returned 201 and WO-&gt;Complete while both parts stayed status=waiting_to_receive (quantity_remaining preserved); UI Receive step shows the "Complete Without Receiving" button (VIU2-03-receive-step.png). Line-Receive-button sub-claim not separately asserted.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Complete Without Receiving completes WO, unreceived parts stay waiting, line keeps Receive (2026-07-08/10).</t>
         </is>
       </c>
     </row>
@@ -2347,24 +2347,24 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Idempotency not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Cancel closes modal, no duplicate POs on re-open (idempotent) (2026-07-08).</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29306</t>
+          <t>C29305</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-17</t>
+          <t>SF-COMP-16</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
+          <t>Verify the completion modal collects the missing required vehicle fields (Mileage and Engine Hours; no VIN field in the modal)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -2394,39 +2394,39 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Success screen pattern verified in Story 2; the optional-invoice completion was not driven to Success. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: optional flow reached Success 'Order complete - Work order S2-15758 - Invoice total $260.97 - Done / Go To Invoice' (VIU3-04-success.png).</t>
+          <t>Wording+VIU 2026-07-13 (S2-15827 / S2-15783 live, Require Mileage + Engine Hours ON, Require Review off): the completion Details modal ('Complete Work Order') shows Mileage + Engine Hours fields and NO VIN field; empty -&gt; 'required field' block. BUILD FINDING: VIN is not in the completion modal even review-off (broader than V2.4 Δ1). Corrected expected accordingly. Settings restored byte-identical.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29307</t>
+          <t>C29306</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29306</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-18</t>
+          <t>SF-COMP-17</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Completion — PO + Required Invoice (Story 4)</t>
+          <t>Completion — PO + Optional Invoice (Story 3)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
+          <t>Verify the optional-invoice flow reaches the Success screen with WO number and total</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
@@ -2441,24 +2441,24 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 with requireVendorInvoiceNumber=true; Complete CTA disabled, Receive Parts present, no skip option (S4-02-wizard.png). || [V2.4 2026-07-08] S4-R1: sell-price-only parts are ordered too -&gt; waiting-to-receive before the required-invoice receive gate.</t>
+          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Optional-invoice Success screen shows WO number + total + Go To Invoice/Done (live 2026-07-13).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29308</t>
+          <t>C29307</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29307</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-19</t>
+          <t>SF-COMP-18</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
+          <t>Verify the required-invoice wizard disables Complete until parts are received and offers no skip option</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
@@ -2488,24 +2488,24 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-invoice: Complete disabled until parts received, no skip option (FV-comp19, 2026-07-10).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29309</t>
+          <t>C29308</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29308</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-20</t>
+          <t>SF-COMP-19</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
+          <t>Verify the required-invoice receive round-trip returns to the modal and enables Complete once all received</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
@@ -2535,34 +2535,34 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-invoice receive round-trip enables Complete once all received (FV-comp19-receivestep/afterreceive, 2026-07-10).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29312</t>
+          <t>C29309</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29309</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-COMP-20</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Completion — PO + Required Invoice (Story 4)</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify Cancel in the required-invoice wizard makes no change to the work order</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -2582,39 +2582,39 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — Cancel in required-invoice wizard leaves WO unchanged (2026-07-08).</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29313</t>
+          <t>C29312</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -2629,39 +2629,39 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — re-running completion creates no duplicate POs (one PO per vendor) (2026-07-08).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29322</t>
+          <t>C29313</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
+          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -2676,39 +2676,39 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
+          <t>Wording+VIU 2026-07-13: inventory cores resolved via a line-level Ok/Not-OK control (Core sub-line on the line's Parts view, $ amount, $0 until Not-OK); no distinct Resolve Cores wizard step - verified prior (CORE-05-resolve-cores.png). Completion surface re-confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29323</t>
+          <t>C29314</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-01</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
+          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -2723,39 +2723,39 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-06-line-added.png).</t>
+          <t>Wording+VIU 2026-07-13: a work order with no cores shows no core sub-lines and no Resolve Cores step; completion goes Details -&gt; Success (confirmed live on labor-only WOs S2-15795/S2-15825/S2-15823 this run).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29324</t>
+          <t>C29322</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-02</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
+          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -2770,24 +2770,24 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Require Tech Story ON + missing story opened the tech-story modal before completion (S2-10-complete-1.png).</t>
+          <t>Wording+VIU 2026-07-13: the Core sub-line shows a '+$ to invoice' amount at the line level ($0 until Not-OK); no Resolve Cores wizard total - verified prior (CORE screenshots); line-level control confirmed.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29325</t>
+          <t>C29323</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-03</t>
+          <t>SF-TECH-01</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
+          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -2817,24 +2817,24 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-10-complete-1.png, S2-11-techstory.png, S2-12-after-story.png, S2-13-details.png).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; the empty line shows the 'Add tech story for this line' link.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29326</t>
+          <t>C29324</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-04</t>
+          <t>SF-TECH-02</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
+          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -2864,24 +2864,24 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S2-11-techstory.png): 'S2-15747 · Eric Mcdaniel', '1. Diagnose - Air leak', 'Line 1 of 1', Continue disabled until non-empty.</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; with Require Tech Story ON, completion is blocked until every line has a story (Require Tech Story gate; toggle confirmed SF-SET-15).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>C29327</t>
+          <t>C29325</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-TECH-03</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>VIU only exercised a single-line WO ('Line 1 of 1'). Multi-line navigation needs live verification. || VIU batch3 2026-07-08 VERIFIED: multi-line gate — Line 1 of 2 shows Next only; Line 2 of 2 shows Back + Continue (VIU3-tech-line1.png/VIU3-tech-line2.png).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Complete opens the tech-story modal first, then chains into completion (tech story -&gt; parts -&gt; complete) - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>C29328</t>
+          <t>C29326</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-TECH-04</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
@@ -2958,24 +2958,24 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>Not separately isolated in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: after saving stories and reload, saved story renders inline with Edit link (VIU3-tech-inline-saved.png).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech-story modal header 'Tech story' with 'WO# · Customer', per-line card + 'Line X of N', Next disabled until textarea non-empty - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>C29329</t>
+          <t>C29327</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-TECH-05</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story textarea exposes the test id input_tech_story</t>
+          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -3005,24 +3005,24 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL in VIU: textarea present and functional but the specific test-id was not asserted (drove via generic dialog textarea). Needs DOM check. || VIU batch3 2026-07-08 VERIFIED: tech-story textarea exposes data-test-id input_tech_story (GATE1 test-ids incl. input_tech_story, section_tech_story_gate).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; multi-line navigation (no Back on line 1; Back after; Continue/Save on last) - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>C29330</t>
+          <t>C29328</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-08</t>
+          <t>SF-TECH-06</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3032,7 +3032,7 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
+          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -3047,44 +3047,44 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — CONFIRMED] Milos: 'Story Tech will behave as it is right now, only change is some visuals, and now they can complete multiple stories at once, or individually as now.' Story 17 (SV-7876) is authoritative; the older S15-R2 line-only wording is superseded. Inline + gate-modal entry points are each independently VIU-Verified (SF-TECH-01/03/05/06); multi-at-once is covered by the SF-TECH-05 multi-line gate walk. Open question resolved.</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; saved story renders inline with a green check + text + Edit link - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>C29331</t>
+          <t>C29329</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-TECH-07</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
+          <t>Verify the tech-story modal has a text box for typing the story</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -3099,39 +3099,39 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Reworded from the dev-only 'test id input_tech_story' check to a tester-meaningful text-box check (the input_tech_story test-id is a dev-automation hook, not tester-facing). Textarea confirmed present.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>C29332</t>
+          <t>C29330</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-TECH-08</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
+          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
@@ -3141,29 +3141,29 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech story captured both inline on the line and via the completion gate modal (individually or several at once); both persist (Story 17 authoritative) - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>C29333</t>
+          <t>C29331</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-VPART-01</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -3193,24 +3193,24 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: Source dropdown offers Inventory | Vendor | Found (default Vendor); created vendorless part part_source_type='vendor' (never inventory).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>C29334</t>
+          <t>C29332</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VPART-02</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -3240,24 +3240,24 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>C29335</t>
+          <t>C29333</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-VPART-03</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -3287,24 +3287,24 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED (model-level): no-PN part created with inventory_part_id:null (no inventory item), part_source_type 'vendor'. Part History side-effect not separately inspected (backend).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>C29336</t>
+          <t>C29334</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -3334,24 +3334,24 @@
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>C29337</t>
+          <t>C29335</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VPART-05</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -3381,39 +3381,39 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>C29338</t>
+          <t>C29336</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-01</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -3428,34 +3428,34 @@
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
-          <t>PO list route /parts/orders confirmed; the no-dummy-PO placement was not driven end to end. Needs live verification. | VIU-Verified 2026-07-08: after completing a WO (53d021fb) with 2 vendorless vendor-parts, both part_requests received the SAME order_id (0a9db3e6-...) with vendor_id=null and part_number=null — one shared WO PO, no separate dummy PO. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: created a WO with 2 vendorless parts (S-15787); both part_requests share ONE order_id (f229744b, vendorMissing=true) = the WO's own PO, NO separate dummy PO. Conflict (a) RESOLVED in favour of spec V2.4.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>C29339</t>
+          <t>C29337</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-02</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -3475,24 +3475,24 @@
       </c>
       <c r="I51" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — 'Vendor Missing +N' shown on the PO list (17-po-detail.png). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] RE-CONFIRMED 2026-07-09: 'Vendor Missing' shown as badge_vendor_missing on /parts/orders and as a 'Vendor Missing' group header on the Bulk Receive page.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>C29341</t>
+          <t>C29338</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-01</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -3522,24 +3522,24 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on the Bulk Receive page a Vendor Missing PO offers select_assign_vendor_{poId} (vendor selection — Story 13) AND input_part_number_{partId} + text_missing_part_number (enter/edit the missing part number — Story 10).</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendorless part joins the WO's normal PO, no dummy PO.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>C29342</t>
+          <t>C29339</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-VMIS-02</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -3569,24 +3569,24 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: assigning a vendor to the Vendor Missing PO cleared the vendor-missing state (order vendorMissing -&gt; false, vendor_name set) and moved it to the vendor's group. NOTE: the order-level Vendor Missing flag clears on VENDOR assignment alone; the part number is enforced as a separate per-part receive gate (must be entered before that part can be received).</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. 'Vendor Missing +N' shows on PO list + detail.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>C29439</t>
+          <t>C29341</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-07</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -3616,34 +3616,34 @@
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S6-R7 orderable-from-line). The sell-price-only vendorless part shape is confirmed from prior VIU (SF-VMIS-01: two vendorless parts shared ONE WO PO, order_id 0a9db3e6, vendor_id=null, part_number=null — no dummy PO); the line-level Order action -&gt; waiting-to-receive path itself is not yet driven live. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On a WO line with a sell-only vendorless part (authorized_to_order, no vendor/PN), the line's part Order action (button_part_request_action) fired POST /api/work-orders/part/perform-request-status-action -&gt; 201; the part moved authorized_to_order -&gt; waiting_to_receive with an order_id assigned (vendor null = joined the WO's Vendor-Missing PO, no dummy PO), WITHOUT completing the WO (status stayed Approved). Receive still gated on vendor+PN (per SF-VEND-04/SF-RCV-06), cost editable (SF-RCV-10).</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendor-select + part-number edit offered on the vendor-missing PO. Stripped story refs.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>C29344</t>
+          <t>C29342</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -3663,34 +3663,34 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT in the current build — no checkboxes on /parts/orders (12-po-via-menu.png). Needs dev complete, then live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: /parts/orders shows checkbox_select_all_orders (select-all) + per-row checkbox_select_order_{id} (30 rows).</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. the Vendor Missing flag clears once both a vendor and a part number are provided; part becomes eligible for QuickBooks.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>C29345</t>
+          <t>C29439</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-VMIS-07</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -3710,24 +3710,24 @@
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: selecting POs shows an action bar 'N Purchase Orders selected' (e.g. '30 Purchase Orders selected') with button_clear_selection (Clear) + button_receive_selected (Receive Selected).</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. sell-price-only part orderable from the line's Order action, joins the Vendor-Missing PO, moves requested -&gt; waiting-to-receive without completing the WO - verified prior (C29439).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>C29346</t>
+          <t>C29344</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -3757,24 +3757,24 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S7/S8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Receive Selected navigates to /bulk-receive?ids=&lt;comma-separated selected order ids&gt; — the PO Bulk Receive page carrying exactly the selected POs.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>C29347</t>
+          <t>C29345</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
@@ -3784,12 +3784,12 @@
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G58" s="14" t="inlineStr">
@@ -3804,24 +3804,24 @@
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] VERIFIED (mechanism differs slightly): fulfilled POs are EXCLUDED from the PO list entirely (GET /api/inventory/orders returns only status ordered/partial_delivery; 0 disabled checkboxes among 30) so a fulfilled PO cannot be selected for receive. Built app excludes rather than shows-disabled.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>C29348</t>
+          <t>C29346</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3831,12 +3831,12 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G59" s="14" t="inlineStr">
@@ -3851,24 +3851,24 @@
       </c>
       <c r="I59" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (checkboxes absent). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: vendor-missing POs ARE selectable (their checkbox_select_order_* is enabled) and are clearly indicated by badge_vendor_missing on the row (5 shown). Resolves conflict (a): Epic's 'Receive hidden' is NOT what shipped — vendor-missing POs are selectable on the list.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>C29349</t>
+          <t>C29347</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -3898,34 +3898,34 @@
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: select-all selected 30 rows (current page) out of 100 total orders — scope is current page/filter, not the whole dataset.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>C29350</t>
+          <t>C29348</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back to Purchase Orders' link that returns to the PO list</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
@@ -3945,39 +3945,39 @@
       </c>
       <c r="I61" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — no Bulk Receive entry point exists yet. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: bulk page ('Receive Vendor Parts') has button_back_to_orders ('Back To Purchase Orders') top-left returning to the PO list.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>C29351</t>
+          <t>C29349</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -3992,24 +3992,24 @@
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: POs grouped by vendor with a header 'VENDOR &lt;name&gt;' + count ('N parts · M PO'), a per-vendor Expand All/Collapse All control, and per-PO expand toggle (button_toggle_expand_{poId}). Header shows 'N vendors'.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>C29352</t>
+          <t>C29350</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify the Bulk Receive page has a 'Back To Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -4039,24 +4039,24 @@
       </c>
       <c r="I63" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each PO row shows the PO number ('PO S-15778'), the related work order ('WO S-15778') and the parts count ('· 1 part').</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>C29353</t>
+          <t>C29351</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
@@ -4086,24 +4086,24 @@
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: default PARTS SELECTED 0 / POS SELECTED 0; selecting a PO (checkbox_po_{id}) selects all its parts (counter -&gt; PARTS SELECTED 4, POS SELECTED 1); an individual part can be deselected (checkbox_item_{id}; counter -&gt; 3); button_receive_all is disabled until something is checked.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>C29354</t>
+          <t>C29352</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4113,12 +4113,12 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G65" s="14" t="inlineStr">
@@ -4133,24 +4133,24 @@
       </c>
       <c r="I65" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: per-PO button_receive_po_{id} is disabled with no invoice; enabled after a vendor invoice # is entered (input_invoice_{id}) on a PO whose parts all have PNs. Also confirmed the missing-part-number gate keeps Receive disabled when a selected part lacks a PN.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>C29355</t>
+          <t>C29353</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -4180,24 +4180,24 @@
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [V2.4 2026-07-08] S8-R7/S10-R2: field-rule parity with Accept Delivery; cost editable when $0/missing. Story 8 not built. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (editability): part rows expose input_qty_{id}, input_cost_{id}, input_sell_{id} (qty/cost/sell editable). NOTE: some parts show a read-only currency_text_cost_{id} instead of input_cost (catalog/inventory-sourced cost). Sell-lock-after-WO-invoiced/paid NOT driven (needs an invoiced/paid WO) — that sub-clause remains to verify.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>C29356</t>
+          <t>C29354</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
@@ -4227,24 +4227,24 @@
       </c>
       <c r="I67" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. Bulk Receive only assigns a vendor (merge/keep-separate is Story 13, out of scope here). || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group offers select_assign_vendor_{poId} ('Assign a vendor to receive these parts') + input_part_number_{partId}. Assigning a vendor MOVED the PO out of the 'Vendor Missing' group into that vendor's group (order vendorMissing API flag -&gt; false) and the missing-PN indicator cleared; receive then follows the PN gate.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>C29357</t>
+          <t>C29355</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive all receives everything selected at once and supports partial receive</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -4274,24 +4274,24 @@
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: on a self-created deliverable WO PO (S-15786, 2 units) set received qty to 1 and received -&gt; order status partial_delivery, item already_received 1.00 of 2.00; remaining 1 stays waiting to receive. Receive-all mechanism present (button_receive_all).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>C29358</t>
+          <t>C29356</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -4321,34 +4321,34 @@
       </c>
       <c r="I69" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete + QuickBooks inspection. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (delivery leg): bulk receive ran POST /api/orders/receive-requested-parts -&gt; 200 (+ /api/inventory/orders/receive-view 200) and created a Delivery / Vendor Bill (invoice 'ZZAUTOTEST-APPLY-1', vendor Aabridge Beverages, visible on /parts/deliveries). MAJOR: BUG-11 (WO-PO receive HTTP 500 via the old /api/inventory/orders/accept path) does NOT reproduce on the bulk-receive pipeline — the WO-PO receive round-trip now works. QuickBooks sync leg not separately inspected (needs QB access).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>C29360</t>
+          <t>C29357</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply invoice to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify Receive All receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -4368,34 +4368,34 @@
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on Story 8). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: each vendor group has an apply-invoice control under the vendor name — input_apply_invoice_{vendorId} + apply date/tax + 'Apply to selected POs' with an 'N of M selected' counter. Enabled with an invoice # and &gt;=1 PO of that vendor selected.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>C29361</t>
+          <t>C29358</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -4415,24 +4415,24 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: entering an invoice # in input_apply_invoice_{vendorId} and clicking 'Apply to selected POs' pre-filled that number into the selected PO's own invoice field (input_invoice_{poId} = 'ZZAUTOTEST-APPLY-1'), which stays editable per PO.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). Bulk Receive uses the same pipeline (creates a Delivery + Vendor Bill via receive-requested-parts) - pipeline confirmed prior. FLAG: the QuickBooks-side vendor-bill/AP internals need a human logged into QuickBooks (no QB read API) - QB half not independently verified.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>C29362</t>
+          <t>C29360</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify each vendor group has an 'Apply to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G72" s="14" t="inlineStr">
@@ -4462,34 +4462,34 @@
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: Apply Invoice is scoped per vendor group (input_apply_invoice_{vendorId} exists only for real vendor groups); the 'Vendor Missing' (vendorless) group has NO apply-invoice control.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>C29363</t>
+          <t>C29361</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -4509,39 +4509,39 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED on the built Bulk Receive page (Story 8/10 inline PN-fix UI is shipped; the BATCH-6 'appears tied to Story 8, NOT built' note is SUPERSEDED). A no-number part shows 'Missing part number' (text visible); the inline input_part_number_{partId} Edit -&gt; enter PN -&gt; the 'Missing part number' text clears AND the PN persists immediately to the backend (order item.part_number=ZZPN-FIX01, PartRequest pn set) without a page reload.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>C29369</t>
+          <t>C29362</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -4556,34 +4556,34 @@
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
-          <t>PARTIAL: per-row Receive action verified on the PO list (17-po-detail.png). The PO detail-card Receive fix was not separately confirmed. Needs live verification of the detail card.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>C29370</t>
+          <t>C29363</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -4603,24 +4603,24 @@
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): drove /accept-delivery/{order} for the provided receivable PO 93fb82e9 (PO 'I2-1202', vendor Aabridge Beverages). The destination IS the shared Accept Delivery / Purchase Order Details surface (Invoice Number, Invoice Date, per-line Quantity Received, Tax, Delivery Note, Receive). Receive completed via POST /api/inventory/orders/accept -&gt; 201 and the PO left the ordered list. Evidence R6-01-accept-delivery.png, R6-03-after-receive.png.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>C29371</t>
+          <t>C29369</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-03</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -4650,39 +4650,39 @@
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negative not yet verified live. Fulfilled-PO hiding also needs live verification. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED (via Technician as a no-Order-Parts proxy; not the exact Office role). Tech redirected from /parts/orders; Receive not reachable (TECH-po-list.png). Fulfilled-PO hiding not separately re-driven.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>C29372</t>
+          <t>C29370</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-04</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G77" s="14" t="inlineStr">
@@ -4697,34 +4697,34 @@
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>Existing surface present at /parts/deliveries (13-vendor-invoices.png); reused not rebuilt. Not deep-driven — group fields not each asserted.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>C29377</t>
+          <t>C29371</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-RCV-03</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -4744,24 +4744,24 @@
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): on PO 93fb82e9 Accept Delivery, set the main line's Quantity Received to 15 (ordered = 10) -&gt; the row surfaced a 'Received More Than Ordered' warning. Existing behavior confirmed. Evidence R9-01-over-quantity.png.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>C29440</t>
+          <t>C29372</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-10</t>
+          <t>SF-RCV-04</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -4791,39 +4791,39 @@
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>NEW in V2.4 (S12-R5 editable-cost parity). VIU confirmed cost is editable in the receive tooling on $0 and $25 parts, but the WO-originated-PO receive round-trip is blocked by BUG-11 (HTTP 500), so the Accept-Delivery parity path is verify-pending. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive, which is the consolidated Accept Delivery for WO POs). Cost field editable when $0 (readonly=false, value '0' -&gt; edited to 9.99), quantity editable, sell field editable (WO not invoiced -&gt; sell-lock rule unchanged).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>C29378</t>
+          <t>C29377</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G80" s="14" t="inlineStr">
@@ -4838,39 +4838,39 @@
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the Vendor Missing group's vendor dropdown (select_assign_vendor_{poId}) assigns a vendor at PO level; after picking 'Aabridge Beverages' the order's vendorMissing flag went false (persisted to backend, GET /api/inventory/orders/{id}) and the PO moved into that vendor's group.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>C29383</t>
+          <t>C29440</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G81" s="14" t="inlineStr">
@@ -4885,39 +4885,39 @@
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT — 'Waiting on Parts' is absent from the WO-list column selector (16-wo-columns.png lists Asset, VIN/Serial#, Progress, Service Advisor, Lead Technician, Clocked In, Lines, Total price, Created on, Invoiced Date, Days open, Parts, Returns). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: the WO-list column selector (button_column_selection) offers a 'Waiting On Parts' column, OFF by default (toggle_column_unreceivedPartRequestsCount, aria-checked=false). It counts unreceived part requests (backing field unreceivedPartRequestsCount on GET /api/work-orders). Column renders when enabled. Resolves conflict (b): the shipped LABEL is 'Waiting On Parts' (NOT the Epic's 'Waiting on Receive') — our wording is correct.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>C29384</t>
+          <t>C29378</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -4932,24 +4932,24 @@
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT (depends on S14-R1). Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] Column + count BUILT (see SF-WOP-01) but the click-count-&gt;Accept Delivery navigation was NOT driven this pass — harness column-persistence flakiness + no non-zero cell surfaced in the sampled page. reachable-now: needs a stable WO row with a non-zero unreceived count.  || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. Enabled the 'Waiting On Parts' column (via storedColumns), clicked a WO's '2 Parts Waiting' count -&gt; navigated to the built receive surface /bulk-receive?ids=&lt;poId&gt; (Receive Vendor Parts) for that WO's unreceived PO. DEVIATION (wording only): the count opens the NEW consolidated Bulk Receive page, not the legacy 'Accept Delivery' named in the original expected; same end-state (receive the WO's first unreceived PO). Expected refined; TestRail push pending user approval.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>C29385</t>
+          <t>C29383</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -4959,12 +4959,12 @@
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
@@ -4979,39 +4979,39 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED: with the column enabled, WOs with nothing to receive show '—' with no clickable link (12/12 sampled rows).</t>
+          <t>Wording+VIU 2026-07-13: 'Waiting on Parts' column is off by default (toggle_column_unreceivedPartRequestsCount), enabled from the column selector - Story 14 built, verified prior runs (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon. FLAG: exact column-selector label not re-surfaced this run (width_normal control did not open the selector panel).</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>C29386</t>
+          <t>C29384</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-01</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Verify the Require Review setting drives the review flow when turned on</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -5026,39 +5026,39 @@
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — the settings toggle drives the flow (08-settings-workorders.png, S16-04-review-wizard.png).</t>
+          <t>Wording+VIU 2026-07-13: clicking the Waiting on Parts count opens the Bulk Receive page for the WO's first unreceived PO - verified prior (case 29384 pushed 2026-07-09/10).</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>C29387</t>
+          <t>C29385</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-02</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -5073,24 +5073,24 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 (S16-04-review-wizard.png).</t>
+          <t>Wording+VIU 2026-07-13: WO with nothing to receive shows '—' (no link) - verified prior (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>C29388</t>
+          <t>C29386</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-01</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -5120,24 +5120,24 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): with Require Review ON, completing routes into the review flow (Send To Review), not a direct complete.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>C29389</t>
+          <t>C29387</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-02</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -5167,24 +5167,24 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (supersedes BATCH-6 BUG-11 block). With requireReview=ON, the completion CTA = 'Send To Review' (wizard 'Complete &amp; Send to Review'); the receive step contains NO inline receive fields (0 qty/invoice inputs inside the dialog) and 'Receive Parts' routes to the shared receive page /bulk-receive (returnTo=WorkOrder), not an inline modal. Setting restored.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): ready-WO toolbar button = 'Send To Review' (confirmed); part-bearing WO shows 'Complete Work Order' -&gt; wizard. FLAG: the wizard's final review CTA wording ('Complete &amp; Send to Review' per prior notes) not cleanly reproduced this run.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>C29390</t>
+          <t>C29388</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-05</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -5214,24 +5214,24 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>Status→Review + 'Sent for review' verified 2026-07-06 (S16-05-after-send.png). Line-lock and auto-pick details (R6) not separately asserted.</t>
+          <t>Wording+VIU 2026-07-13: the completion Details modal shows Mileage + Engine Hours and no VIN field (confirmed live on the review-off modal S2-15827; review-on captures VIN in Mark Reviewed per SF-REV-06). Upgraded from Pending - the field set is now confirmed.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>C29391</t>
+          <t>C29389</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-06</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -5241,12 +5241,12 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -5261,24 +5261,24 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>[V2.4 Δ4 APPLIED 2026-07-13] Mark-Reviewed optional note removed (R7 = VIN-only) — this case is already note-free (VIN-only, Confirm-disabled-until-VIN), so no content change was needed; V2.4 2026-07-13 confirms the removal. FLAG (do not assert): spec R10 still lists the test id input_review_note even though R7 dropped the note field — an internal spec inconsistency to confirm on the live build during re-VIU (the note field itself is treated as removed). || Verified 2026-07-06 — dialog with VIN field, VIN pre-filled from asset, Confirm enabled (S16-06-mark-reviewed-dialog.png, S16-07-review-filled.png). Confirm-disabled-until-VIN inferred from VIN-required rule but not forced empty.</t>
+          <t>Wording+VIU 2026-07-13: 'Receive Parts' opens the shared receive page (not an inline modal) in the review flow — verified prior drive (FV-rev04-receivestep/afterreceive.png, 2026-07-10); review flow re-confirmed live this run.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>C29392</t>
+          <t>C29390</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-05</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -5308,24 +5308,24 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Not separately asserted in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): Send To Review -&gt; status 'Review' + 'Ready for Review' indicator; lines lock to Complete. (amber colour per design; status text 'Review' confirmed.)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>C29393</t>
+          <t>C29391</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-08</t>
+          <t>SF-REV-06</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
+          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -5350,29 +5350,29 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed action confirmed live (S2-15823). The VIN-required dialog surfaces only when the WO lacks a valid VIN; every test WO this run had a VIN (so Mark Reviewed completed directly - see SF-REV-08). VIN-required dialog verified prior run 2026-07-06 (S16-04-review-wizard.png). Stripped dev test-id 'input_review_vin' from tester wording.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>C29394</t>
+          <t>C29392</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-09</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -5402,24 +5402,24 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): on Send To Review the lines lock to Complete and inventory is auto-picked (design; review state confirmed live).</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>C29395</t>
+          <t>C29393</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-10</t>
+          <t>SF-REV-08</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
+          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G93" s="14" t="inlineStr">
@@ -5444,29 +5444,29 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>[V2.4 Δ4 CONFIRMED 2026-07-13] The V2.4 2026-07-13 spec (R7 = VIN-only, no note) confirms the note removal already applied here in the Milos Round-2 pass — expected is already VIN-only with no review note field, so no content change was needed. FLAG (do not assert): spec R10 still lists the test id input_review_note even though R7 dropped the note field — internal spec inconsistency to confirm on the live build during re-VIU. || [MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): Mark Reviewed (VIN present) signs off and moves the WO directly Review -&gt; Complete; no distinct 'Reviewed' holding state and no separate final Complete click (S2-15823 went Review-&gt;Complete).</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>C29397</t>
+          <t>C29394</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-REV-09</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -5496,24 +5496,24 @@
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>A per-WO 'Ready for Review' indicator was seen (S16-05), but the list-level queue filter/column is flagged pending in the design handoff and was not verified. Needs dev complete / live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. WO list 'By Status' tab exposes a status multiselect whose options include 'Review'; selecting it filters the list to review-status work orders (surfaced the reviewer queue). A dedicated Ready-for-Review filter exists via the By Status -&gt; Review filter.</t>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed gated by Review Work Orders (woReviewWorkOrders) per fresh roles matrix (roles-matrix-2026-07-13.md); role without it sees Mark Reviewed disabled + 'Awaiting review'; self-review allowed when the role holds the permission (Milos ruling). Review flow re-confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>C29398</t>
+          <t>C29395</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-REV-10</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -5538,39 +5538,39 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (line-approval gate was PARTIAL). Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed uses VIN / Serial # only, no review note field (V2.4 Δ4 confirmed; SF-REV-06/10 were already note-free). Dialog surfaces when VIN missing (verified prior 2026-07-06); Mark Reviewed action re-confirmed live this run.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>C29401</t>
+          <t>C29397</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-01</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>Verify the work order primary button reads 'Create Work Order'</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
@@ -5590,34 +5590,34 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Create flow verified during Story 2 setup (S2-01-create-form.png).</t>
+          <t>Wording+VIU 2026-07-13: 'Ready for Review' indicator confirmed on a WO in Review (S2-15823). Reviewer-queue surfacing on the WO list per design; the 'Ready for Review' label is build-accurate.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>C29402</t>
+          <t>C29398</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-02</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -5637,24 +5637,24 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Centralized Details modal verified (S2-13-details.png); tech story ran as its own gate before the wizard (S2-11-techstory.png).</t>
+          <t>Wording+VIU 2026-07-13: Send To Review is blocked by the existing 'approve the line' error while any line is unapproved (existing approve-line gate; consistent with SF-COMP-21/22 non-required-invoice behaviour). Review flow confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>C29403</t>
+          <t>C29401</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-03</t>
+          <t>SF-UX-01</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
+          <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
@@ -5684,39 +5684,39 @@
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Success screen verified (S2-14-success.png). Finance-step invoice-number location not separately driven.</t>
+          <t>Wording+VIU 2026-07-13 (UX-workorders-list.png): the Work Orders create form's primary button reads 'Create Work Order' (confirmed on /workorders list Create Work Order button).</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>C29405</t>
+          <t>C29402</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-01</t>
+          <t>SF-UX-02</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
+          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
@@ -5731,34 +5731,34 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>Permission defined by SV-8183: the Work Order settings inherit the existing settingsApp route guard (no new atom); editable by any role with App Settings ON (defaults Admin, Service Manager, Office). Note Office can edit settings but cannot operate the flow. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): CONFIRMED (FE+BE). Tech (Technician, no settingsApp) redirected from /administration/settings to /workorders (FE route guard, TECH-settings.png). BE POST /api/organizations/settings/change -&gt; 403 'Access denied' for tech; admin -&gt; 200. Settings atom is fully enforced both FE and BE.</t>
+          <t>Wording+VIU 2026-07-13: required fields collected in the centralized 'Complete Work Order' modal (Mileage + Engine Hours; no VIN field in the modal - see SF-COMP-16/SF-VAL-02 build finding); tech story handled separately.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>C29406</t>
+          <t>C29403</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-02</t>
+          <t>SF-UX-03</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
+          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -5778,24 +5778,24 @@
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
+          <t>Wording+VIU 2026-07-13: success screen shows WO number + total with 'Done' and 'Go To Invoice'; invoice number appears on the Finance step (confirmed live via SF-COMP drives S2-15825 'Invoice total $434.95').</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>C29407</t>
+          <t>C29405</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-PERM-01</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
@@ -5825,24 +5825,24 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix (Bulk Receive = Vendor &amp; Order Mgmt C&amp;E + See Financial Data; Office is view-only). Bulk Receive is also not yet built. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Bulk Receive depends on Stories 7/8 (PO multi-select + Bulk Receive page) which are NOT BUILT; also tech is redirected from /parts routes. Role matrix for Bulk Receive not drivable until the page ships. || [RE-VIU 2026-07-09 sv7301 — Stories 7/8/9/14 CONFIRMED BUILT] BUILT &amp; VERIFIED (gating): the Bulk Receive page (/bulk-receive) and /parts/orders both REDIRECT a no-Order-Parts role (Technician) to /workorders — Bulk Receive is FE-gated by the Order Parts / Vendor &amp; Order Mgmt permission. Full per-role matrix derives from the live-verified SF-PERM-10 fe_permissions sweep (woOrderParts). NOTE: the finer 'Office view-only can open-but-not-receive' nuance was not separately driven (needs a live Office role-swap).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Settings gate re-driven live: Technician POST /api/organizations/settings/change = 403, Admin = 200 (App Settings / settingsApp atom, BE-enforced). FE redirects non-admin from the settings route.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>C29408</t>
+          <t>C29406</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -5872,24 +5872,24 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Complete-WO gate = workOrdersCreateAndEdit; roles that can complete (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager) vs cannot (Technician, Parts Tech, Office, Sales Rep, Time Clock) match the matrix. FE confirmed (Complete Work Order button hidden for Technician, prior TECH-wo-detail.png); BE does not enforce WO completion (documented gap, see SF-PERM-06).</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>C29409</t>
+          <t>C29407</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
@@ -5919,24 +5919,24 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 resolves 'office/readonly' to concrete atoms: Receive-on-WO is FE-gated by Order Parts; Office (WO View-only / Vendor &amp; Order View-only) lacks it. Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED. Technician (no woOrderParts) redirected from /parts/orders to /workorders; no Receive action reachable (TECH-po-list.png). BE receive endpoint not driven this pass (part+PO setup), but per SF-PERM-06 the WO-atom collapse implies BE would allow it.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Bulk Receive gate = vendorOrderManagementCreateAndEdit + seeFinancialData; per-role result (Admin/SM/SrSA/SA/Foreman/Parts Manager/Parts Tech can; Office view-only; Sales Rep &amp; Time Clock cannot) matches the matrix. Stories 7/8 confirmed BUILT.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>C29410</t>
+          <t>C29408</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
@@ -5966,24 +5966,24 @@
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Mark Reviewed gate = woReviewWorkOrders (not open-to-all). Self-review allowed when the role holds the permission (Milos ruling 2026-07-10; no reviewer!=completer identity block). Per-role has/lacks matches the matrix.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>C29411</t>
+          <t>C29409</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-07</t>
+          <t>SF-PERM-05</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G105" s="14" t="inlineStr">
@@ -6013,24 +6013,24 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). PO Receive gate = woOrderParts (Order Parts); Office lacks it -&gt; no Receive on PO list/detail. FE confirmed (Technician redirected from /parts/orders, prior TECH-po-list.png).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>C29412</t>
+          <t>C29410</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-08</t>
+          <t>SF-PERM-06</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6040,12 +6040,12 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -6060,24 +6060,24 @@
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>[RE-PURPOSED 2026-07-10] Milos ruling (relayed by QA lead): self-review IS acceptable — a user MAY Mark Reviewed a work order they completed, PROVIDED their role holds the Mark Reviewed permission (permission-gated only, NO identity restriction). This case flipped from the obsolete negative (was: completer cannot Mark Reviewed) into the POSITIVE case above. | VIU EVIDENCE: the self-review-by-a-permissioned-role positive WAS directly observed — the SAME admin (who holds Review Work Orders) who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). The permission-gating half (a role WITHOUT the permission cannot) was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2; FE hides the control for non-reviewers). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). =&gt; VIU-Verified: self-review allowed for permissioned role per Milos ruling 2026-07-10; permission-gating verified. Origin defect BUG-5 / TICKET 1 dropped as expected behavior.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Live: BE enforces the distinct settings atom (Technician settings save -&gt; 403, Admin -&gt; 200) but does NOT enforce the WO-completion / review atoms (documented 'app blocks / backend allows' gap, draft TICKET 2). v1 pass = app-level restriction (Milos Round-2 ruling). Cleaned tester wording: removed backend enum names and internal 'UI pass/API fail' phrasing.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>C29413</t>
+          <t>C29411</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-PERM-07</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
@@ -6107,24 +6107,24 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>SV-8183 Decision 4: adding a vendorless part requires See Financial Data (sell is mandatory, no catalog source). Role-gating negative not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): Not driven this pass: the vendorless part-add sits in a line Parts sub-form not reached within budget. Tech CONFIRMED to lack seeFinancialData (role capture). BE financial-gate on add-part remains untested. | 2026-07-08: tech confirmed lacks seeFinancialData (roles-capture). The vendorless part-add sub-form could not be reached even as admin this pass (see SF-VPART-01), so the FE See-Financial-Data gate on the add sub-form is still unverified. Note: given the app's pattern (mileage/VIN/completion gates are FE-only, BE non-enforcing), this gate is likely FE-only too. Still needs a driven add-part sub-form + a non-SFD role. || VIU batch3 2026-07-08 VERIFIED (FE gate): as Technician (non-SFD) the New Part Request form HIDES all financial fields (Sell Price, Cost, Core Charge, Margin, Vendor, Category) — tech sees only Part Number, Description, Quantity, so cannot supply the mandatory sell price for a vendorless part (PERM09-tech-partform.png). FE-only gate (consistent with BUG-6/7/8).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Review sign-off = Review Work Orders (woReviewWorkOrders), custom-role gated, not open-to-all for v1. Self-review allowed when the role holds the permission (Milos ruling 2026-07-10).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>C29414</t>
+          <t>C29412</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-PERM-08</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
@@ -6154,34 +6154,34 @@
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — FULL LIVE 11-ROLE SWEEP (all system roles are REAL/assignable; the prior 'only 3 instantiated' assumption was WRONG). Assigned the Tech user each of the 11 roles in turn via POST /api/staff/{id}/change, quick-login'd tech, and read /api/auth/me/fe-permissions. Complete-WO gate = workOrdersCreateAndEdit. LIVE RESULT matches §9.2 EXACTLY: HAS complete (workOrdersCreateAndEdit=true) -&gt; Admin, Service Manager, Senior Service Advisor, Service Advisor, Foreman, Parts Manager; NO complete -&gt; Technician (view=tech), Parts Tech, Office, Sales Representative, Time Clock. Mark-Reviewed gate (woReviewWorkOrders) and Settings gate (settingsApp) and Pick/Order gates also matched §9.2 for all 11. Tech restored to Technician + verified. Evidence /tmp/simple-flow/role-matrix-6.json. (Completion gate is FE-only at BE per BUG-6/atom-collapse — matrix realised as FE button visibility.)</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Positive self-review: a role holding woReviewWorkOrders may Mark Reviewed a WO it completed (permission-gated only, no identity block). A role lacking it cannot. Matches matrix + Milos ruling.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>C29415</t>
+          <t>C29413</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
@@ -6201,39 +6201,39 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Technician lacks seeFinancialData (confirmed live: Tech 6 perms, no seeFinancialData) so cannot add a vendorless / no-part-number part (sell price mandatory, gated by See Financial Data). FE gate holds; BE financial-gate on part-add not re-driven this session.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>C29417</t>
+          <t>C29414</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G110" s="14" t="inlineStr">
@@ -6248,24 +6248,24 @@
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Per-role completion matrix (Complete gate = workOrdersCreateAndEdit) matches roles-matrix-2026-07-13.md exactly: HAS = Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager; LACKS = Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>C29418</t>
+          <t>C29415</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-04</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G111" s="14" t="inlineStr">
@@ -6295,24 +6295,24 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>Verified 2026-07-06 — Continue disabled until non-empty (S2-11-techstory.png).</t>
+          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Mileage ON): the completion Details modal shows a Mileage field; leaving it empty and pressing 'Complete Work Order' shows a 'required field' error and completion does not proceed. Settings restored byte-identical.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>C29419</t>
+          <t>C29417</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
@@ -6322,12 +6322,12 @@
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
@@ -6342,24 +6342,24 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
+          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Engine Hours ON): the completion Details modal shows an Engine Hours field; empty -&gt; 'required field' error, completion blocked. Same modal as SF-VAL-01 (Mileage + Engine Hours).</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>C29421</t>
+          <t>C29418</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-VAL-04</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
@@ -6389,24 +6389,24 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>In VIU the VIN was pre-filled from the asset, so the empty-VIN disabled state was not forced. Needs a WO with no VIN to verify.</t>
+          <t>Wording+VIU 2026-07-13: tech-story modal Next/Continue disabled while the story textarea is empty (Require Tech Story gate) - behavior per prior VIU; tech-story requirement is a Work Orders setting toggle (see SF-SET-15).</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>C29422</t>
+          <t>C29419</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G114" s="14" t="inlineStr">
@@ -6436,54 +6436,148 @@
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. (Also covered from the flow side in SF-COMP-23.)</t>
+          <t>Wording+VIU 2026-07-13: required-invoice receive blocked without a vendor invoice number - verified prior drive (FV-val05-noinvoice/withinvoice.png, 2026-07-10). Require Vendor Invoice Number gate.</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
         <is>
+          <t>C29421</t>
+        </is>
+      </c>
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-07</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="inlineStr">
+        <is>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+        </is>
+      </c>
+      <c r="F115" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G115" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H115" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: Confirm Review disabled until VIN entered in the Mark Reviewed dialog (surfaces when the WO lacks a valid VIN) - same gate as SF-REV-06; Mark Reviewed action confirmed live this run, VIN-required dialog per prior 2026-07-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>C29422</t>
+        </is>
+      </c>
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-08</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="inlineStr">
+        <is>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+        </is>
+      </c>
+      <c r="F116" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G116" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H116" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I116" s="12" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: re-completing after cancel creates no duplicate POs (idempotent) - verified prior (2026-07-08); consistent with SF-COMP-15/23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
           <t>C29424</t>
         </is>
       </c>
-      <c r="B115" s="13" t="inlineStr">
+      <c r="B117" s="13" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
         </is>
       </c>
-      <c r="C115" s="12" t="inlineStr">
+      <c r="C117" s="12" t="inlineStr">
         <is>
           <t>SF-VAL-10</t>
         </is>
       </c>
-      <c r="D115" s="12" t="inlineStr">
+      <c r="D117" s="12" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="E115" s="12" t="inlineStr">
+      <c r="E117" s="12" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="F115" s="12" t="inlineStr">
+      <c r="F117" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G115" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H115" s="12" t="inlineStr">
+      <c r="G117" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr">
         <is>
           <t>READY (VIU-Verified)</t>
         </is>
       </c>
-      <c r="I115" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED. On the Bulk Receive page with two POs (S-15788, S-15789), applied the SAME vendor invoice number 'ZZAUTOTEST-VAL10' to both via the vendor group 'Apply to selected POs'; both PO invoice fields carried the reused number and Receive All ran POST /api/orders/receive-requested-parts -&gt; 200 for both. Reused invoice number accepted (uniqueness relaxed); both received.</t>
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: the same vendor invoice number can be reused across POs (uniqueness relaxed) - verified prior (2026-07-10, Story 9 apply-invoice).</t>
         </is>
       </c>
     </row>
@@ -6603,6 +6697,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B113" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B114" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6614,7 +6710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6678,17 +6774,17 @@
     <row r="2">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>C29282</t>
+          <t>C29284</t>
         </is>
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29282</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29284</t>
         </is>
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>SF-SET-08</t>
+          <t>SF-SET-10</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
@@ -6698,12 +6794,12 @@
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>Verify first-use defaults on a brand-new org (auto-approve OFF, create POs ON, vendor invoice REQUIRED)</t>
+          <t>Verify a settings change applies to future completions only and not to already-completed work orders</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G2" s="15" t="inlineStr">
@@ -6713,44 +6809,44 @@
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q3, Q4 — First-use defaults: spec (Auto-approve OFF / invoice REQUIRED) vs design (ON / Optional).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: toggle the setting and confirm the downstream behaviour.</t>
         </is>
       </c>
       <c r="I2" s="12" t="inlineStr">
         <is>
-          <t>CONFLICT: spec defaults (Auto-approve OFF, invoice REQUIRED) vs design HANDOFF.md defaults (Auto-approve ON, invoice Optional). Current org baseline shows autoApproveLines:true, requireVendorInvoiceNumber:false. Also 'Create Purchase Orders' toggle is absent (bug #1). Confirm the authoritative first-use defaults before pass/fail. See Open Questions. || [RECONCILED 2026-07-08] Milos Q3: spec defaults confirmed AUTHORITATIVE (Auto-approve OFF / Create POs ON / Vendor Invoice REQUIRED) — 'per spec' hedge dropped. Live first-use defaults show Auto-approve ON / Vendor Invoice Optional = spec-vs-build gap (wrong first-use defaults; build lags spec).</t>
+          <t>VIU-Pending: verifying that a settings change affects only future completions needs one WO completed under the old setting and a second completed after the change, back-to-back. Not driven this run (avoids extra settings churn on the shared env while a tester may be active). Standard forward-only settings behavior; needs a live two-completion drive to confirm.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>C29287</t>
+          <t>C29310</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29287</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>SF-SET-13</t>
+          <t>SF-COMP-21</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>Completion — Line approval gate</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Verify the Save Settings button is only enabled when there is an unsaved change</t>
+          <t>Verify on a required-invoice work order an unapproved line disables the Complete Work Order button with a tooltip</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr">
@@ -6760,44 +6856,44 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q6 — Save Settings always enabled (no dirty-state gating) — intended or bug?</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #2: Save Settings is always enabled (no dirty-state gating) — S1-01-settings-baseline.png. Confirm intended behavior; do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q6: dirty-state gating not required in v1; BUG-2 downgraded to nice-to-have (Save-always-enabled acceptable).</t>
+          <t>V2.4 Δ2 wording applied (required-invoice-only disabled Complete button + tooltip; other flows keep the active-CTA + error-message model). VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines OFF, and a WO with a Needs-Approval line; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>C29314</t>
+          <t>C29311</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-COMP-22</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Completion — Line approval gate</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
+          <t>Verify a manually unapproved line disables the required-invoice Complete Work Order button with a tooltip even when Auto-approve is ON</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G4" s="15" t="inlineStr">
@@ -6807,12 +6903,12 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
+          <t>V2.4 Δ2 wording applied. VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines ON, and a line manually un-approved after add; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6955,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Verifies special-order cores leave optional-invoice completion unchanged + Complete Without Receiving stays available.</t>
         </is>
       </c>
     </row>
@@ -6906,7 +7002,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Also needs invoicing to see the 'Cores pending' invoice flag (invoicing not drivable in-harness).</t>
         </is>
       </c>
     </row>
@@ -6953,7 +7049,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Also needs the Create Invoice gate (invoicing not drivable in-harness).</t>
         </is>
       </c>
     </row>
@@ -7000,7 +7096,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Cancel-at-invoice-gate path needs invoicing (not drivable in-harness).</t>
         </is>
       </c>
     </row>
@@ -7047,7 +7143,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs the required-invoice receive round-trip with a special-order core.</t>
         </is>
       </c>
     </row>
@@ -7094,7 +7190,7 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs an unresolved special-order core existing only as a PartRequest + the invoice gate.</t>
         </is>
       </c>
     </row>
@@ -7141,24 +7237,24 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs a part-sale WO and a service WO each with a core to compare auto-resolve vs manual Ok/Not OK.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>C29340</t>
+          <t>C29343</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29340</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-03</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -7168,12 +7264,12 @@
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO is flagged and excluded from QuickBooks sync</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -7188,39 +7284,39 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks state not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. verifying reports mark Vendor-Missing POs as 'needs vendor' needs a vendor-missing PO + the reports surface; not driven this session (needs seeded vendor-missing PO).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>C29343</t>
+          <t>C29359</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -7230,44 +7326,44 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: needs a genuine cored part on a PO to verify the Ok/Not OK resolution after receive + core-only partial receive. A genuine special-order (vendor-source) core is not seedable in-app (see SF-CORE cluster). Bulk Receive surface confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>C29359</t>
+          <t>C29364</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -7277,29 +7373,29 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
         </is>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>NOT BUILT. Needs dev complete. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a GENUINE special-order (vendor-source) cored part received on the Bulk Receive page to expose the Ok/Not-OK resolution. Confirmed again this pass: the only seedable core (catalog P550848) forces Source=Inventory (auto-picked, never routed through a receivable PO), and the manual part sub-form's Core Charge yields is_core=false. A vendor-source is_core part is not seedable in-app.</t>
+          <t>Wording+VIU 2026-07-13: entering a NEW part number should create inventory/catalog stock + Part History on receive - blocked by OBS-6 (Part-History surface GET /api/inventory/parts/history returns 500; part-detail page crashes) + needs a vendor-missing/no-PN part to receive.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>C29364</t>
+          <t>C29365</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -7309,7 +7405,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -7329,24 +7425,24 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED. Received a WO-PO vendor part carrying a NEW free-text part number (ZZPN-FIX01) via /bulk-receive (POST /api/orders/receive-requested-parts 200). NO new inventory part was created (GET /api/inventory/parts?search=ZZPN-FIX01 = 0 before AND after) — consistent with vendor-source parts being direct-to-WO consumption, not inventory-tracked (cf. SF-VPART-05); /api/catalogue/parts search 404. Whether a new PN should create a catalog/inventory item + Part History on receive needs the inventory-integrity/Part-History surface, which is BLOCKED-ENV (OBS-6). Applies equally to SF-PNFIX-03/06.</t>
+          <t>Wording+VIU 2026-07-13: entering an EXISTING part number should link + update stock/cost/history without overwriting description/category - blocked by OBS-6 (Part-History 500) + needs a no-PN part to receive.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>C29365</t>
+          <t>C29366</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -7356,12 +7452,12 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G16" s="15" t="inlineStr">
@@ -7376,24 +7472,24 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: inline part-number field-locking (sell locks after invoiced/paid) - needs an invoiced/paid WO (not drivable in-harness).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>C29366</t>
+          <t>C29367</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -7403,12 +7499,12 @@
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
@@ -7423,7 +7519,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
+          <t>V2.4 Δ3 wording applied. VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08). The invoiced/paid overlay also needs an invoiced WO (not drivable in-harness).</t>
         </is>
       </c>
     </row>
@@ -7470,7 +7566,7 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
+          <t>Wording+VIU 2026-07-13: inline part-number save should drive real catalog creation/linking + inventory + Part History - blocked by OBS-6 (Part-History 500).</t>
         </is>
       </c>
     </row>
@@ -7517,24 +7613,24 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] Milos Q11: vendor-missing group LEADS (top), not bottom — title/step/expected corrected.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>C29375</t>
+          <t>C29374</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -7544,12 +7640,12 @@
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G20" s="15" t="inlineStr">
@@ -7559,29 +7655,29 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>S12-R1 says vendor-missing at the bottom; S12-R3 says vendor-missing leads — spec inconsistency worth confirming. Not driven in VIU.</t>
+          <t>V2.4 Δ3 wording applied (S13-R6 part# + S13-R7 cost/sell receive gates). VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>C29376</t>
+          <t>C29375</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29376</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-08</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -7591,12 +7687,12 @@
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group produces its own vendor bill and separate AP entry in QuickBooks</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -7606,12 +7702,12 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: '+N' vendor indicator + vendor-missing group at top. VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7754,7 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs a same-vendor collision on ONE PO (a per-part vendor assignment matching the PO's existing vendor) to trigger the 'Add to {vendor}?' Merge vs Keep-Separate prompt. Vendor assignment on the Bulk Receive Vendor-Missing group is PO-level (verified SF-VEND-04: assigning a NON-colliding vendor auto-assigns with no prompt); the collision prompt state was not reachable with a single-vendor vendor-missing PO.</t>
+          <t>Wording+VIU 2026-07-13: needs a same-vendor-already-on-PO collision to surface the 'Add to {vendor}?' Merge vs Keep Separate prompt - not seedable without the vendor-missing collision state. Bulk Receive vendor group confirmed live.</t>
         </is>
       </c>
     </row>
@@ -7705,24 +7801,24 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Merge scope is same work order. Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs TWO POs on the SAME work order sharing a vendor to trigger the merge-POs prompt. A WO's vendorless parts collapse onto ONE shared PO (SF-VMIS-01), so producing two same-WO POs for the same vendor needs targeted multi-vendor seeding not achieved this pass.</t>
+          <t>Wording+VIU 2026-07-13: needs two POs for the same WO with a shared vendor to surface the merge-POs prompt - merge-collision state not seedable in-harness.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29382</t>
+          <t>C29381</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -7732,7 +7828,7 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -7752,39 +7848,39 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification (likely partly backend). || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - the 'receiving blocked when WO invoiced/paid' guardrail depends on the invoiced/paid WO state (same blocker as SF-VAL-09: invoicing not drivable in-harness). Match-by-ID + merge-scoped-to-WO also need the multi-PO merge collision state (SF-VEND-02/03).</t>
+          <t>V2.4 Δ3 wording applied (receive enables only with part# + cost/sell). VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29396</t>
+          <t>C29382</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -7794,44 +7890,44 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
+          <t>Wording+VIU 2026-07-13: vendor matched by ID (not name) + merge scoped to same WO + receiving blocked when WO invoiced/paid - the invoiced/paid block needs an invoiced/paid WO (not drivable in-harness).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29399</t>
+          <t>C29442</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29442</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-VEND-06</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -7841,44 +7937,44 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>V2.4 Δ3 NEW case (S13-R7 cost/sell receive gate). VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29404</t>
+          <t>C29396</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-04</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -7888,39 +7984,39 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>S15-R4 close-confirm design is explicitly pending ('Figma still to be added') — no design surface to test yet. Confirm before authoring expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q10 (S15-R4): behavior defined — Close = modal-only / no discard; Cancel = returns to previous screen. Un-blocked (was pending design).</t>
+          <t>Direct Review-&gt;Complete confirmed live (S2-15823, no separate final Complete). VIU-Pending on the invoicing-block half: verifying invoicing is blocked until the WO is reviewed needs an invoicing drive on a pre-sign-off WO (invoicing not driven in-harness). Not driven this session.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29423</t>
+          <t>C29399</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-09</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -7935,44 +8031,44 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FOLLOW-UP VIU 2026-07-09] STILL PENDING - needs an invoiced/paid WO carrying an unreceived part. Seeded WO5 (S-15792) complete with an unreceived vendor PO, but invoicing is not drivable here: API POST /api/work-orders/change-status {status:'invoiced'} -&gt; 400 'Work order status cannot be changed manually to invoiced'; the finance-page button_create_invoice (UI) did not fire in headless (needs the invoice builder / IBS-approval flow). Needs a proper invoiced-WO state to observe the sell-field lock icon + tooltip on the receive surface.</t>
+          <t>VIU-Pending (non-seedable): needs a WO with genuine inventory + special-order cores to verify core resolution before sign-off and the invoicing block until Reviewed AND cores resolved. A genuine special-order (vendor-source) core is not seedable in-app (see SF-CORE cluster). Review flow confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29426</t>
+          <t>C29404</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-01</t>
+          <t>SF-UX-04</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
@@ -7982,44 +8078,44 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
         </is>
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>§8 open question: auto-receive of in-stock inventory on simple completion is unconfirmed, and the spec flags the bare status setter as an integrity risk. Not driven in VIU. See Open Questions. || [RECONCILED V2.4 2026-07-08] Un-held: No-PO path RETAINED (V2.4). || [MILOS ROUND-2 2026-07-09 — Q3 CONFIRMED] Milos confirmed the invariant: in-stock inventory parts DO decrement on-hand and write Part History on completion (his PO note is separate from this data-integrity invariant). Expected already correct — no wording change. Still VIU-Pending on a live decrement drive. || [FRESH VIU 2026-07-10 sv7301] PARTIAL: decrement half PROVEN (P550848 on-hand 6-&gt;5 on pick, persisted 5 through simple-complete 201, WO 1490338a; skip-path did NOT bypass inventory movement). Part-History LOG surface BLOCKED-ENV (not fake-able): GET /api/inventory/parts/history -&gt; 500 (requestId 8d752c7...); /parts/inventory/{id} detail route CRASHES ('this page is totaled'); /api/inventory/parts/{id}/history + /api/reports/part-history -&gt; 404; POST .../history -&gt; 405. QuickBooks-integrity leg still needs QB access. Stays VIU-Pending on the Part-History/QB display surface (OBS-6 flags the 500/crash as a possible env/build defect).</t>
+          <t>VIU-Pending: the close-confirmation dialog (Close = closes modal only; Cancel text-link = closes + returns) needs a completion modal with a discardable in-progress state to trigger it; the labor-only WOs available complete directly without that state. Wording kept build-accurate; needs a part-bearing in-progress completion to drive.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>C29428</t>
+          <t>C29416</t>
         </is>
       </c>
       <c r="B30" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29428</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-03</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E30" s="12" t="inlineStr">
         <is>
-          <t>Verify POs ON plus receiving runs the full pipeline: receive → Delivery → Vendor Bill → QuickBooks (both surfaces sync)</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
@@ -8029,44 +8125,44 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Bulk Receive surface not yet built. Needs live verification.</t>
+          <t>BUILD FINDING (live 2026-07-13): the completion modal has NO VIN field (only Mileage + Engine Hours), even with Require Review off — broader than V2.4 Δ1. VIN validity surfaces via the 'Valid VIN Required' header chip. VIU-Pending on the hard-block half: confirming a VIN-less WO cannot complete needs a VIN-less asset, which is not seedable (POST /api/vehicles 405). Expected reworded to the observed build behavior + flagged.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>C29429</t>
+          <t>C29420</t>
         </is>
       </c>
       <c r="B31" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-04</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E31" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
@@ -8076,39 +8172,39 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>V2.4 Δ3 wording applied (new S13-R6 part# + S13-R7 cost/sell receive gates). VIU-Pending: verifying the three receive-time gates needs a vendor-missing part on the Bulk Receive / vendor-missing surface; to be driven in the SF-VEND / SF-RCV receive-cluster pass (seed a vendor-missing PO). Not driven in this SF-VAL slice.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>C29430</t>
+          <t>C29423</t>
         </is>
       </c>
       <c r="B32" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29430</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29423</t>
         </is>
       </c>
       <c r="C32" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-05</t>
+          <t>SF-VAL-09</t>
         </is>
       </c>
       <c r="D32" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E32" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are excluded from QuickBooks until a vendor and part number are provided</t>
+          <t>Verify the sell field is locked after the work order is invoiced/paid with a lock icon and tooltip</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -8123,39 +8219,39 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>VIU-Pending (non-drivable state): the sell-locked-after-invoiced/paid behavior (lock icon + 'Locked - this part is already invoiced or paid' tooltip) needs an invoiced/paid work order; invoicing/payment is not drivable in-harness on this env. Wording kept build-accurate for the lock icon + tooltip.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29431</t>
+          <t>C29425</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29431</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-06</t>
+          <t>SF-VAL-11</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>QuickBooks / Inventory Integrity</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify cost at completion behavior to avoid $0-cost margins in QuickBooks</t>
+          <t>Verify an unapproved line blocks completion — required-invoice shows a disabled Complete button with a tooltip; other flows show the approve-line error</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -8170,29 +8266,29 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Resolved by SV-8183 (Decision 4): the cost-at-completion concern is addressed by requiring See Financial Data to enter the mandatory sell on a vendorless add. Money figures still need live verification.</t>
+          <t>V2.4 Δ2 wording applied; story-ref jargon stripped. VIU-Pending (could not seed the state): no work order currently has a line in Needs Approval (Auto-approve Lines has been ON historically) and seeding one requires completing the multi-field New Line form in headless (Save &amp; Add Line/Save &amp; Close), which was too flaky to drive reliably this session. Needs a WO with a Needs-Approval line + Require Vendor Invoice Number ON. Same blocker as SF-COMP-21/22.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29432</t>
+          <t>C29426</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29432</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29426</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-QB-07</t>
+          <t>SF-QB-01</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
@@ -8202,12 +8298,12 @@
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify the Journal Entry / Inventory sync to QuickBooks fires on invoice creation (not PO-dependent)</t>
+          <t>Verify in-stock parts decrement inventory and write Part History on simple completion (skip path still runs lifecycle)</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -8222,54 +8318,101 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: the inventory-decrement half is verified (SF-COMP-07, live 2026-07-10). The Part History half is blocked by OBS-6 (GET /api/inventory/parts/history returns 500; part-detail page crashes) - VIU-Pending until the Part-History surface is fixed.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
+          <t>C29429</t>
+        </is>
+      </c>
+      <c r="B35" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29429</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>SF-QB-04</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>QuickBooks / Inventory Integrity</t>
+        </is>
+      </c>
+      <c r="E35" s="12" t="inlineStr">
+        <is>
+          <t>Verify a vendorless / no-PN part has zero inventory interaction until a vendor and/or part number is added</t>
+        </is>
+      </c>
+      <c r="F35" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
+        </is>
+      </c>
+      <c r="I35" s="12" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: a vendorless / no-PN part having zero inventory interaction until a vendor/PN is added is partly observable, but confirming 'no item, no history' is blocked by OBS-6 (Part-History surface 500). VIU-Pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
           <t>C29433</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B36" s="13" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29433</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C36" s="12" t="inlineStr">
         <is>
           <t>SF-QB-08</t>
         </is>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E36" s="12" t="inlineStr">
         <is>
           <t>Verify Inventory Part History is preserved for any part that becomes inventory-tracked</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F36" s="12" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G35" s="15" t="inlineStr">
+      <c r="G36" s="15" t="inlineStr">
         <is>
           <t>VIU-Pending</t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="H36" s="12" t="inlineStr">
         <is>
           <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr">
-        <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+      <c r="I36" s="12" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: Part History preservation for an inventory-tracked part is blocked by OBS-6 (Part-History surface GET /api/inventory/parts/history returns 500). VIU-Pending.</t>
         </is>
       </c>
     </row>
@@ -8309,6 +8452,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8320,7 +8464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8388,34 +8532,26 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>C29277</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29277</t>
-        </is>
-      </c>
+      <c r="A2" s="12" t="inlineStr"/>
+      <c r="B2" s="12" t="inlineStr"/>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>SF-SET-03</t>
+          <t>SF-QB-09</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>Work Order Settings</t>
+          <t>QuickBooks / Inventory Integrity</t>
         </is>
       </c>
       <c r="E2" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Create Purchase Orders' toggle exists and, when off, hides the Vendor Invoice sub-setting</t>
+          <t>Investigate: Part Sales unaffected by the shared order/status logic (requested -&gt; orderable/waiting-to-receive)</t>
         </is>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G2" s="16" t="inlineStr">
@@ -8425,227 +8561,21 @@
       </c>
       <c r="H2" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q5 — 'Create purchase orders' toggle absent / POs always-on — descope or bug?</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="I2" s="12" t="inlineStr">
         <is>
-          <t>Milos answers Open Question Q5 — 'Create purchase orders' toggle absent / POs always-on — descope or bug?</t>
+          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
         </is>
       </c>
       <c r="J2" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #1: no 'Create purchase orders' toggle in the UI and no createPurchaseOrders field in GET /api/organizations/settings (08-settings-workorders.png). POs appear always-on. Expected above is spec-authored; do NOT record as passing. See Open Questions tab. || [RECONCILED V2.4 2026-07-08 — last-update-wins] Rewrite to 'POs always on' CANCELLED. V2.4 S1-R2 + §4 RETAIN the Create-POs toggle (default On) and the No-PO path, overriding the round-1 answer. BUG-1 (toggle absent live) = spec-vs-build gap, build lags V2.4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>C29295</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29295</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>SF-COMP-06</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Completion — No-PO / Skip (Story 2)</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>Verify with Create POs OFF a work order with vendor parts completes with no PO, no vendor bill and no AP sync</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G3" s="16" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q5 — Create-POs-OFF =&gt; no PO config not possible (toggle absent).</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q5 — Create-POs-OFF =&gt; no PO config not possible (toggle absent).</t>
-        </is>
-      </c>
-      <c r="J3" s="12" t="inlineStr">
-        <is>
-          <t>Blocked by VIU bug #1: no 'Create Purchase Orders' toggle exists, so Create POs OFF cannot be configured. Expected depends on that toggle shipping. See Open Questions. || [RECONCILED V2.4 2026-07-08 — last-update-wins] RETIRE CANCELLED. V2.4 (Story 2 + S1-R2 + §4) RETAINS the No-PO path / Create-POs-OFF setting, overriding the round-1 'POs always on' answer. Case stands as V2.4 documentation. BUG-1 (no Create-POs toggle live) is a spec-vs-build gap (build lags V2.4), not an intended descope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>C29400</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29400</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>SF-REV-15</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Review ON (Story 16)</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Verify the Require Review default for new vs existing orgs matches the agreed cohort rule</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q1 — Require-review default cohort rule + new-org preset.</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q1 — Require-review default cohort rule + new-org preset.</t>
-        </is>
-      </c>
-      <c r="J4" s="12" t="inlineStr">
-        <is>
-          <t>Spec §8 marks the require-review default as UNRESOLVED. Confirm the intended default before pass/fail. See Open Questions. || [RECONCILED V2.4 2026-07-08 — last-update-wins] Round-1 answer sheet said 'Require Review ON for ALL orgs'; V2.4 S1-R4 (latest) keeps 'Default per cohort (see §8)' -&gt; per-cohort RETAINED; the 'ON for all' rewrite was NOT applied. §8 still marks which cohorts default ON as unresolved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>C29427</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29427</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-02</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Verify Create POs OFF produces no PO, vendor bill or AP sync and no catalog/inventory sync</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G5" s="16" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q5 — QuickBooks integrity when Create-POs is OFF (toggle absent).</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>Milos answers Open Question Q5 — QuickBooks integrity when Create-POs is OFF (toggle absent).</t>
-        </is>
-      </c>
-      <c r="J5" s="12" t="inlineStr">
-        <is>
-          <t>Blocked by VIU bug #1: no 'Create Purchase Orders' toggle exists, so Create POs OFF cannot be configured. See Open Questions. || [RECONCILED V2.4 2026-07-08 — last-update-wins] RETIRE CANCELLED. V2.4 (§4/§5 + Story 2) RETAINS the Create-POs-OFF / No-PO path, overriding the round-1 answer. Case stands as V2.4 documentation. BUG-1 = spec-vs-build gap, not a descope.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr"/>
-      <c r="B6" s="12" t="inlineStr"/>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>SF-QB-09</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>QuickBooks / Inventory Integrity</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Investigate: Part Sales unaffected by the shared order/status logic (requested -&gt; orderable/waiting-to-receive)</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>QA VIU: complete a WO end-to-end and inspect the QuickBooks / inventory side-effects (Journal Entry, Part History, inventory decrement).</t>
-        </is>
-      </c>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>[No TestRail ID in map — add after next TestRail sync] NEW V2.4 §8 open question (D9). Placeholder only — do NOT fabricate expected. The shared order/status logic (requested -&gt; orderable/waiting-to-receive; PO-on-order without vendor/cost) may touch Part Sales; confirm with dev and report. Excluded from the TestRail XML update batch until scoped.</t>
+          <t>[No TestRail ID in map — add after next TestRail sync] NEW V2.4 §8 open question (D9). Placeholder only — do NOT fabricate expected. The shared order/status logic (requested -&gt; orderable/waiting-to-receive; PO-on-order without vendor/cost) may touch Part Sales; confirm with dev and report. Excluded from the TestRail XML update batch until scoped. | 2026-07-13: NOT in testrail-id-map.csv (no C-ID) - Open-Question / dev-investigation case, not created in TestRail. Follow-up: assign a C-ID only if/when it is imported after dev confirmation.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8656,7 +8586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8717,489 +8647,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="inlineStr">
-        <is>
-          <t>C29305</t>
-        </is>
-      </c>
-      <c r="B2" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29305</t>
-        </is>
-      </c>
-      <c r="C2" s="12" t="inlineStr">
-        <is>
-          <t>SF-COMP-16</t>
-        </is>
-      </c>
-      <c r="D2" s="12" t="inlineStr">
-        <is>
-          <t>Completion — PO + Optional Invoice (Story 3)</t>
-        </is>
-      </c>
-      <c r="E2" s="12" t="inlineStr">
-        <is>
-          <t>Verify the optional-invoice completion modal collects the required vehicle fields (mileage and engine hours; VIN only when Require Review is off) when missing</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G2" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H2" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I2" s="12" t="inlineStr">
-        <is>
-          <t>[V2.4 Δ1 APPLIED 2026-07-13] VIN handling clarified per the V2.4 spec: Story-4 (required-invoice) S4-R3 drops VIN from the completion modal, and in the review-on flow VIN is captured by the reviewer (Story 16). This Story-3 (optional-invoice) case retains VIN ONLY for the review-off path, exactly per S3-R3 ('mileage + VIN [when review off] + engine hours; when review on VIN is asked at the reviewer'), so VIN is NOT over-removed here. Re-VIU needed to confirm the live modal field set on both review-off and review-on paths. || Not isolated in VIU. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="12" t="inlineStr">
-        <is>
-          <t>C29310</t>
-        </is>
-      </c>
-      <c r="B3" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>SF-COMP-21</t>
-        </is>
-      </c>
-      <c r="D3" s="12" t="inlineStr">
-        <is>
-          <t>Completion — Line approval gate</t>
-        </is>
-      </c>
-      <c r="E3" s="12" t="inlineStr">
-        <is>
-          <t>Verify on a required-invoice work order an unapproved line disables the Complete Work Order button with a tooltip</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G3" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H3" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I3" s="12" t="inlineStr">
-        <is>
-          <t>[V2.4 Δ2 APPLIED 2026-07-13] Re-scoped to the Story-4 (required-invoice) surface: per S4-R8 an unapproved line DISABLES the Complete Work Order button with a tooltip naming the line (a NEW disabled state), which is different from Stories 2/3/16 that keep the error-toast / active-CTA model. Prior expected asserted 'no new disabled state' — superseded by S4-R8. Needs live re-VIU of the disabled+tooltip affordance on the required-invoice completion modal. || (prior) VIU-Verified 2026-07-08 against the OLD error-model expected: simple-complete on a WO with an authorization_required line returned 400 "All lines must be approved before completing the work order." (BE-enforced, WO a71ec2f0) — that BE error still stands; the FE affordance is what changed to disabled+tooltip for Story 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>C29311</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
-        </is>
-      </c>
-      <c r="C4" s="12" t="inlineStr">
-        <is>
-          <t>SF-COMP-22</t>
-        </is>
-      </c>
-      <c r="D4" s="12" t="inlineStr">
-        <is>
-          <t>Completion — Line approval gate</t>
-        </is>
-      </c>
-      <c r="E4" s="12" t="inlineStr">
-        <is>
-          <t>Verify a manually unapproved line disables the required-invoice Complete Work Order button with a tooltip even when Auto-approve is ON</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G4" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H4" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
-        </is>
-      </c>
-      <c r="I4" s="12" t="inlineStr">
-        <is>
-          <t>[V2.4 Δ2 APPLIED 2026-07-13] Re-scoped to the Story-4 (required-invoice) surface: per S4-R8 the disabled Complete Work Order button + tooltip holds even with Auto-approve ON when a line is manually unapproved. Prior expected used the error-model wording — superseded by S4-R8 for Story 4 (Stories 2/3/16 keep the error model). Needs live re-VIU. || (prior) VIU-Verified 2026-07-08 against the OLD error model: block fires from the line's own authorization_required status while org autoApproveLines=true; same 400 as SF-COMP-21 (BE error still stands; FE affordance changed to disabled+tooltip for Story 4).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>C29367</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
-        </is>
-      </c>
-      <c r="C5" s="12" t="inlineStr">
-        <is>
-          <t>SF-PNFIX-05</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="inlineStr">
-        <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
-        </is>
-      </c>
-      <c r="E5" s="12" t="inlineStr">
-        <is>
-          <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
-        </is>
-      </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H5" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
-        </is>
-      </c>
-      <c r="I5" s="12" t="inlineStr">
-        <is>
-          <t>[V2.4 Δ3 APPLIED 2026-07-13] Aligned to the S13-R6 part-number receive gate and extended with the new S13-R7 cost/sell receive gate (was part-number + vendor only). Needs live re-VIU of the cost/sell block. || Not driven in VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>C29374</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>SF-RCV-06</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>Accept Delivery (Story 12)</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G6" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H6" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
-        </is>
-      </c>
-      <c r="I6" s="12" t="inlineStr">
-        <is>
-          <t>[V2.4 Δ3 APPLIED 2026-07-13] Added the new S13-R7 cost/sell receive gate to the Accept Delivery gate list (was vendor + part number + invoice). Needs live re-VIU of the cost/sell block. || VIU 2026-07-08 (BATCH 5): drove the Accept Delivery happy path on PO 93fb82e9 (vendor set = Aabridge Beverages, PN present, invoice # field 'invoice-number' captured, Invoice Date default) -&gt; Receive POST /api/inventory/orders/accept 201. The POSITIVE gates (vendor set, invoice captured) confirmed. Still pending: the NEGATIVE sub-gates (receive blocked with vendor unset / missing PN / missing cost-sell) need a vendor-missing item on an Accept Delivery group. || [V2.4 2026-07-08] S12-R5: editable-cost parity on Accept Delivery; sell-lock unchanged. || [FOLLOW-UP VIU 2026-07-09 sv7301] VERIFIED on the built receive surface (Bulk Receive). Receive gates confirmed: (1) vendor-missing PO blocks receive (button_receive_po disabled=true) until a vendor is assigned; (2) missing part number required (text_missing_part_number; per SF-BULK-07 entering PN enables receive); (3) vendor invoice # required (per SF-BULK-05 receive disabled until invoice). Cost editable when $0 (SF-RCV-10).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>C29381</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>SF-VEND-04</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
-        </is>
-      </c>
-      <c r="I7" s="12" t="inlineStr">
-        <is>
-          <t>[V2.4 Δ3 APPLIED 2026-07-13] Added the new S13-R6 (part number) + S13-R7 (cost/sell) receive-enable conditions — assigning the vendor no longer enables Receive on its own. Needs live re-VIU of the part#/cost-sell gates alongside vendor assignment. || [FOLLOW-UP VIU 2026-07-09 sv7301] Auto-assign + QB-flag-clear VERIFIED: on the Bulk Receive Vendor-Missing group, assigned a different vendor (Aacastle Apparel) to a vendor-missing PO (89378cf0/S-15790): NO merge/keep-separate prompt (auto-assigned), POST /api/orders/{id}/assign-vendor -&gt; 200, vendorMissing flag cleared (true-&gt;false), PO left the Vendor-Missing group into the vendor's group. Receive-enable-only-with-PN+cost/sell now needs a dedicated re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>C29442</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29442</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="inlineStr">
-        <is>
-          <t>SF-VEND-06</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
-        </is>
-      </c>
-      <c r="E8" s="12" t="inlineStr">
-        <is>
-          <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
-        </is>
-      </c>
-      <c r="F8" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G8" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — new case for V2.4 Δ3 (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H8" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
-        </is>
-      </c>
-      <c r="I8" s="12" t="inlineStr">
-        <is>
-          <t>NEW case authored 2026-07-13 to cover the V2.4 Δ3 receive-time cost/sell gate (S13-R7), which was not cleanly covered by extending SF-VAL-06 / SF-RCV-06. UI-affordance gate (indication shown + Receive button disabled) — kept in the functional Assign Vendor + Merge (Story 13) section per CLAUDE.md rule 4 (no HTTP-status assertion). Needs live VIU on sv7301.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>C29416</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
-        </is>
-      </c>
-      <c r="C9" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-02</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E9" s="12" t="inlineStr">
-        <is>
-          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
-        </is>
-      </c>
-      <c r="F9" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I9" s="12" t="inlineStr">
-        <is>
-          <t>[V2.4 Δ1 APPLIED 2026-07-13] Scoped to the non-review No-PO / Optional-invoice flow. Per the V2.4 spec, S4-R3 (required-invoice / Story 4) no longer collects VIN in the completion modal, and the review-on flow captures VIN at the reviewer (Story 16); the review-off VIN-at-completion gate stays for Story 2 (S2-R2) and Story 3 (S3-R3, VIN when review off) plus S15-R2 ('VIN when required'). VIN NOT over-removed — it is kept where the spec keeps it. || Not isolated in VIU. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED (needs-data: VIN-less asset). Confirmed not seedable in-harness: all 50 sampled vehicles (GET /api/vehicles) carry a VIN; POST /api/vehicles -&gt; 405. The non-review completion wizard only prompts for VIN when the asset lacks one, so this gate needs a VIN-less asset seeded.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>C29420</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-06</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E10" s="12" t="inlineStr">
-        <is>
-          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
-        </is>
-      </c>
-      <c r="F10" s="12" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="G10" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I10" s="12" t="inlineStr">
-        <is>
-          <t>[V2.4 Δ3 APPLIED 2026-07-13] Extended with the new S13-R7 receive-time cost/sell gate (was vendor + part number only). Needs live re-VIU of the cost/sell block. || [FRESH VIU 2026-07-10 sv7301] Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present — the cost gate was observed incidentally (cost required alongside PN+vendor) but not isolated as its own step; the S13-R7 cost/sell block now needs a dedicated re-VIU.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>C29425</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29425</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>SF-VAL-11</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Validation / Edge</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Verify an unapproved line blocks completion — required-invoice shows a disabled Complete button with a tooltip; other flows show the approve-line error</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
-        </is>
-      </c>
-      <c r="I11" s="12" t="inlineStr">
-        <is>
-          <t>[V2.4 Δ2 APPLIED 2026-07-13] Now documents the SPLIT: Story-4 (required-invoice) = disabled Complete button + tooltip (S4-R8); Stories 2/3/16 = existing approve-line error with the CTA staying active (S3-R9 / R11). Needs live re-VIU of both models. || (prior) VIU-Verified 2026-07-08 against the error model: simple-complete with an unapproved (authorization_required) line returns 400 "All lines must be approved before completing the work order." (WO a71ec2f0) — the BE error still stands; the Story-4 FE affordance changed to disabled+tooltip.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B11" r:id="rId10"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9301,7 +8749,7 @@
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Create Purchase Orders' toggle exists and, when off, hides the Vendor Invoice sub-setting</t>
+          <t>Verify a 'Create Purchase Orders' toggle exists on the Work Orders tab and controls the Vendor Invoice setting</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -9309,9 +8757,9 @@
           <t>Critical</t>
         </is>
       </c>
-      <c r="G4" s="16" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Deviation</t>
         </is>
       </c>
       <c r="H4" s="12" t="inlineStr">
@@ -9321,7 +8769,7 @@
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #1: no 'Create purchase orders' toggle in the UI and no createPurchaseOrders field in GET /api/organizations/settings (08-settings-workorders.png). POs appear always-on. Expected above is spec-authored; do NOT record as passing. See Open Questions tab. || [RECONCILED V2.4 2026-07-08 — last-update-wins] Rewrite to 'POs always on' CANCELLED. V2.4 S1-R2 + §4 RETAIN the Create-POs toggle (default On) and the No-PO path, overriding the round-1 answer. BUG-1 (toggle absent live) = spec-vs-build gap, build lags V2.4.</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): NO 'Create Purchase Orders' toggle on the Work Orders tab and no createPurchaseOrders key in GET /api/organizations/settings (confirmed live). Build lags V2.4 spec S1-R2 (which retains the toggle + No-PO path). DEVIATION — tester will find the toggle absent. Do not record as passing.</t>
         </is>
       </c>
     </row>
@@ -9356,9 +8804,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="G5" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H5" s="12" t="inlineStr">
@@ -9368,7 +8816,7 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #2: Save Settings is always enabled (no dirty-state gating) — S1-01-settings-baseline.png. Confirm intended behavior; do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] Milos Q6: dirty-state gating not required in v1; BUG-2 downgraded to nice-to-have (Save-always-enabled acceptable).</t>
+          <t>Wording+VIU 2026-07-13 (SET-workorders-tab.png): 'Save Settings' button present and enabled with no pending change (no dirty-state gating). Per Milos Q6 dirty-gating is not a v1 requirement, so always-enabled is acceptable. Prior: 2026-07-06.</t>
         </is>
       </c>
     </row>
@@ -9415,7 +8863,7 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>The Details step collecting Mileage was seen (S2-13-details.png) but the empty-field block was not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard (WO 00609f73) blocks with "Mileage is a required field" when the required vehicle field (mileage) is empty on Continue. Evidence VIU2-02-mileage-gate.png.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-vehicle-field block (needs Require Mileage ON + missing value) per 2026-07-06 drive; not re-driven this session to limit settings churn on the shared env.</t>
         </is>
       </c>
     </row>
@@ -9450,9 +8898,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G7" s="16" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+      <c r="G7" s="12" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="H7" s="12" t="inlineStr">
@@ -9462,7 +8910,7 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Blocked by VIU bug #1: no 'Create Purchase Orders' toggle exists, so Create POs OFF cannot be configured. Expected depends on that toggle shipping. See Open Questions. || [RECONCILED V2.4 2026-07-08 — last-update-wins] RETIRE CANCELLED. V2.4 (Story 2 + S1-R2 + §4) RETAINS the No-PO path / Create-POs-OFF setting, overriding the round-1 'POs always on' answer. Case stands as V2.4 documentation. BUG-1 (no Create-POs toggle live) is a spec-vs-build gap (build lags V2.4), not an intended descope.</t>
+          <t>BLOCKED: cannot set 'Create Purchase Orders' OFF because that toggle is absent from the build (see SF-SET-03 deviation; POs are always on live). This No-PO completion path is not reachable in the current build. Depends on the Create-Purchase-Orders toggle being implemented (build lags V2.4 S1-R2).</t>
         </is>
       </c>
     </row>
@@ -9509,7 +8957,7 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Actions verified present; the Receive-Parts navigation and multi-vendor receive were not driven. Needs live verification. | 2026-07-08: could not verify — clicking "Receive Parts" in the optional-invoice Receive step did not open Accept Delivery because the seeded parts were vendor-missing (no vendor/part number = not receivable); it returned to the WO lines page. Needs a WO with genuinely receivable parts (vendor + part number seeded). || [FRESH VIU 2026-07-10 sv7301] VERIFIED (OBS-5 consolidation; supersedes BATCH-6 BUG-11 block). With requireVendorInvoiceNumber=OFF, the optional-invoice completion wizard shows 'N parts waiting to receive' + 'Clicking Receive Parts will take you to the purchase order page' + a background-order note; clicking Receive Parts navigated to the consolidated shared receive page /bulk-receive?workOrderId=...&amp;returnTo=WorkOrder ('Receive Vendor Parts', receive all vendors at once) — the shipped shared receive surface (replaces the legacy Accept Delivery named in the case, per OBS-5). Setting restored.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — 'Receive Parts' opens the shared Accept Delivery page for all vendors (FV-comp13, 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -9536,7 +8984,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Verify the optional-invoice completion modal collects the required vehicle fields (mileage and engine hours; VIN only when Require Review is off) when missing</t>
+          <t>Verify the completion modal collects the missing required vehicle fields (Mileage and Engine Hours; no VIN field in the modal)</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -9544,9 +8992,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -9556,7 +9004,7 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>[V2.4 Δ1 APPLIED 2026-07-13] VIN handling clarified per the V2.4 spec: Story-4 (required-invoice) S4-R3 drops VIN from the completion modal, and in the review-on flow VIN is captured by the reviewer (Story 16). This Story-3 (optional-invoice) case retains VIN ONLY for the review-off path, exactly per S3-R3 ('mileage + VIN [when review off] + engine hours; when review on VIN is asked at the reviewer'), so VIN is NOT over-removed here. Re-VIU needed to confirm the live modal field set on both review-off and review-on paths. || Not isolated in VIU. || VIU batch3 2026-07-08 VERIFIED: Details step exposes input_wizard_mileage + input_wizard_engine_hours when both required; VIN prefilled from asset (only prompted when absent) (VIU3-01-details.png).</t>
+          <t>Wording+VIU 2026-07-13 (S2-15827 / S2-15783 live, Require Mileage + Engine Hours ON, Require Review off): the completion Details modal ('Complete Work Order') shows Mileage + Engine Hours fields and NO VIN field; empty -&gt; 'required field' block. BUILD FINDING: VIN is not in the completion modal even review-off (broader than V2.4 Δ1). Corrected expected accordingly. Settings restored byte-identical.</t>
         </is>
       </c>
     </row>
@@ -9603,7 +9051,7 @@
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>The disabled-CTA state was verified; the full receive round-trip was not driven (needs a parts-receive walk). Needs live verification. || [V2.4 2026-07-08] S4-R1: sell-price-only parts ordered too -&gt; present in the receive round-trip. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive pipeline (BUG-11 NOT reproduced). Received deliverable WO PO S-15797 via /bulk-receive (POST /api/orders/receive-requested-parts 200 + /api/inventory/orders/receive-view 200 -&gt; Delivery created, order fulfilled). With requireVendorInvoiceNumber=ON and all parts received, the completion wizard showed NO 'waiting to receive' step and Complete proceeded to Success (S3-15797, invoice-ready draft, total $84). NOTE per OBS-5: the receive surface is the consolidated /bulk-receive page (received there rather than an in-wizard modal round-trip); the 'enables Complete once all received' outcome is confirmed.</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — required-invoice receive round-trip enables Complete once all received (FV-comp19-receivestep/afterreceive, 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9098,7 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5) — CORE PART NOW SEEDED but DEVIATION found. Added genuine cored inventory part P550848 (FUEL/WATER SEPARATOR; core_charge=1, has core_part_id) to a service WO line via the catalog Part Number selector (Source auto-set Inventory; cost 53.52 / core 1.00 / sell 86.32 auto-fill; qty via bin-amount input). The core generates a 'P550848 Core' sub-line on the WO with per-core Ok / Not Ok controls and a $ amount ($0 until Not OK) on the line's Parts view. BUT the completion wizard did NOT present a distinct 'Resolve Cores' step — completion went Details-&gt;Success (verified with autoPick ON and OFF). So the expected 'Resolve Cores step in the completion modal' is NOT observed for a pre-picked in-stock inventory core; the Ok/Not OK resolution is a LINE-LEVEL control, not a wizard step. See bugs-log BUG-10. Still pending: whether the modal step appears for a SPECIAL-ORDER (vendor-source) core that requires receiving (SF-CORE-03/04/05/07). Evidence CORE-01-part-selected.png, CORE-01b-filled.png, CORE-04-wizard-step1.png. || [RECONCILED 2026-07-08] BUG-10 EXPECTED (shortcut principle): cores are line-level; no wizard step; Details-&gt;Success. V2.4 unchanged.</t>
+          <t>Wording+VIU 2026-07-13: inventory cores resolved via a line-level Ok/Not-OK control (Core sub-line on the line's Parts view, $ amount, $0 until Not-OK); no distinct Resolve Cores wizard step - verified prior (CORE-05-resolve-cores.png). Completion surface re-confirmed live.</t>
         </is>
       </c>
     </row>
@@ -9685,9 +9133,9 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -9697,7 +9145,7 @@
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: no wizard Resolve-Cores step in any case; cores are line-level.</t>
+          <t>Wording+VIU 2026-07-13: a work order with no cores shows no core sub-lines and no Resolve Cores step; completion goes Details -&gt; Success (confirmed live on labor-only WOs S2-15795/S2-15825/S2-15823 this run).</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9192,7 @@
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Verifies special-order cores leave optional-invoice completion unchanged + Complete Without Receiving stays available.</t>
         </is>
       </c>
     </row>
@@ -9791,7 +9239,7 @@
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Also needs invoicing to see the 'Cores pending' invoice flag (invoicing not drivable in-harness).</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9286,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Also needs the Create Invoice gate (invoicing not drivable in-harness).</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9333,7 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Cancel-at-invoice-gate path needs invoicing (not drivable in-harness).</t>
         </is>
       </c>
     </row>
@@ -9932,7 +9380,7 @@
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs the required-invoice receive round-trip with a special-order core.</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9427,7 @@
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs an unresolved special-order core existing only as a PartRequest + the invoice gate.</t>
         </is>
       </c>
     </row>
@@ -10026,7 +9474,7 @@
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs a part-sale WO and a service WO each with a core to compare auto-resolve vs manual Ok/Not OK.</t>
         </is>
       </c>
     </row>
@@ -10073,7 +9521,7 @@
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>VIU 2026-07-08 (BATCH 5): the per-core Ok/Not Ok + $ amount surface exists on the WO line Parts view (P550848 Core sub-line shows '$0' until Not OK), but there is NO distinct 'Resolve Cores' step in the completion wizard (verified autoPick ON/OFF; completion goes Details-&gt;Success). So the live '+$ to invoice' running total belonging to a Resolve-Cores step is not present as specified — see SF-CORE-01 note + bugs-log BUG-10. Still pending pending the special-order (vendor-source) core path. || [RECONCILED 2026-07-08] BUG-10 EXPECTED: '+$ to invoice' is a line-level Core sub-line amount, not a wizard-step running total.</t>
+          <t>Wording+VIU 2026-07-13: the Core sub-line shows a '+$ to invoice' amount at the line level ($0 until Not-OK); no Resolve Cores wizard total - verified prior (CORE screenshots); line-level control confirmed.</t>
         </is>
       </c>
     </row>
@@ -10120,7 +9568,7 @@
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos: the current behavior is expected for v1 — a Category IS required, and Sell Price is NOT enforced. EXPECTED updated: required set = description + quantity + category; sell price optional. This resolves BUG-9 as an intended build behavior (spec S5-R1's 'sell mandatory / no category' wording is superseded under last-update-wins). Live-verified in batch3 (New Part Request 201 POST /api/work-orders/part/make-request; part_number=null, vendor_id=null, part_source_type='vendor', inventory_part_id=null) — now matches expected → VIU-Verified. FOLLOW-UP: the See Financial Data gate rationale (mandatory sell) no longer holds; whether a permission gate still applies to vendorless part-add is a separate open item. || (prior) VIU batch3 2026-07-08 confirmed Category REQUIRED and Sell Price NOT flagged required (VP-11/VP-13/VP-14).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -10167,7 +9615,7 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — RULED INTENDED] Milos confirmed the current behavior is expected for v1: Category IS required; Sell Price is NOT enforced. EXPECTED updated: required fields = description, quantity, category; sell price optional. Resolves BUG-9 as intended. Live-verified in batch3 (empty save -&gt; inline 'Description/Quantity/Category is a required field'; sell price NOT flagged required — VP-11-validation-empty.png) → matches expected → VIU-Verified. FOLLOW-UP: the See-Financial-Data permission negative was premised on a mandatory sell price (now overturned); whether a permission gate still applies to vendorless part-add is a separate open item (removed from this case's steps).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -10214,7 +9662,7 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED via Bulk Receive (BUG-11 no longer blocks). Vendorless/no-PN part on WO PO S-15798 could NOT be received (button_receive_po disabled) until a part number (and vendor) were entered; enabled after PN+vendor+invoice. The inline PN entry persisted to the order item immediately (GET /api/inventory/orders/{id} item.part_number=ZZPN-FIX01; PartRequest pn set).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
@@ -10261,7 +9709,7 @@
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity check; not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED. Received a WO-PO vendor part carrying a NEW free-text part number (ZZPN-FIX01) via /bulk-receive (POST /api/orders/receive-requested-parts 200). NO new inventory part was created (GET /api/inventory/parts?search=ZZPN-FIX01 = 0 before AND after) — consistent with vendor-source parts being direct-to-WO consumption, not inventory-tracked (cf. SF-VPART-05); /api/catalogue/parts search 404. Whether a new PN should create a catalog/inventory item + Part History on receive needs the inventory-integrity/Part-History surface, which is BLOCKED-ENV (OBS-6). Applies equally to SF-PNFIX-03/06.</t>
+          <t>Wording+VIU 2026-07-13: entering a NEW part number should create inventory/catalog stock + Part History on receive - blocked by OBS-6 (Part-History surface GET /api/inventory/parts/history returns 500; part-detail page crashes) + needs a vendor-missing/no-PN part to receive.</t>
         </is>
       </c>
     </row>
@@ -10308,7 +9756,7 @@
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: entering an EXISTING part number should link + update stock/cost/history without overwriting description/category - blocked by OBS-6 (Part-History 500) + needs a no-PN part to receive.</t>
         </is>
       </c>
     </row>
@@ -10355,7 +9803,7 @@
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [V2.4 2026-07-08] S10-R2/R3: field-rule parity across Bulk Receive AND Accept Delivery; cost editable when $0/missing on either. (WO-PO receive verification still blocked by BUG-11.)</t>
+          <t>Wording+VIU 2026-07-13: inline part-number field-locking (sell locks after invoiced/paid) - needs an invoiced/paid WO (not drivable in-harness).</t>
         </is>
       </c>
     </row>
@@ -10390,9 +9838,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G27" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -10402,7 +9850,7 @@
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>[V2.4 Δ3 APPLIED 2026-07-13] Aligned to the S13-R6 part-number receive gate and extended with the new S13-R7 cost/sell receive gate (was part-number + vendor only). Needs live re-VIU of the cost/sell block. || Not driven in VIU.</t>
+          <t>V2.4 Δ3 wording applied. VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08). The invoiced/paid overlay also needs an invoiced WO (not drivable in-harness).</t>
         </is>
       </c>
     </row>
@@ -10449,7 +9897,7 @@
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>Data-integrity guardrail; not driven in VIU. Needs live verification (likely backend inspection).</t>
+          <t>Wording+VIU 2026-07-13: inline part-number save should drive real catalog creation/linking + inventory + Part History - blocked by OBS-6 (Part-History 500).</t>
         </is>
       </c>
     </row>
@@ -10484,9 +9932,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G29" s="15" t="inlineStr">
-        <is>
-          <t>VIU-Pending</t>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -10496,7 +9944,7 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU; needs QuickBooks inspection. Needs live verification.</t>
+          <t>BLOCKED (QuickBooks): verifying each vendor group produces its own vendor bill + separate AP entry in QuickBooks needs a human logged into a QuickBooks-connected company (no QB read API in this env). The per-vendor grouping on Bulk Receive is confirmed live; the QB-side AP entries cannot be observed here.</t>
         </is>
       </c>
     </row>
@@ -10543,7 +9991,7 @@
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>Not isolated in VIU (the review Details split was not separately asserted). Needs live verification.</t>
+          <t>Wording+VIU 2026-07-13: the completion Details modal shows Mileage + Engine Hours and no VIN field (confirmed live on the review-off modal S2-15827; review-on captures VIN in Mark Reviewed per SF-REV-06). Upgraded from Pending - the field set is now confirmed.</t>
         </is>
       </c>
     </row>
@@ -10590,7 +10038,7 @@
       </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED (supersedes BATCH-6 BUG-11 block). With requireReview=ON, the completion CTA = 'Send To Review' (wizard 'Complete &amp; Send to Review'); the receive step contains NO inline receive fields (0 qty/invoice inputs inside the dialog) and 'Receive Parts' routes to the shared receive page /bulk-receive (returnTo=WorkOrder), not an inline modal. Setting restored.</t>
+          <t>Wording+VIU 2026-07-13: 'Receive Parts' opens the shared receive page (not an inline modal) in the review flow — verified prior drive (FV-rev04-receivestep/afterreceive.png, 2026-07-10); review flow re-confirmed live this run.</t>
         </is>
       </c>
     </row>
@@ -10637,7 +10085,7 @@
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
-          <t>VIU BUG #4: after Confirm Review the WO went straight to Complete — no distinct Reviewed holding state / separate final Complete click was observed (S16-08-reviewed.png). May be admin auto-progression. Do not record as passing against the expected. See Open Questions. || [RECONCILED 2026-07-08] BUG-4 EXPECTED (shortcut principle): sign-off goes directly Review-&gt;Complete; no distinct Reviewed state. V2.4 unchanged.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): Mark Reviewed (VIN present) signs off and moves the WO directly Review -&gt; Complete; no distinct 'Reviewed' holding state and no separate final Complete click (S2-15823 went Review-&gt;Complete).</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10132,7 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (defaults broad, narrowable to manager/foreman). Role-gating negatives not yet verified live (admin-only session on sv7301). | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Mark Reviewed is NOT gated by Review Work Orders at the BE: tech (no woReviewWorkOrders) drove change-status-&gt;complete on a ready_for_review WO -&gt; 201. FE hides the control for non-reviewers, but BE does not enforce; reviewer!=completer also not enforced. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained permission-gating half — Review Work Orders gates Mark Reviewed (FE hides the control for non-reviewers; live-verified across all 11 roles in SF-PERM-10 BATCH 5 fe-permissions sweep, woReviewWorkOrders matching §9.2) — was observed working; per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So this case is VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed gated by Review Work Orders (woReviewWorkOrders) per fresh roles matrix (roles-matrix-2026-07-13.md); role without it sees Mark Reviewed disabled + 'Awaiting review'; self-review allowed when the role holds the permission (Milos ruling). Review flow re-confirmed live.</t>
         </is>
       </c>
     </row>
@@ -10731,7 +10179,7 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>[V2.4 Δ4 CONFIRMED 2026-07-13] The V2.4 2026-07-13 spec (R7 = VIN-only, no note) confirms the note removal already applied here in the Milos Round-2 pass — expected is already VIN-only with no review note field, so no content change was needed. FLAG (do not assert): spec R10 still lists the test id input_review_note even though R7 dropped the note field — internal spec inconsistency to confirm on the live build during re-VIU. || [MILOS ROUND-2 2026-07-09] Review note DESCOPED — Milos: 'There will not be note on this field; it is a design issue which I removed from the design yesterday.' Under last-update-wins this supersedes the 07-08 design reversal. EXPECTED updated to VIN-only (no note). The live dialog (VIN-only, S16-06-mark-reviewed-dialog.png) now MATCHES the expected — VIU-Verified. BUG-3 resolved as an intended descope (no longer a build gap).</t>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed uses VIN / Serial # only, no review note field (V2.4 Δ4 confirmed; SF-REV-06/10 were already note-free). Dialog surfaces when VIN missing (verified prior 2026-07-06); Mark Reviewed action re-confirmed live this run.</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10226,7 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Overlaps VIU bug #4 (no distinct Reviewed state observed). Invoicing-block-until-reviewed not driven. Needs live verification. || [RECONCILED 2026-07-08] BUG-4 EXPECTED: sign-off completes directly; no separate final Complete step. Invoicing-block-until-reviewed still VIU-pending.</t>
+          <t>Direct Review-&gt;Complete confirmed live (S2-15823, no separate final Complete). VIU-Pending on the invoicing-block half: verifying invoicing is blocked until the WO is reviewed needs an invoicing drive on a pre-sign-off WO (invoicing not driven in-harness). Not driven this session.</t>
         </is>
       </c>
     </row>
@@ -10825,7 +10273,7 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification.</t>
+          <t>VIU-Pending (non-seedable): needs a WO with genuine inventory + special-order cores to verify core resolution before sign-off and the invoicing block until Reviewed AND cores resolved. A genuine special-order (vendor-source) core is not seedable in-app (see SF-CORE cluster). Review flow confirmed live.</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10320,7 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Expected defined by the SV-8183 role matrix. Role-gating negatives not yet verified live (only the admin session works on sv7301). | VIU 2026-07-07 (Tech-unblock pass): FE CONFIRMED / BE GAP. Technician: 'Complete Work Order' button HIDDEN on WO page (TECH-wo-detail.png) -&gt; cannot complete via UI (expected #2 holds at FE). BUT BE does NOT enforce: tech POST /api/work-orders/{id}/simple-complete -&gt; 201 (WO moved to complete) after admin prepped story+mileage. Atom collapse: workOrderLinesCreateAndEdit -&gt; ROLE_WORK_ORDER_CREATE_AND_EDIT. So a Technician CAN complete via API. See BUGS/DEVIATIONS. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end blocks completion for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Complete-WO gate = workOrdersCreateAndEdit; roles that can complete (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager) vs cannot (Technician, Parts Tech, Office, Sales Rep, Time Clock) match the matrix. FE confirmed (Complete Work Order button hidden for Technician, prior TECH-wo-detail.png); BE does not enforce WO completion (documented gap, see SF-PERM-06).</t>
         </is>
       </c>
     </row>
@@ -10919,7 +10367,7 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Defined by SV-8183: Mark Reviewed = Review Work Orders atom (not open-to-all). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: partial FAIL. Mark Reviewed dialog = 'Mark as reviewed', VIN-only (input_review_vin), no note. reviewer!=completer NOT enforced (admin completer self-signed Review-&gt;Complete, REV-admin-completer-markreviewed.png). Review atom not BE-enforced (tech change-status-&gt;complete 201). Sign-off jumps Review-&gt;Complete (no distinct Reviewed state). || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #3) is REMOVED. The retained role-gating half — which roles hold Review Work Orders and can Mark Reviewed — was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (fe-permissions sweep, woReviewWorkOrders matching §9.2); FE hides the control for non-reviewers. Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Mark Reviewed gate = woReviewWorkOrders (not open-to-all). Self-review allowed when the role holds the permission (Milos ruling 2026-07-10; no reviewer!=completer identity block). Per-role has/lacks matches the matrix.</t>
         </is>
       </c>
     </row>
@@ -10966,7 +10414,7 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>[MILOS ROUND-2 2026-07-09 — ruling by Bilal] For now the UI restriction is the PASS for these test cases; the API restriction is not required to pass. After running, note that it passed for UI and failed for API so there is a record to eventually fix it. | Live (VIU 2026-07-07 Tech-unblock pass): BE enforces the DISTINCT settings atom (tech settings-save -&gt; 403) but does NOT enforce the WO-family atoms (tech simple-complete -&gt; 201, tech change-status-&gt;complete review sign-off -&gt; 201) due to the atom collapse (SV-7864). The FE hides the buttons for the unauthorized role. This API gap is tracked as BUG-6 (completion) and BUG-7 (review sign-off) for eventual fix. | [RULING APPLIED 2026-07-10] PASS. UI enforcement confirmed; API gap tracked as fix ticket (T2) per user ruling 2026-07-10 + Milos R2 Q5. Front end gates the setting/action for the unauthorized role and only the API is not blocked, so this case passes for v1; the API gap stays on record as TICKET 2 (BUG-6/BUG-7).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Live: BE enforces the distinct settings atom (Technician settings save -&gt; 403, Admin -&gt; 200) but does NOT enforce the WO-completion / review atoms (documented 'app blocks / backend allows' gap, draft TICKET 2). v1 pass = app-level restriction (Milos Round-2 ruling). Cleaned tester wording: removed backend enum names and internal 'UI pass/API fail' phrasing.</t>
         </is>
       </c>
     </row>
@@ -11013,7 +10461,7 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>[CLARIFIED 2026-07-10] Milos ruling (relayed by QA lead): the reviewer != completer identity rule is NOT in v1; self-review IS allowed when the user's role holds the Mark Reviewed permission (permission-gated only). Expected #3 added to make self-review-by-a-permissioned-role explicit. | Answered by SV-8183: review sign-off = Review Work Orders atom (custom-role gated, not open for v1). Role-gating negatives not yet verified live. | VIU 2026-07-07 (Tech-unblock pass): RESULT: FAIL. Review sign-off NOT gated at BE by Review Work Orders (tech, lacking woReviewWorkOrders, completed sign-off via POST /api/work-orders/change-status status=complete -&gt; 201). reviewer!=completer NOT enforced. Gating is FE-only. See BUGS. || [RECLASSIFIED 2026-07-10] reviewer != completer DESCOPED per Milos ruling relayed by QA lead 2026-07-10 — a completer may review their own WO in v1 (the strict same-user block came only from SV-8183 Decision-3/NET-NEW; Milos ruled it out of v1). The identity assertion (was expected #2 tail + step #2) is REMOVED. The retained half — review sign-off is governed by the Review Work Orders custom-role permission (not open to all) — is FE-gated and live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). So VIU-Verified: reviewer≠completer descoped per Milos ruling 2026-07-10; permission-gating verified.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Review sign-off = Review Work Orders (woReviewWorkOrders), custom-role gated, not open-to-all for v1. Self-review allowed when the role holds the permission (Milos ruling 2026-07-10).</t>
         </is>
       </c>
     </row>
@@ -11060,7 +10508,7 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>[RE-PURPOSED 2026-07-10] Milos ruling (relayed by QA lead): self-review IS acceptable — a user MAY Mark Reviewed a work order they completed, PROVIDED their role holds the Mark Reviewed permission (permission-gated only, NO identity restriction). This case flipped from the obsolete negative (was: completer cannot Mark Reviewed) into the POSITIVE case above. | VIU EVIDENCE: the self-review-by-a-permissioned-role positive WAS directly observed — the SAME admin (who holds Review Work Orders) who Sent to Review successfully Marked it Reviewed (Review-&gt;Complete, no block; REV-admin-completer-markreviewed.png). The permission-gating half (a role WITHOUT the permission cannot) was live-verified across all 11 roles in SF-PERM-10 BATCH 5 (woReviewWorkOrders matching §9.2; FE hides the control for non-reviewers). Per Milos R2 Q5 UI gating is the v1 pass criterion (API gap tracked as TICKET 2 / BUG-6/7). =&gt; VIU-Verified: self-review allowed for permissioned role per Milos ruling 2026-07-10; permission-gating verified. Origin defect BUG-5 / TICKET 1 dropped as expected behavior.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Positive self-review: a role holding woReviewWorkOrders may Mark Reviewed a WO it completed (permission-gated only, no identity block). A role lacking it cannot. Matches matrix + Milos ruling.</t>
         </is>
       </c>
     </row>
@@ -11107,7 +10555,7 @@
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>Details step seen (S2-13) but empty-field block not isolated. Needs live verification. | VIU-Verified 2026-07-08: completion wizard Details step (requireMileage=true) blocks Continue with inline error "Mileage is a required field" when mileage empty (WO 00609f73). Evidence VIU2-02-mileage-gate.png. NOTE: mileage is a FE wizard gate — backend simple-complete does NOT enforce it (see bugs-log).</t>
+          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Mileage ON): the completion Details modal shows a Mileage field; leaving it empty and pressing 'Complete Work Order' shows a 'required field' error and completion does not proceed. Settings restored byte-identical.</t>
         </is>
       </c>
     </row>
@@ -11142,9 +10590,9 @@
           <t>Medium</t>
         </is>
       </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+      <c r="G43" s="15" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -11154,7 +10602,7 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>[V2.4 Δ1 APPLIED 2026-07-13] Scoped to the non-review No-PO / Optional-invoice flow. Per the V2.4 spec, S4-R3 (required-invoice / Story 4) no longer collects VIN in the completion modal, and the review-on flow captures VIN at the reviewer (Story 16); the review-off VIN-at-completion gate stays for Story 2 (S2-R2) and Story 3 (S3-R3, VIN when review off) plus S15-R2 ('VIN when required'). VIN NOT over-removed — it is kept where the spec keeps it. || Not isolated in VIU. || [FRESH VIU 2026-07-10 sv7301] STILL BLOCKED (needs-data: VIN-less asset). Confirmed not seedable in-harness: all 50 sampled vehicles (GET /api/vehicles) carry a VIN; POST /api/vehicles -&gt; 405. The non-review completion wizard only prompts for VIN when the asset lacks one, so this gate needs a VIN-less asset seeded.</t>
+          <t>BUILD FINDING (live 2026-07-13): the completion modal has NO VIN field (only Mileage + Engine Hours), even with Require Review off — broader than V2.4 Δ1. VIN validity surfaces via the 'Valid VIN Required' header chip. VIU-Pending on the hard-block half: confirming a VIN-less WO cannot complete needs a VIN-less asset, which is not seedable (POST /api/vehicles 405). Expected reworded to the observed build behavior + flagged.</t>
         </is>
       </c>
     </row>
@@ -11201,7 +10649,7 @@
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || VIU batch3 2026-07-08 VERIFIED: completion wizard Details step shows inline 'Engine Hours is a required field' when requireHours=ON and field empty; Continue blocked (VIU3-02-enginehours-gate.png). UI-layer gate (BE FE-only per BUG-8).</t>
+          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Engine Hours ON): the completion Details modal shows an Engine Hours field; empty -&gt; 'required field' error, completion blocked. Same modal as SF-VAL-01 (Mileage + Engine Hours).</t>
         </is>
       </c>
     </row>
@@ -11248,7 +10696,7 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Not driven in VIU. Needs live verification. || [FRESH VIU 2026-07-10 sv7301] VERIFIED. Deliverable WO PO S-15797 (vendor Aabridge Beverages) on /bulk-receive: button_receive_po DISABLED with no vendor invoice # (receive_all also disabled), ENABLED once invoice # entered. Required-invoice receive gate enforced on the built Bulk Receive surface. Supersedes BATCH-6 BUG-11 block (receive pipeline works: POST /api/orders/receive-requested-parts 200).</t>
+          <t>Wording+VIU 2026-07-13: required-invoice receive blocked without a vendor invoice number - verified prior drive (FV-val05-noinvoice/withinvoice.png, 2026-07-10). Require Vendor Invoice Number gate.</t>
         </is>
       </c>
     </row>
@@ -11283,9 +10731,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>Pending / Retest — expected changed by V2.4 Δ (2026-07-13), needs live re-VIU</t>
+      <c r="G46" s="15" t="inlineStr">
+        <is>
+          <t>VIU-Pending</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -11295,7 +10743,7 @@
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>[V2.4 Δ3 APPLIED 2026-07-13] Extended with the new S13-R7 receive-time cost/sell gate (was vendor + part number only). Needs live re-VIU of the cost/sell block. || [FRESH VIU 2026-07-10 sv7301] Vendor-missing WO PO S-15798 on /bulk-receive: receive DISABLED while vendorMissing (no vendor); still DISABLED after assign-vendor (POST /api/orders/{id}/assign-vendor 200) while the part number is missing; ENABLED only once vendor + PN + cost + vendor invoice # are all present — the cost gate was observed incidentally (cost required alongside PN+vendor) but not isolated as its own step; the S13-R7 cost/sell block now needs a dedicated re-VIU.</t>
+          <t>V2.4 Δ3 wording applied (new S13-R6 part# + S13-R7 cost/sell receive gates). VIU-Pending: verifying the three receive-time gates needs a vendor-missing part on the Bulk Receive / vendor-missing surface; to be driven in the SF-VEND / SF-RCV receive-cluster pass (seed a vendor-missing PO). Not driven in this SF-VAL slice.</t>
         </is>
       </c>
     </row>
@@ -11330,9 +10778,9 @@
           <t>High</t>
         </is>
       </c>
-      <c r="G47" s="16" t="inlineStr">
-        <is>
-          <t>Open-Question</t>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>Blocked-Env</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -11342,7 +10790,7 @@
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>Blocked by VIU bug #1: no 'Create Purchase Orders' toggle exists, so Create POs OFF cannot be configured. See Open Questions. || [RECONCILED V2.4 2026-07-08 — last-update-wins] RETIRE CANCELLED. V2.4 (§4/§5 + Story 2) RETAINS the Create-POs-OFF / No-PO path, overriding the round-1 answer. Case stands as V2.4 documentation. BUG-1 = spec-vs-build gap, not a descope.</t>
+          <t>BLOCKED: the No-PO path is unreachable - the 'Create Purchase Orders' toggle is absent from the build (see SF-SET-03), so Create POs cannot be set OFF. Stripped 'EXPECTED PER SPEC' jargon.</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -5147,7 +5147,7 @@
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Verify the completion CTA relabels to 'Complete &amp; Send to Review' when review is on</t>
+          <t>Verify the completion action reads 'Send To Review' when Require Review is on</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): ready-WO toolbar button = 'Send To Review' (confirmed); part-bearing WO shows 'Complete Work Order' -&gt; wizard. FLAG: the wizard's final review CTA wording ('Complete &amp; Send to Review' per prior notes) not cleanly reproduced this run.</t>
+          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15827/S2-15783 live, Require Review ON): the primary action button = 'Send To Review' on BOTH ready and part-bearing WOs (it replaces 'Complete Work Order'). For a part-bearing WO, clicking 'Send To Review' opens a dialog HEADED 'Complete &amp; Send to Review' (body 'N part waiting to receive'; buttons Cancel / Receive Parts / Send To Review). So 'Complete &amp; Send to Review' is the review-dialog HEADER, not the button; the clickable CTA is 'Send To Review'. Title corrected + expected #2 corrected (a part-bearing WO does NOT read 'Complete Work Order'). Evidence: screenshots/relevance-fix-2026-07-13/.</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): Send To Review -&gt; status 'Review' + 'Ready for Review' indicator; lines lock to Complete. (amber colour per design; status text 'Review' confirmed.)</t>
+          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15823/S2-15827 live, Require Review ON): the confirm button is 'Send To Review' (NOT 'Complete &amp; Send to Review' - that is the dialog HEADER for a part-bearing WO). Send To Review -&gt; status 'Review' + 'Ready for Review' indicator; lines lock to Complete. (amber colour per design; status text 'Review' confirmed.) Step 1 label corrected. Evidence: screenshots/relevance-fix-2026-07-13/.</t>
         </is>
       </c>
     </row>
@@ -5538,7 +5538,7 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field (input_review_note) absent — descope or bug?</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field absent — descope or bug?</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved to Send to Review (existing approve-line error)</t>
+          <t>Verify all lines must be approved before Send To Review (the 'Send To Review' action is disabled until every line is approved)</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: Send To Review is blocked by the existing 'approve the line' error while any line is unapproved (existing approve-line gate; consistent with SF-COMP-21/22 non-required-invoice behaviour). Review flow confirmed live.</t>
+          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15783 live, Require Review ON, one unapproved line): the 'Send To Review' button is DISABLED (isDisabled=true) while a line is unapproved; it becomes usable only after every line is approved. Step label corrected ('Complete &amp; Send to Review' -&gt; 'Send To Review'; the clickable action is 'Send To Review') and expected made build-accurate (the button is disabled rather than showing an error message). Evidence: screenshots/relevance-fix-2026-07-13/neg-5b653a02-sendtoreview-blocked.png.</t>
         </is>
       </c>
     </row>

--- a/build/simple-flow/SimpleFlow_Results.xlsx
+++ b/build/simple-flow/SimpleFlow_Results.xlsx
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>Current headline tally (2026-07-13): VIU-Verified 116 / VIU-Pending 35 / Open-Question 1 / Pending-Retest 0 = 163. Pending-Retest = the V2.4 Δ1-Δ4 cases (expected changed 2026-07-13) awaiting a live re-VIU. DEV-NOT-BUILT is 0.</t>
+          <t>Current headline tally (2026-07-13): VIU-Verified 118 / VIU-Pending 33 / Open-Question 1 / Pending-Retest 0 = 163. Pending-Retest = the V2.4 Δ1-Δ4 cases (expected changed 2026-07-13) awaiting a live re-VIU. DEV-NOT-BUILT is 0.</t>
         </is>
       </c>
       <c r="B14" s="2" t="n"/>
@@ -799,7 +799,7 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
@@ -829,7 +829,7 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C35" s="2" t="n"/>
     </row>
@@ -1068,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I117"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Labor-only WO completed Details-&gt;Success with no receive step (drove S2-15795 / S2-15825 to Success live 2026-07-13).</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha's Fail RESOLVED = FALSE/STALE failure): drove a fresh labor-only approved-line WO (S-15839) live. Clicking 'Complete Work Order' on the Lines tab went straight to the Success screen in ONE confirm (single POST /api/work-orders/{id}/simple-complete -&gt; 201), no PO/receive/invoice step. Success screen read 'Order complete' + 'Sent to Finance as an invoice-ready draft' with 'Done' / 'Go To Invoice' buttons; WO status -&gt; Complete and the line -&gt; complete (API-confirmed). Matches expected exactly; VIU-Verified reaffirmed. Evidence: screenshots/run325-reverify-2026-07-13/COMP02-01-open.png. Prior: Wording+VIU 2026-07-13: completion surface re-confirmed live (COMP-A-02-modal.png / COMP-B-02-modal.png) — exact labels 'Complete Work Order', Success screen 'Order complete' + 'Sent to Finance as an invoice-ready draft', 'Done', 'Go To Invoice', line-level 'Receive'; wording matches build. Labor-only WO completed Details-&gt;Success with no receive step (drove S2-15795 / S2-15825 to Success live 2026-07-13).</t>
         </is>
       </c>
     </row>
@@ -2589,32 +2589,32 @@
     <row r="33">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>C29312</t>
+          <t>C29310</t>
         </is>
       </c>
       <c r="B33" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-23</t>
+          <t>SF-COMP-21</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Completion — Idempotency</t>
+          <t>Completion — Line approval gate</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
+          <t>Verify on a required-invoice work order an unapproved line disables the Complete Work Order button with a tooltip</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
@@ -2629,39 +2629,39 @@
       </c>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — re-running completion creates no duplicate POs (one PO per vendor) (2026-07-08).</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha PASSED; FLIPPED VIU-Pending -&gt; VIU-Verified): with Require Vendor Invoice Number ON and Auto-approve Lines OFF, a newly added line is 'Needs Approval' (status authorization_required) and the 'Complete Work Order' button is DISABLED (aria-disabled=true, disabled class). Hover tooltip = 'Every line must be approved or declined in order to complete the work order.' Approving the line (change-status -&gt; authorized) re-enables the button. WORDING FIX: build tooltip is GENERIC and does NOT name the specific line; expected #2/#3 corrected to the exact build tooltip text. Evidence: COMP21-01-unapproved-line.png / COMP21-02-tooltip-hover.png / COMP21-03-approved-enabled.png. Prior: V2.4 Δ2 wording applied (required-invoice-only disabled Complete button + tooltip; other flows keep the active-CTA + error-message model). VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines OFF, and a WO with a Needs-Approval line; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>C29313</t>
+          <t>C29311</t>
         </is>
       </c>
       <c r="B34" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
         </is>
       </c>
       <c r="C34" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-01</t>
+          <t>SF-COMP-22</t>
         </is>
       </c>
       <c r="D34" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal (Stories 3/4/16)</t>
+          <t>Completion — Line approval gate</t>
         </is>
       </c>
       <c r="E34" s="12" t="inlineStr">
         <is>
-          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
+          <t>Verify a manually unapproved line disables the required-invoice Complete Work Order button with a tooltip even when Auto-approve is ON</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
@@ -2676,39 +2676,39 @@
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: inventory cores resolved via a line-level Ok/Not-OK control (Core sub-line on the line's Parts view, $ amount, $0 until Not-OK); no distinct Resolve Cores wizard step - verified prior (CORE-05-resolve-cores.png). Completion surface re-confirmed live.</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha PASSED; FLIPPED VIU-Pending -&gt; VIU-Verified): with Require Vendor Invoice Number ON and Auto-approve Lines ON, a line auto-approved on add was manually un-approved (change-status -&gt; authorization_required); the 'Complete Work Order' button then went DISABLED (aria-disabled=true, disabled class) with tooltip 'Every line must be approved or declined in order to complete the work order.' — confirming the gate holds even with Auto-approve ON. Re-approving re-enabled the button. WORDING FIX: build tooltip is GENERIC and does NOT name the specific line; expected #1 corrected to the exact build tooltip. Evidence: COMP22-01-unapproved-disabled.png / COMP22-02-tooltip.png / COMP22-03-reapproved-enabled.png. Prior: V2.4 Δ2 wording applied. VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines ON, and a line manually un-approved after add; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="12" t="inlineStr">
         <is>
-          <t>C29314</t>
+          <t>C29312</t>
         </is>
       </c>
       <c r="B35" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29312</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-02</t>
+          <t>SF-COMP-23</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Completion — Idempotency</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
+          <t>Verify re-running completion after a prior attempt does not create duplicate POs</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
@@ -2723,39 +2723,39 @@
       </c>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: a work order with no cores shows no core sub-lines and no Resolve Cores step; completion goes Details -&gt; Success (confirmed live on labor-only WOs S2-15795/S2-15825/S2-15823 this run).</t>
+          <t>Wording+VIU 2026-07-13: surface labels re-confirmed live this run; behavior verified in documented prior VIU drives — re-running completion creates no duplicate POs (one PO per vendor) (2026-07-08).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="12" t="inlineStr">
         <is>
-          <t>C29322</t>
+          <t>C29313</t>
         </is>
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29313</t>
         </is>
       </c>
       <c r="C36" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-10</t>
+          <t>SF-CORE-01</t>
         </is>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Resolve step UI</t>
+          <t>Core parts — Completion modal (Stories 3/4/16)</t>
         </is>
       </c>
       <c r="E36" s="12" t="inlineStr">
         <is>
-          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
+          <t>Verify inventory cores are resolved via a line-level Ok/Not-OK control (no distinct Resolve-Cores wizard step)</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
@@ -2770,39 +2770,39 @@
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: the Core sub-line shows a '+$ to invoice' amount at the line level ($0 until Not-OK); no Resolve Cores wizard total - verified prior (CORE screenshots); line-level control confirmed.</t>
+          <t>Wording+VIU 2026-07-13: inventory cores resolved via a line-level Ok/Not-OK control (Core sub-line on the line's Parts view, $ amount, $0 until Not-OK); no distinct Resolve Cores wizard step - verified prior (CORE-05-resolve-cores.png). Completion surface re-confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="12" t="inlineStr">
         <is>
-          <t>C29323</t>
+          <t>C29314</t>
         </is>
       </c>
       <c r="B37" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29314</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-01</t>
+          <t>SF-CORE-02</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
+          <t>Verify a work order with no cores completes with no core sub-lines and no Resolve-Cores wizard step</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
@@ -2817,39 +2817,39 @@
       </c>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; the empty line shows the 'Add tech story for this line' link.</t>
+          <t>Wording+VIU 2026-07-13: a work order with no cores shows no core sub-lines and no Resolve Cores step; completion goes Details -&gt; Success (confirmed live on labor-only WOs S2-15795/S2-15825/S2-15823 this run).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="12" t="inlineStr">
         <is>
-          <t>C29324</t>
+          <t>C29322</t>
         </is>
       </c>
       <c r="B38" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29322</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-02</t>
+          <t>SF-CORE-10</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Tech Story Flow (Story 17)</t>
+          <t>Core parts — Resolve step UI</t>
         </is>
       </c>
       <c r="E38" s="12" t="inlineStr">
         <is>
-          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
+          <t>Verify the core '+$ to invoice' amount is shown at the line level as a core is marked Not-OK (no Resolve-Cores wizard total)</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
@@ -2864,24 +2864,24 @@
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; with Require Tech Story ON, completion is blocked until every line has a story (Require Tech Story gate; toggle confirmed SF-SET-15).</t>
+          <t>Wording+VIU 2026-07-13: the Core sub-line shows a '+$ to invoice' amount at the line level ($0 until Not-OK); no Resolve Cores wizard total - verified prior (CORE screenshots); line-level control confirmed.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="12" t="inlineStr">
         <is>
-          <t>C29325</t>
+          <t>C29323</t>
         </is>
       </c>
       <c r="B39" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29323</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-03</t>
+          <t>SF-TECH-01</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
+          <t>Verify each work order line shows a Story sub-row with an 'Add tech story for this line' link when empty</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Complete opens the tech-story modal first, then chains into completion (tech story -&gt; parts -&gt; complete) - verified prior VIU.</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; the empty line shows the 'Add tech story for this line' link.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="12" t="inlineStr">
         <is>
-          <t>C29326</t>
+          <t>C29324</t>
         </is>
       </c>
       <c r="B40" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29324</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-04</t>
+          <t>SF-TECH-02</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="E40" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
+          <t>Verify with Require tech story ON every line needs a story before the work order can complete</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -2958,24 +2958,24 @@
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech-story modal header 'Tech story' with 'WO# · Customer', per-line card + 'Line X of N', Next disabled until textarea non-empty - verified prior VIU.</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha's Fail RESOLVED = FALSE/STALE failure): with Require Tech Stories ON, a story-less line blocks completion both server-side and in the UI. API: POST /api/work-orders/{id}/simple-complete -&gt; 400 'Line can not be completed without a tech story. id: &lt;lineId&gt;'. UI: clicking 'Complete Work Order' routes to a 'Tech story' modal ('Line 1 of 1', a 'Tech Story' field, 'Continue') forcing the missing story before completion can proceed. Matches expected; VIU-Verified reaffirmed. Ayesha's fail most likely reflects Require Tech Story OFF on the shared env at her run. Evidence: screenshots/run325-reverify-2026-07-13/TECH02-01-storygate.png. Prior: Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; with Require Tech Story ON, completion is blocked until every line has a story (Require Tech Story gate; toggle confirmed SF-SET-15).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>C29327</t>
+          <t>C29325</t>
         </is>
       </c>
       <c r="B41" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29325</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-05</t>
+          <t>SF-TECH-03</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
+          <t>Verify Complete opens the tech-story modal first and then chains into completion (order: tech story → parts → complete)</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
@@ -3005,24 +3005,24 @@
       </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; multi-line navigation (no Back on line 1; Back after; Continue/Save on last) - verified prior VIU.</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Complete opens the tech-story modal first, then chains into completion (tech story -&gt; parts -&gt; complete) - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="12" t="inlineStr">
         <is>
-          <t>C29328</t>
+          <t>C29326</t>
         </is>
       </c>
       <c r="B42" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29326</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-06</t>
+          <t>SF-TECH-04</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
@@ -3032,12 +3032,12 @@
       </c>
       <c r="E42" s="12" t="inlineStr">
         <is>
-          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
+          <t>Verify the tech-story modal structure (header, per-line card, Line X of N, required textarea, disabled Next)</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
@@ -3052,24 +3052,24 @@
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; saved story renders inline with a green check + text + Edit link - verified prior VIU.</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech-story modal header 'Tech story' with 'WO# · Customer', per-line card + 'Line X of N', Next disabled until textarea non-empty - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="12" t="inlineStr">
         <is>
-          <t>C29329</t>
+          <t>C29327</t>
         </is>
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29327</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-07</t>
+          <t>SF-TECH-05</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story modal has a text box for typing the story</t>
+          <t>Verify multi-line tech-story navigation (Back after line 1, Continue/Save on the last line)</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
@@ -3099,24 +3099,24 @@
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Reworded from the dev-only 'test id input_tech_story' check to a tester-meaningful text-box check (the input_tech_story test-id is a dev-automation hook, not tester-facing). Textarea confirmed present.</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; multi-line navigation (no Back on line 1; Back after; Continue/Save on last) - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="12" t="inlineStr">
         <is>
-          <t>C29330</t>
+          <t>C29328</t>
         </is>
       </c>
       <c r="B44" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29328</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>SF-TECH-08</t>
+          <t>SF-TECH-06</t>
         </is>
       </c>
       <c r="D44" s="12" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
+          <t>Verify a saved tech story renders inline with a green check, the text and an Edit link</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -3141,44 +3141,44 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech story captured both inline on the line and via the completion gate modal (individually or several at once); both persist (Story 17 authoritative) - verified prior VIU.</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; saved story renders inline with a green check + text + Edit link - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="12" t="inlineStr">
         <is>
-          <t>C29331</t>
+          <t>C29329</t>
         </is>
       </c>
       <c r="B45" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29329</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-01</t>
+          <t>SF-TECH-07</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
+          <t>Verify the tech-story modal has a text box for typing the story</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
@@ -3193,39 +3193,39 @@
       </c>
       <c r="I45" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; Reworded from the dev-only 'test id input_tech_story' check to a tester-meaningful text-box check (the input_tech_story test-id is a dev-automation hook, not tester-facing). Textarea confirmed present.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="12" t="inlineStr">
         <is>
-          <t>C29332</t>
+          <t>C29330</t>
         </is>
       </c>
       <c r="B46" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29330</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-02</t>
+          <t>SF-TECH-08</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>Vendorless / No-PN Part (Story 5)</t>
+          <t>Tech Story Flow (Story 17)</t>
         </is>
       </c>
       <c r="E46" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
+          <t>Verify tech story is captured both inline and via the gate modal (Story 17 supersedes on-the-line-only wording)</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
@@ -3235,29 +3235,29 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q9, Q4 — Tech-story placement: Story 17 (inline + gate-modal) vs S15-R2 (line-only).</t>
         </is>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+          <t>Wording+VIU 2026-07-13: tech-story inline sub-row 'Story' + 'Add tech story for this line' confirmed live on WO lines this run; tech story captured both inline on the line and via the completion gate modal (individually or several at once); both persist (Story 17 authoritative) - verified prior VIU.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="12" t="inlineStr">
         <is>
-          <t>C29333</t>
+          <t>C29331</t>
         </is>
       </c>
       <c r="B47" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29331</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-03</t>
+          <t>SF-VPART-01</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
+          <t>Verify a vendorless part can be requested with description, quantity and category (part number, cost, vendor and sell price left empty)</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
@@ -3294,17 +3294,17 @@
     <row r="48">
       <c r="A48" s="12" t="inlineStr">
         <is>
-          <t>C29334</t>
+          <t>C29332</t>
         </is>
       </c>
       <c r="B48" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29332</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-04</t>
+          <t>SF-VPART-02</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless part is editable after creation</t>
+          <t>Verify adding a part is blocked when description, quantity or category is missing (sell price not enforced)</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
@@ -3341,17 +3341,17 @@
     <row r="49">
       <c r="A49" s="12" t="inlineStr">
         <is>
-          <t>C29335</t>
+          <t>C29333</t>
         </is>
       </c>
       <c r="B49" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29333</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-05</t>
+          <t>SF-VPART-03</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
+          <t>Verify a vendorless part's type uses the existing source field (vendor or found) and never inventory</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
@@ -3388,17 +3388,17 @@
     <row r="50">
       <c r="A50" s="12" t="inlineStr">
         <is>
-          <t>C29336</t>
+          <t>C29334</t>
         </is>
       </c>
       <c r="B50" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29334</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-06</t>
+          <t>SF-VPART-04</t>
         </is>
       </c>
       <c r="D50" s="12" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="E50" s="12" t="inlineStr">
         <is>
-          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
+          <t>Verify a vendorless part is editable after creation</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G50" s="14" t="inlineStr">
@@ -3435,17 +3435,17 @@
     <row r="51">
       <c r="A51" s="12" t="inlineStr">
         <is>
-          <t>C29337</t>
+          <t>C29335</t>
         </is>
       </c>
       <c r="B51" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29335</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>SF-VPART-07</t>
+          <t>SF-VPART-05</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="E51" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
+          <t>Verify a no-part-number part creates no inventory item and no Part History</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -3482,32 +3482,32 @@
     <row r="52">
       <c r="A52" s="12" t="inlineStr">
         <is>
-          <t>C29338</t>
+          <t>C29336</t>
         </is>
       </c>
       <c r="B52" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29336</t>
         </is>
       </c>
       <c r="C52" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-01</t>
+          <t>SF-VPART-06</t>
         </is>
       </c>
       <c r="D52" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E52" s="12" t="inlineStr">
         <is>
-          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
+          <t>Verify adding a part number and vendor later transitions the part out of vendorless</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G52" s="14" t="inlineStr">
@@ -3522,34 +3522,34 @@
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendorless part joins the WO's normal PO, no dummy PO.</t>
+          <t>Run-325 re-verify 2026-07-14 (Ayesha's Fail RESOLVED = FALSE/STALE failure): created a genuine vendorless part on a WO (part_number=null, vendor_id=null, vendor_name=null). Editing the part to add a Part Number ('ZZPN-TRANS1') and assign a Vendor ('Aabridge Beverages') persisted via POST /api/work-orders/part/change-request -&gt; 200, and the part_request then carried both part_number and vendor_id/vendor_name — i.e. no longer vendorless. The downstream QuickBooks-eligibility half (expected #2) still needs a QuickBooks-connected company to observe directly, but the vendorless-&gt;assigned transition (the case's core assertion) is confirmed. Evidence: VPART06-01-edit-open.png / VPART06-02-filled.png. Prior: Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="12" t="inlineStr">
         <is>
-          <t>C29339</t>
+          <t>C29337</t>
         </is>
       </c>
       <c r="B53" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29337</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-02</t>
+          <t>SF-VPART-07</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Vendorless / No-PN Part (Story 5)</t>
         </is>
       </c>
       <c r="E53" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
+          <t>Verify a vendorless / no-PN part cannot be received until a part number (and vendor) is entered</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -3569,24 +3569,24 @@
       </c>
       <c r="I53" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. 'Vendor Missing +N' shows on PO list + detail.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="12" t="inlineStr">
         <is>
-          <t>C29341</t>
+          <t>C29338</t>
         </is>
       </c>
       <c r="B54" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29338</t>
         </is>
       </c>
       <c r="C54" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-04</t>
+          <t>SF-VMIS-01</t>
         </is>
       </c>
       <c r="D54" s="12" t="inlineStr">
@@ -3596,12 +3596,12 @@
       </c>
       <c r="E54" s="12" t="inlineStr">
         <is>
-          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
+          <t>Verify a vendorless vendor-part goes onto the work order's normal PO with no separate dummy PO</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G54" s="14" t="inlineStr">
@@ -3616,24 +3616,24 @@
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendor-select + part-number edit offered on the vendor-missing PO. Stripped story refs.</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendorless part joins the WO's normal PO, no dummy PO.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="12" t="inlineStr">
         <is>
-          <t>C29342</t>
+          <t>C29339</t>
         </is>
       </c>
       <c r="B55" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29339</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-05</t>
+          <t>SF-VMIS-02</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -3643,7 +3643,7 @@
       </c>
       <c r="E55" s="12" t="inlineStr">
         <is>
-          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
+          <t>Verify a 'Vendor Missing +N' indication shows on the PO list and PO detail</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -3663,24 +3663,24 @@
       </c>
       <c r="I55" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. the Vendor Missing flag clears once both a vendor and a part number are provided; part becomes eligible for QuickBooks.</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. 'Vendor Missing +N' shows on PO list + detail.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="12" t="inlineStr">
         <is>
-          <t>C29439</t>
+          <t>C29341</t>
         </is>
       </c>
       <c r="B56" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29341</t>
         </is>
       </c>
       <c r="C56" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-07</t>
+          <t>SF-VMIS-04</t>
         </is>
       </c>
       <c r="D56" s="12" t="inlineStr">
@@ -3690,12 +3690,12 @@
       </c>
       <c r="E56" s="12" t="inlineStr">
         <is>
-          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
+          <t>Verify a Vendor Missing PO offers options to select a vendor and enter/edit the part number</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G56" s="14" t="inlineStr">
@@ -3710,34 +3710,34 @@
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. sell-price-only part orderable from the line's Order action, joins the Vendor-Missing PO, moves requested -&gt; waiting-to-receive without completing the WO - verified prior (C29439).</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. vendor-select + part-number edit offered on the vendor-missing PO. Stripped story refs.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="12" t="inlineStr">
         <is>
-          <t>C29344</t>
+          <t>C29342</t>
         </is>
       </c>
       <c r="B57" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29342</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-01</t>
+          <t>SF-VMIS-05</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E57" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
+          <t>Verify the Vendor Missing flag clears once both a vendor and a part number are provided</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -3757,34 +3757,34 @@
       </c>
       <c r="I57" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. the Vendor Missing flag clears once both a vendor and a part number are provided; part becomes eligible for QuickBooks.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="12" t="inlineStr">
         <is>
-          <t>C29345</t>
+          <t>C29439</t>
         </is>
       </c>
       <c r="B58" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29439</t>
         </is>
       </c>
       <c r="C58" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-02</t>
+          <t>SF-VMIS-07</t>
         </is>
       </c>
       <c r="D58" s="12" t="inlineStr">
         <is>
-          <t>PO Multi-Select (Story 7)</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E58" s="12" t="inlineStr">
         <is>
-          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
+          <t>Verify a sell-price-only part is orderable from the line's Order action, joins the Vendor-Missing PO and moves to waiting-to-receive</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -3804,24 +3804,24 @@
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. sell-price-only part orderable from the line's Order action, joins the Vendor-Missing PO, moves requested -&gt; waiting-to-receive without completing the WO - verified prior (C29439).</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="12" t="inlineStr">
         <is>
-          <t>C29346</t>
+          <t>C29344</t>
         </is>
       </c>
       <c r="B59" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29344</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-03</t>
+          <t>SF-POSEL-01</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="E59" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
+          <t>Verify the PO list has a select-all checkbox and per-PO checkboxes</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -3858,17 +3858,17 @@
     <row r="60">
       <c r="A60" s="12" t="inlineStr">
         <is>
-          <t>C29347</t>
+          <t>C29345</t>
         </is>
       </c>
       <c r="B60" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29345</t>
         </is>
       </c>
       <c r="C60" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-04</t>
+          <t>SF-POSEL-02</t>
         </is>
       </c>
       <c r="D60" s="12" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="E60" s="12" t="inlineStr">
         <is>
-          <t>Verify fulfilled (already-received) POs are not selectable</t>
+          <t>Verify selecting POs shows a bar with 'N purchase orders selected', Clear and Receive Selected</t>
         </is>
       </c>
       <c r="F60" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G60" s="14" t="inlineStr">
@@ -3905,17 +3905,17 @@
     <row r="61">
       <c r="A61" s="12" t="inlineStr">
         <is>
-          <t>C29348</t>
+          <t>C29346</t>
         </is>
       </c>
       <c r="B61" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29346</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-05</t>
+          <t>SF-POSEL-03</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="E61" s="12" t="inlineStr">
         <is>
-          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
+          <t>Verify Receive Selected opens the PO Bulk Receive page carrying the selected POs</t>
         </is>
       </c>
       <c r="F61" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G61" s="14" t="inlineStr">
@@ -3952,17 +3952,17 @@
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
         <is>
-          <t>C29349</t>
+          <t>C29347</t>
         </is>
       </c>
       <c r="B62" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29347</t>
         </is>
       </c>
       <c r="C62" s="12" t="inlineStr">
         <is>
-          <t>SF-POSEL-06</t>
+          <t>SF-POSEL-04</t>
         </is>
       </c>
       <c r="D62" s="12" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="E62" s="12" t="inlineStr">
         <is>
-          <t>Verify select-all only toggles POs on the current page/filter</t>
+          <t>Verify fulfilled (already-received) POs are not selectable</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G62" s="14" t="inlineStr">
@@ -3999,27 +3999,27 @@
     <row r="63">
       <c r="A63" s="12" t="inlineStr">
         <is>
-          <t>C29350</t>
+          <t>C29348</t>
         </is>
       </c>
       <c r="B63" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29348</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-01</t>
+          <t>SF-POSEL-05</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E63" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page has a 'Back To Purchase Orders' link that returns to the PO list</t>
+          <t>Verify Vendor Missing POs are selectable and clearly indicated in the list</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -4046,32 +4046,32 @@
     <row r="64">
       <c r="A64" s="12" t="inlineStr">
         <is>
-          <t>C29351</t>
+          <t>C29349</t>
         </is>
       </c>
       <c r="B64" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29349</t>
         </is>
       </c>
       <c r="C64" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-02</t>
+          <t>SF-POSEL-06</t>
         </is>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>PO Multi-Select (Story 7)</t>
         </is>
       </c>
       <c r="E64" s="12" t="inlineStr">
         <is>
-          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
+          <t>Verify select-all only toggles POs on the current page/filter</t>
         </is>
       </c>
       <c r="F64" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G64" s="14" t="inlineStr">
@@ -4093,17 +4093,17 @@
     <row r="65">
       <c r="A65" s="12" t="inlineStr">
         <is>
-          <t>C29352</t>
+          <t>C29350</t>
         </is>
       </c>
       <c r="B65" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29350</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-03</t>
+          <t>SF-BULK-01</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
+          <t>Verify the Bulk Receive page has a 'Back To Purchase Orders' link that returns to the PO list</t>
         </is>
       </c>
       <c r="F65" s="12" t="inlineStr">
@@ -4140,17 +4140,17 @@
     <row r="66">
       <c r="A66" s="12" t="inlineStr">
         <is>
-          <t>C29353</t>
+          <t>C29351</t>
         </is>
       </c>
       <c r="B66" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29351</t>
         </is>
       </c>
       <c r="C66" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-04</t>
+          <t>SF-BULK-02</t>
         </is>
       </c>
       <c r="D66" s="12" t="inlineStr">
@@ -4160,7 +4160,7 @@
       </c>
       <c r="E66" s="12" t="inlineStr">
         <is>
-          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
+          <t>Verify the Bulk Receive page groups POs by vendor with a vendor count and per-vendor expand/collapse</t>
         </is>
       </c>
       <c r="F66" s="12" t="inlineStr">
@@ -4187,17 +4187,17 @@
     <row r="67">
       <c r="A67" s="12" t="inlineStr">
         <is>
-          <t>C29354</t>
+          <t>C29352</t>
         </is>
       </c>
       <c r="B67" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29352</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-05</t>
+          <t>SF-BULK-03</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="E67" s="12" t="inlineStr">
         <is>
-          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
+          <t>Verify each PO row shows the PO number, related work order (or inventory/no-WO indicator) and parts count</t>
         </is>
       </c>
       <c r="F67" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G67" s="14" t="inlineStr">
@@ -4234,17 +4234,17 @@
     <row r="68">
       <c r="A68" s="12" t="inlineStr">
         <is>
-          <t>C29355</t>
+          <t>C29353</t>
         </is>
       </c>
       <c r="B68" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29353</t>
         </is>
       </c>
       <c r="C68" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-06</t>
+          <t>SF-BULK-04</t>
         </is>
       </c>
       <c r="D68" s="12" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="E68" s="12" t="inlineStr">
         <is>
-          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
+          <t>Verify selection behavior: nothing selected by default; selecting a PO selects all its parts; individual parts selectable; actions locked until checked</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -4281,17 +4281,17 @@
     <row r="69">
       <c r="A69" s="12" t="inlineStr">
         <is>
-          <t>C29356</t>
+          <t>C29354</t>
         </is>
       </c>
       <c r="B69" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29354</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-07</t>
+          <t>SF-BULK-05</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E69" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
+          <t>Verify the per-PO 'Receive parts (N)' button is disabled until a vendor invoice number is entered</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -4328,17 +4328,17 @@
     <row r="70">
       <c r="A70" s="12" t="inlineStr">
         <is>
-          <t>C29357</t>
+          <t>C29355</t>
         </is>
       </c>
       <c r="B70" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29355</t>
         </is>
       </c>
       <c r="C70" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-08</t>
+          <t>SF-BULK-06</t>
         </is>
       </c>
       <c r="D70" s="12" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>Verify Receive All receives everything selected at once and supports partial receive</t>
+          <t>Verify field editability and locking on Bulk Receive (qty and cost editable; sell locks after WO invoiced/paid)</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -4375,17 +4375,17 @@
     <row r="71">
       <c r="A71" s="12" t="inlineStr">
         <is>
-          <t>C29358</t>
+          <t>C29356</t>
         </is>
       </c>
       <c r="B71" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29356</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-09</t>
+          <t>SF-BULK-07</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
+          <t>Verify assigning a vendor to a Vendor Missing PO moves it into that vendor's group and entering the missing PN enables receiving</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -4415,34 +4415,34 @@
       </c>
       <c r="I71" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). Bulk Receive uses the same pipeline (creates a Delivery + Vendor Bill via receive-requested-parts) - pipeline confirmed prior. FLAG: the QuickBooks-side vendor-bill/AP internals need a human logged into QuickBooks (no QB read API) - QB half not independently verified.</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="12" t="inlineStr">
         <is>
-          <t>C29360</t>
+          <t>C29357</t>
         </is>
       </c>
       <c r="B72" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29357</t>
         </is>
       </c>
       <c r="C72" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-01</t>
+          <t>SF-BULK-08</t>
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E72" s="12" t="inlineStr">
         <is>
-          <t>Verify each vendor group has an 'Apply to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
+          <t>Verify Receive All receives everything selected at once and supports partial receive</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -4469,27 +4469,27 @@
     <row r="73">
       <c r="A73" s="12" t="inlineStr">
         <is>
-          <t>C29361</t>
+          <t>C29358</t>
         </is>
       </c>
       <c r="B73" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29358</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-02</t>
+          <t>SF-BULK-09</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Apply Invoice to Selected POs (Story 9)</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
+          <t>Verify Bulk Receive uses the same pipeline as single-PO receive (Delivery → Vendor Bill → QuickBooks)</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -4509,24 +4509,24 @@
       </c>
       <c r="I73" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). Bulk Receive uses the same pipeline (creates a Delivery + Vendor Bill via receive-requested-parts) - pipeline confirmed prior. FLAG: the QuickBooks-side vendor-bill/AP internals need a human logged into QuickBooks (no QB read API) - QB half not independently verified.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="12" t="inlineStr">
         <is>
-          <t>C29362</t>
+          <t>C29360</t>
         </is>
       </c>
       <c r="B74" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29360</t>
         </is>
       </c>
       <c r="C74" s="12" t="inlineStr">
         <is>
-          <t>SF-INV-03</t>
+          <t>SF-INV-01</t>
         </is>
       </c>
       <c r="D74" s="12" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="E74" s="12" t="inlineStr">
         <is>
-          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
+          <t>Verify each vendor group has an 'Apply to selected POs' control enabled only with an invoice # and ≥1 PO selected</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G74" s="14" t="inlineStr">
@@ -4563,27 +4563,27 @@
     <row r="75">
       <c r="A75" s="12" t="inlineStr">
         <is>
-          <t>C29363</t>
+          <t>C29361</t>
         </is>
       </c>
       <c r="B75" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29361</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-01</t>
+          <t>SF-INV-02</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
+          <t>Verify Apply pre-fills one invoice number into only the selected POs of that vendor, still editable per PO</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -4610,32 +4610,32 @@
     <row r="76">
       <c r="A76" s="12" t="inlineStr">
         <is>
-          <t>C29369</t>
+          <t>C29362</t>
         </is>
       </c>
       <c r="B76" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29362</t>
         </is>
       </c>
       <c r="C76" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-01</t>
+          <t>SF-INV-03</t>
         </is>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Apply Invoice to Selected POs (Story 9)</t>
         </is>
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
+          <t>Verify Apply Invoice is scoped per vendor, not offered for the vendorless group, and allows a reused invoice number</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G76" s="14" t="inlineStr">
@@ -4657,27 +4657,27 @@
     <row r="77">
       <c r="A77" s="12" t="inlineStr">
         <is>
-          <t>C29370</t>
+          <t>C29363</t>
         </is>
       </c>
       <c r="B77" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29363</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-02</t>
+          <t>SF-PNFIX-01</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>Receive Button on WO POs (Story 11)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
+          <t>Verify a no-number part shows 'Missing part number' with Edit → enter → save that persists immediately</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -4704,17 +4704,17 @@
     <row r="78">
       <c r="A78" s="12" t="inlineStr">
         <is>
-          <t>C29371</t>
+          <t>C29369</t>
         </is>
       </c>
       <c r="B78" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29369</t>
         </is>
       </c>
       <c r="C78" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-03</t>
+          <t>SF-RCV-01</t>
         </is>
       </c>
       <c r="D78" s="12" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="E78" s="12" t="inlineStr">
         <is>
-          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
+          <t>Verify a Receive action appears on WO-originated POs in both the PO list and the PO detail card</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -4751,32 +4751,32 @@
     <row r="79">
       <c r="A79" s="12" t="inlineStr">
         <is>
-          <t>C29372</t>
+          <t>C29370</t>
         </is>
       </c>
       <c r="B79" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29370</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-04</t>
+          <t>SF-RCV-02</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
+          <t>Verify the Receive action opens the shared Accept Delivery surface</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G79" s="14" t="inlineStr">
@@ -4798,27 +4798,27 @@
     <row r="80">
       <c r="A80" s="12" t="inlineStr">
         <is>
-          <t>C29377</t>
+          <t>C29371</t>
         </is>
       </c>
       <c r="B80" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29371</t>
         </is>
       </c>
       <c r="C80" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-09</t>
+          <t>SF-RCV-03</t>
         </is>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Receive Button on WO POs (Story 11)</t>
         </is>
       </c>
       <c r="E80" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
+          <t>Verify the Receive action is hidden for office/readonly users and for fulfilled POs</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
@@ -4845,17 +4845,17 @@
     <row r="81">
       <c r="A81" s="12" t="inlineStr">
         <is>
-          <t>C29440</t>
+          <t>C29372</t>
         </is>
       </c>
       <c r="B81" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29372</t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-10</t>
+          <t>SF-RCV-04</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
+          <t>Verify the existing Accept Delivery screen groups by vendor with per-group invoice #, date, tax, note and Receive</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -4892,32 +4892,32 @@
     <row r="82">
       <c r="A82" s="12" t="inlineStr">
         <is>
-          <t>C29378</t>
+          <t>C29377</t>
         </is>
       </c>
       <c r="B82" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29377</t>
         </is>
       </c>
       <c r="C82" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-01</t>
+          <t>SF-RCV-09</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E82" s="12" t="inlineStr">
         <is>
-          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
+          <t>Verify a 'received more than ordered' warning appears when received quantity exceeds ordered quantity</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G82" s="14" t="inlineStr">
@@ -4939,32 +4939,32 @@
     <row r="83">
       <c r="A83" s="12" t="inlineStr">
         <is>
-          <t>C29383</t>
+          <t>C29440</t>
         </is>
       </c>
       <c r="B83" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29440</t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-01</t>
+          <t>SF-RCV-10</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
+          <t>Verify cost is editable on the Accept Delivery screen when $0 or missing (parity with Bulk Receive)</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G83" s="14" t="inlineStr">
@@ -4979,39 +4979,39 @@
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: 'Waiting on Parts' column is off by default (toggle_column_unreceivedPartRequestsCount), enabled from the column selector - Story 14 built, verified prior runs (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon. FLAG: exact column-selector label not re-surfaced this run (width_normal control did not open the selector panel).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="12" t="inlineStr">
         <is>
-          <t>C29384</t>
+          <t>C29378</t>
         </is>
       </c>
       <c r="B84" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29378</t>
         </is>
       </c>
       <c r="C84" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-02</t>
+          <t>SF-VEND-01</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
         <is>
-          <t>Waiting on Parts Column (Story 14)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E84" s="12" t="inlineStr">
         <is>
-          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
+          <t>Verify the vendor-missing group provides a vendor dropdown that assigns a vendor at PO level and saves it</t>
         </is>
       </c>
       <c r="F84" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G84" s="14" t="inlineStr">
@@ -5026,24 +5026,24 @@
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: clicking the Waiting on Parts count opens the Bulk Receive page for the WO's first unreceived PO - verified prior (case 29384 pushed 2026-07-09/10).</t>
+          <t>Wording+VIU 2026-07-13: receive surfaces re-confirmed live (RCV-po-list.png / RCV-bulk-receive.png) — PO list 'Purchase Orders'+'Receive'; Bulk Receive 'Receive Vendor Parts'/'Back To Purchase Orders'/vendor groups/'Apply to selected POs'/'Invoice Date'/'Tax'/'Receive All'. Behavior per prior VIU (BATCH 7 / 2026-07-10, FV screenshots). (build labels confirmed match; wording corrected where the build differs.)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="12" t="inlineStr">
         <is>
-          <t>C29385</t>
+          <t>C29383</t>
         </is>
       </c>
       <c r="B85" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29383</t>
         </is>
       </c>
       <c r="C85" s="12" t="inlineStr">
         <is>
-          <t>SF-WOP-03</t>
+          <t>SF-WOP-01</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
+          <t>Verify an optional 'Waiting on Parts' column can be enabled from the column selector and shows the unreceived-parts count per WO</t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G85" s="14" t="inlineStr">
@@ -5073,39 +5073,39 @@
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: WO with nothing to receive shows '—' (no link) - verified prior (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon.</t>
+          <t>Wording+VIU 2026-07-13: 'Waiting on Parts' column is off by default (toggle_column_unreceivedPartRequestsCount), enabled from the column selector - Story 14 built, verified prior runs (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon. FLAG: exact column-selector label not re-surfaced this run (width_normal control did not open the selector panel).</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="12" t="inlineStr">
         <is>
-          <t>C29386</t>
+          <t>C29384</t>
         </is>
       </c>
       <c r="B86" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29384</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-01</t>
+          <t>SF-WOP-02</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E86" s="12" t="inlineStr">
         <is>
-          <t>Verify the Require Review setting drives the review flow when turned on</t>
+          <t>Verify clicking the Waiting on Parts count opens Accept Delivery for the WO's first unreceived PO</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G86" s="14" t="inlineStr">
@@ -5120,39 +5120,39 @@
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): with Require Review ON, completing routes into the review flow (Send To Review), not a direct complete.</t>
+          <t>Wording+VIU 2026-07-13: clicking the Waiting on Parts count opens the Bulk Receive page for the WO's first unreceived PO - verified prior (case 29384 pushed 2026-07-09/10).</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="12" t="inlineStr">
         <is>
-          <t>C29387</t>
+          <t>C29385</t>
         </is>
       </c>
       <c r="B87" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29385</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-02</t>
+          <t>SF-WOP-03</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Waiting on Parts Column (Story 14)</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Verify the completion action reads 'Send To Review' when Require Review is on</t>
+          <t>Verify a work order with nothing to receive shows '—' with no link in the Waiting on Parts column</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -5167,24 +5167,24 @@
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15827/S2-15783 live, Require Review ON): the primary action button = 'Send To Review' on BOTH ready and part-bearing WOs (it replaces 'Complete Work Order'). For a part-bearing WO, clicking 'Send To Review' opens a dialog HEADED 'Complete &amp; Send to Review' (body 'N part waiting to receive'; buttons Cancel / Receive Parts / Send To Review). So 'Complete &amp; Send to Review' is the review-dialog HEADER, not the button; the clickable CTA is 'Send To Review'. Title corrected + expected #2 corrected (a part-bearing WO does NOT read 'Complete Work Order'). Evidence: screenshots/relevance-fix-2026-07-13/.</t>
+          <t>Wording+VIU 2026-07-13: WO with nothing to receive shows '—' (no link) - verified prior (BATCH 7). Stripped 'EXPECTED PER SPEC' jargon.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="12" t="inlineStr">
         <is>
-          <t>C29388</t>
+          <t>C29386</t>
         </is>
       </c>
       <c r="B88" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29386</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-03</t>
+          <t>SF-REV-01</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -5194,12 +5194,12 @@
       </c>
       <c r="E88" s="12" t="inlineStr">
         <is>
-          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
+          <t>Verify the Require Review setting drives the review flow when turned on</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -5214,24 +5214,24 @@
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: the completion Details modal shows Mileage + Engine Hours and no VIN field (confirmed live on the review-off modal S2-15827; review-on captures VIN in Mark Reviewed per SF-REV-06). Upgraded from Pending - the field set is now confirmed.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): with Require Review ON, completing routes into the review flow (Send To Review), not a direct complete.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="12" t="inlineStr">
         <is>
-          <t>C29389</t>
+          <t>C29387</t>
         </is>
       </c>
       <c r="B89" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29387</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-04</t>
+          <t>SF-REV-02</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -5241,12 +5241,12 @@
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
+          <t>Verify the completion action reads 'Send To Review' when Require Review is on</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
@@ -5261,24 +5261,24 @@
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: 'Receive Parts' opens the shared receive page (not an inline modal) in the review flow — verified prior drive (FV-rev04-receivestep/afterreceive.png, 2026-07-10); review flow re-confirmed live this run.</t>
+          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15827/S2-15783 live, Require Review ON): the primary action button = 'Send To Review' on BOTH ready and part-bearing WOs (it replaces 'Complete Work Order'). For a part-bearing WO, clicking 'Send To Review' opens a dialog HEADED 'Complete &amp; Send to Review' (body 'N part waiting to receive'; buttons Cancel / Receive Parts / Send To Review). So 'Complete &amp; Send to Review' is the review-dialog HEADER, not the button; the clickable CTA is 'Send To Review'. Title corrected + expected #2 corrected (a part-bearing WO does NOT read 'Complete Work Order'). Evidence: screenshots/relevance-fix-2026-07-13/.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="12" t="inlineStr">
         <is>
-          <t>C29390</t>
+          <t>C29388</t>
         </is>
       </c>
       <c r="B90" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29388</t>
         </is>
       </c>
       <c r="C90" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-05</t>
+          <t>SF-REV-03</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E90" s="12" t="inlineStr">
         <is>
-          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
+          <t>Verify the Details step collects only mileage and engine hours when review is on (VIN captured later by reviewer)</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G90" s="14" t="inlineStr">
@@ -5308,24 +5308,24 @@
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15823/S2-15827 live, Require Review ON): the confirm button is 'Send To Review' (NOT 'Complete &amp; Send to Review' - that is the dialog HEADER for a part-bearing WO). Send To Review -&gt; status 'Review' + 'Ready for Review' indicator; lines lock to Complete. (amber colour per design; status text 'Review' confirmed.) Step 1 label corrected. Evidence: screenshots/relevance-fix-2026-07-13/.</t>
+          <t>Wording+VIU 2026-07-13: the completion Details modal shows Mileage + Engine Hours and no VIN field (confirmed live on the review-off modal S2-15827; review-on captures VIN in Mark Reviewed per SF-REV-06). Upgraded from Pending - the field set is now confirmed.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="12" t="inlineStr">
         <is>
-          <t>C29391</t>
+          <t>C29389</t>
         </is>
       </c>
       <c r="B91" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29389</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-06</t>
+          <t>SF-REV-04</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
+          <t>Verify 'Receive Parts' routes to the shared receive page (no inline modal) in the review flow</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G91" s="14" t="inlineStr">
@@ -5355,24 +5355,24 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: Mark Reviewed action confirmed live (S2-15823). The VIN-required dialog surfaces only when the WO lacks a valid VIN; every test WO this run had a VIN (so Mark Reviewed completed directly - see SF-REV-08). VIN-required dialog verified prior run 2026-07-06 (S16-04-review-wizard.png). Stripped dev test-id 'input_review_vin' from tester wording.</t>
+          <t>Wording+VIU 2026-07-13: 'Receive Parts' opens the shared receive page (not an inline modal) in the review flow — verified prior drive (FV-rev04-receivestep/afterreceive.png, 2026-07-10); review flow re-confirmed live this run.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="12" t="inlineStr">
         <is>
-          <t>C29392</t>
+          <t>C29390</t>
         </is>
       </c>
       <c r="B92" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29390</t>
         </is>
       </c>
       <c r="C92" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-07</t>
+          <t>SF-REV-05</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -5382,12 +5382,12 @@
       </c>
       <c r="E92" s="12" t="inlineStr">
         <is>
-          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
+          <t>Verify Send to Review moves the WO to Review (amber) with a 'Ready for Review' banner and locks lines to Complete</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G92" s="14" t="inlineStr">
@@ -5402,24 +5402,24 @@
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): on Send To Review the lines lock to Complete and inventory is auto-picked (design; review state confirmed live).</t>
+          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15823/S2-15827 live, Require Review ON): the confirm button is 'Send To Review' (NOT 'Complete &amp; Send to Review' - that is the dialog HEADER for a part-bearing WO). Send To Review -&gt; status 'Review' + 'Ready for Review' indicator; lines lock to Complete. (amber colour per design; status text 'Review' confirmed.) Step 1 label corrected. Evidence: screenshots/relevance-fix-2026-07-13/.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="12" t="inlineStr">
         <is>
-          <t>C29393</t>
+          <t>C29391</t>
         </is>
       </c>
       <c r="B93" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29391</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-08</t>
+          <t>SF-REV-06</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
+          <t>Verify the Mark Reviewed dialog captures VIN (required) and disables Confirm until VIN is entered</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="G93" s="14" t="inlineStr">
@@ -5444,29 +5444,29 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
+          <t>READY (VIU-Verified)</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): Mark Reviewed (VIN present) signs off and moves the WO directly Review -&gt; Complete; no distinct 'Reviewed' holding state and no separate final Complete click (S2-15823 went Review-&gt;Complete).</t>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed action confirmed live (S2-15823). The VIN-required dialog surfaces only when the WO lacks a valid VIN; every test WO this run had a VIN (so Mark Reviewed completed directly - see SF-REV-08). VIN-required dialog verified prior run 2026-07-06 (S16-04-review-wizard.png). Stripped dev test-id 'input_review_vin' from tester wording.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>C29394</t>
+          <t>C29392</t>
         </is>
       </c>
       <c r="B94" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29392</t>
         </is>
       </c>
       <c r="C94" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-09</t>
+          <t>SF-REV-07</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="E94" s="12" t="inlineStr">
         <is>
-          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
+          <t>Verify on Send to Review lines lock to Complete and inventory is auto-picked</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G94" s="14" t="inlineStr">
@@ -5496,24 +5496,24 @@
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: Mark Reviewed gated by Review Work Orders (woReviewWorkOrders) per fresh roles matrix (roles-matrix-2026-07-13.md); role without it sees Mark Reviewed disabled + 'Awaiting review'; self-review allowed when the role holds the permission (Milos ruling). Review flow re-confirmed live.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): on Send To Review the lines lock to Complete and inventory is auto-picked (design; review state confirmed live).</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="12" t="inlineStr">
         <is>
-          <t>C29395</t>
+          <t>C29393</t>
         </is>
       </c>
       <c r="B95" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29393</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-10</t>
+          <t>SF-REV-08</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
+          <t>Verify Confirm Review signs off and completes the work order directly (no distinct Reviewed holding state)</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G95" s="14" t="inlineStr">
@@ -5538,29 +5538,29 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field absent — descope or bug?</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8, Q4 — Distinct 'Reviewed' state before final Complete — expected or single-step?</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: Mark Reviewed uses VIN / Serial # only, no review note field (V2.4 Δ4 confirmed; SF-REV-06/10 were already note-free). Dialog surfaces when VIN missing (verified prior 2026-07-06); Mark Reviewed action re-confirmed live this run.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15823 live, Require Review ON): Mark Reviewed (VIN present) signs off and moves the WO directly Review -&gt; Complete; no distinct 'Reviewed' holding state and no separate final Complete click (S2-15823 went Review-&gt;Complete).</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="12" t="inlineStr">
         <is>
-          <t>C29397</t>
+          <t>C29394</t>
         </is>
       </c>
       <c r="B96" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29394</t>
         </is>
       </c>
       <c r="C96" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-12</t>
+          <t>SF-REV-09</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="E96" s="12" t="inlineStr">
         <is>
-          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
+          <t>Verify Mark Reviewed is gated by the Review Work Orders permission and disabled for a role without it</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
@@ -5590,24 +5590,24 @@
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: 'Ready for Review' indicator confirmed on a WO in Review (S2-15823). Reviewer-queue surfacing on the WO list per design; the 'Ready for Review' label is build-accurate.</t>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed gated by Review Work Orders (woReviewWorkOrders) per fresh roles matrix (roles-matrix-2026-07-13.md); role without it sees Mark Reviewed disabled + 'Awaiting review'; self-review allowed when the role holds the permission (Milos ruling). Review flow re-confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="12" t="inlineStr">
         <is>
-          <t>C29398</t>
+          <t>C29395</t>
         </is>
       </c>
       <c r="B97" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29395</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-13</t>
+          <t>SF-REV-10</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t>Verify all lines must be approved before Send To Review (the 'Send To Review' action is disabled until every line is approved)</t>
+          <t>Verify the Mark Reviewed dialog includes VIN / Serial # (required) with no review note field</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -5632,39 +5632,39 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>READY (VIU-Verified)</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q7 — Optional review-note field absent — descope or bug?</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15783 live, Require Review ON, one unapproved line): the 'Send To Review' button is DISABLED (isDisabled=true) while a line is unapproved; it becomes usable only after every line is approved. Step label corrected ('Complete &amp; Send to Review' -&gt; 'Send To Review'; the clickable action is 'Send To Review') and expected made build-accurate (the button is disabled rather than showing an error message). Evidence: screenshots/relevance-fix-2026-07-13/neg-5b653a02-sendtoreview-blocked.png.</t>
+          <t>Wording+VIU 2026-07-13: Mark Reviewed uses VIN / Serial # only, no review note field (V2.4 Δ4 confirmed; SF-REV-06/10 were already note-free). Dialog surfaces when VIN missing (verified prior 2026-07-06); Mark Reviewed action re-confirmed live this run.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="12" t="inlineStr">
         <is>
-          <t>C29401</t>
+          <t>C29397</t>
         </is>
       </c>
       <c r="B98" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29397</t>
         </is>
       </c>
       <c r="C98" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-01</t>
+          <t>SF-REV-12</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E98" s="12" t="inlineStr">
         <is>
-          <t>Verify the work order primary button reads 'Create Work Order'</t>
+          <t>Verify a 'Ready for Review' list filter/column surfaces the reviewer queue</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
@@ -5684,34 +5684,34 @@
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 (UX-workorders-list.png): the Work Orders create form's primary button reads 'Create Work Order' (confirmed on /workorders list Create Work Order button).</t>
+          <t>Wording+VIU 2026-07-13: 'Ready for Review' indicator confirmed on a WO in Review (S2-15823). Reviewer-queue surfacing on the WO list per design; the 'Ready for Review' label is build-accurate.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="12" t="inlineStr">
         <is>
-          <t>C29402</t>
+          <t>C29398</t>
         </is>
       </c>
       <c r="B99" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29398</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-02</t>
+          <t>SF-REV-13</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
+          <t>Verify all lines must be approved before Send To Review (the 'Send To Review' action is disabled until every line is approved)</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -5731,24 +5731,24 @@
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: required fields collected in the centralized 'Complete Work Order' modal (Mileage + Engine Hours; no VIN field in the modal - see SF-COMP-16/SF-VAL-02 build finding); tech story handled separately.</t>
+          <t>Wording+VIU 2026-07-13 + relevance-fix re-VIU 2026-07-13 (S2-15783 live, Require Review ON, one unapproved line): the 'Send To Review' button is DISABLED (isDisabled=true) while a line is unapproved; it becomes usable only after every line is approved. Step label corrected ('Complete &amp; Send to Review' -&gt; 'Send To Review'; the clickable action is 'Send To Review') and expected made build-accurate (the button is disabled rather than showing an error message). Evidence: screenshots/relevance-fix-2026-07-13/neg-5b653a02-sendtoreview-blocked.png.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="12" t="inlineStr">
         <is>
-          <t>C29403</t>
+          <t>C29401</t>
         </is>
       </c>
       <c r="B100" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29401</t>
         </is>
       </c>
       <c r="C100" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-03</t>
+          <t>SF-UX-01</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="E100" s="12" t="inlineStr">
         <is>
-          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
+          <t>Verify the work order primary button reads 'Create Work Order'</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -5778,39 +5778,39 @@
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: success screen shows WO number + total with 'Done' and 'Go To Invoice'; invoice number appears on the Finance step (confirmed live via SF-COMP drives S2-15825 'Invoice total $434.95').</t>
+          <t>Wording+VIU 2026-07-13 (UX-workorders-list.png): the Work Orders create form's primary button reads 'Create Work Order' (confirmed on /workorders list Create Work Order button).</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="12" t="inlineStr">
         <is>
-          <t>C29405</t>
+          <t>C29402</t>
         </is>
       </c>
       <c r="B101" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29402</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-01</t>
+          <t>SF-UX-02</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
+          <t>Verify required fields at completion appear in a centralized center modal and the tech story is NOT in that modal</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
@@ -5825,34 +5825,34 @@
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Settings gate re-driven live: Technician POST /api/organizations/settings/change = 403, Admin = 200 (App Settings / settingsApp atom, BE-enforced). FE redirects non-admin from the settings route.</t>
+          <t>Wording+VIU 2026-07-13: required fields collected in the centralized 'Complete Work Order' modal (Mileage + Engine Hours; no VIN field in the modal - see SF-COMP-16/SF-VAL-02 build finding); tech story handled separately.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="12" t="inlineStr">
         <is>
-          <t>C29406</t>
+          <t>C29403</t>
         </is>
       </c>
       <c r="B102" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29403</t>
         </is>
       </c>
       <c r="C102" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-02</t>
+          <t>SF-UX-03</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
-          <t>Permissions</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E102" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can complete a work order (Simple completion)</t>
+          <t>Verify the success screen shows WO number and total with Done and Go to Invoice, and the invoice number is on the Finance step</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -5872,24 +5872,24 @@
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Complete-WO gate = workOrdersCreateAndEdit; roles that can complete (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager) vs cannot (Technician, Parts Tech, Office, Sales Rep, Time Clock) match the matrix. FE confirmed (Complete Work Order button hidden for Technician, prior TECH-wo-detail.png); BE does not enforce WO completion (documented gap, see SF-PERM-06).</t>
+          <t>Wording+VIU 2026-07-13: success screen shows WO number + total with 'Done' and 'Go To Invoice'; invoice number appears on the Finance step (confirmed live via SF-COMP drives S2-15825 'Invoice total $434.95').</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="12" t="inlineStr">
         <is>
-          <t>C29407</t>
+          <t>C29405</t>
         </is>
       </c>
       <c r="B103" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29405</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-03</t>
+          <t>SF-PERM-01</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can perform Bulk Receive</t>
+          <t>Verify only owner/admin can view and modify Work Order settings (non-admin blocked)</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G103" s="14" t="inlineStr">
@@ -5919,24 +5919,24 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Bulk Receive gate = vendorOrderManagementCreateAndEdit + seeFinancialData; per-role result (Admin/SM/SrSA/SA/Foreman/Parts Manager/Parts Tech can; Office view-only; Sales Rep &amp; Time Clock cannot) matches the matrix. Stories 7/8 confirmed BUILT.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Settings gate re-driven live: Technician POST /api/organizations/settings/change = 403, Admin = 200 (App Settings / settingsApp atom, BE-enforced). FE redirects non-admin from the settings route.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="12" t="inlineStr">
         <is>
-          <t>C29408</t>
+          <t>C29406</t>
         </is>
       </c>
       <c r="B104" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29406</t>
         </is>
       </c>
       <c r="C104" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-04</t>
+          <t>SF-PERM-02</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E104" s="12" t="inlineStr">
         <is>
-          <t>Verify which roles can Mark Reviewed (sign off)</t>
+          <t>Verify which roles can complete a work order (Simple completion)</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
@@ -5966,24 +5966,24 @@
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Mark Reviewed gate = woReviewWorkOrders (not open-to-all). Self-review allowed when the role holds the permission (Milos ruling 2026-07-10; no reviewer!=completer identity block). Per-role has/lacks matches the matrix.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Complete-WO gate = workOrdersCreateAndEdit; roles that can complete (Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager) vs cannot (Technician, Parts Tech, Office, Sales Rep, Time Clock) match the matrix. FE confirmed (Complete Work Order button hidden for Technician, prior TECH-wo-detail.png); BE does not enforce WO completion (documented gap, see SF-PERM-06).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="12" t="inlineStr">
         <is>
-          <t>C29409</t>
+          <t>C29407</t>
         </is>
       </c>
       <c r="B105" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29407</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-05</t>
+          <t>SF-PERM-03</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Verify the PO Receive button is hidden for office/readonly users</t>
+          <t>Verify which roles can perform Bulk Receive</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -6013,24 +6013,24 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). PO Receive gate = woOrderParts (Order Parts); Office lacks it -&gt; no Receive on PO list/detail. FE confirmed (Technician redirected from /parts/orders, prior TECH-po-list.png).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Bulk Receive gate = vendorOrderManagementCreateAndEdit + seeFinancialData; per-role result (Admin/SM/SrSA/SA/Foreman/Parts Manager/Parts Tech can; Office view-only; Sales Rep &amp; Time Clock cannot) matches the matrix. Stories 7/8 confirmed BUILT.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="12" t="inlineStr">
         <is>
-          <t>C29410</t>
+          <t>C29408</t>
         </is>
       </c>
       <c r="B106" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29408</t>
         </is>
       </c>
       <c r="C106" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-06</t>
+          <t>SF-PERM-04</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="E106" s="12" t="inlineStr">
         <is>
-          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
+          <t>Verify which roles can Mark Reviewed (sign off)</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
@@ -6060,24 +6060,24 @@
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Live: BE enforces the distinct settings atom (Technician settings save -&gt; 403, Admin -&gt; 200) but does NOT enforce the WO-completion / review atoms (documented 'app blocks / backend allows' gap, draft TICKET 2). v1 pass = app-level restriction (Milos Round-2 ruling). Cleaned tester wording: removed backend enum names and internal 'UI pass/API fail' phrasing.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Mark Reviewed gate = woReviewWorkOrders (not open-to-all). Self-review allowed when the role holds the permission (Milos ruling 2026-07-10; no reviewer!=completer identity block). Per-role has/lacks matches the matrix.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="12" t="inlineStr">
         <is>
-          <t>C29411</t>
+          <t>C29409</t>
         </is>
       </c>
       <c r="B107" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29409</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-07</t>
+          <t>SF-PERM-05</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
+          <t>Verify the PO Receive button is hidden for office/readonly users</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G107" s="14" t="inlineStr">
@@ -6107,24 +6107,24 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Review sign-off = Review Work Orders (woReviewWorkOrders), custom-role gated, not open-to-all for v1. Self-review allowed when the role holds the permission (Milos ruling 2026-07-10).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). PO Receive gate = woOrderParts (Order Parts); Office lacks it -&gt; no Receive on PO list/detail. FE confirmed (Technician redirected from /parts/orders, prior TECH-po-list.png).</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="12" t="inlineStr">
         <is>
-          <t>C29412</t>
+          <t>C29410</t>
         </is>
       </c>
       <c r="B108" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29410</t>
         </is>
       </c>
       <c r="C108" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-08</t>
+          <t>SF-PERM-06</t>
         </is>
       </c>
       <c r="D108" s="12" t="inlineStr">
@@ -6134,12 +6134,12 @@
       </c>
       <c r="E108" s="12" t="inlineStr">
         <is>
-          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
+          <t>Verify permission gating of Simple-Flow settings and work-order actions (UI gating is the v1 pass criterion)</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G108" s="14" t="inlineStr">
@@ -6154,24 +6154,24 @@
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Positive self-review: a role holding woReviewWorkOrders may Mark Reviewed a WO it completed (permission-gated only, no identity block). A role lacking it cannot. Matches matrix + Milos ruling.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Live: BE enforces the distinct settings atom (Technician settings save -&gt; 403, Admin -&gt; 200) but does NOT enforce the WO-completion / review atoms (documented 'app blocks / backend allows' gap, draft TICKET 2). v1 pass = app-level restriction (Milos Round-2 ruling). Cleaned tester wording: removed backend enum names and internal 'UI pass/API fail' phrasing.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="12" t="inlineStr">
         <is>
-          <t>C29413</t>
+          <t>C29411</t>
         </is>
       </c>
       <c r="B109" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29411</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-09</t>
+          <t>SF-PERM-07</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
+          <t>Verify review sign-off is governed by the Review Work Orders custom-role permission (not open to all)</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G109" s="14" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Technician lacks seeFinancialData (confirmed live: Tech 6 perms, no seeFinancialData) so cannot add a vendorless / no-part-number part (sell price mandatory, gated by See Financial Data). FE gate holds; BE financial-gate on part-add not re-driven this session.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Review sign-off = Review Work Orders (woReviewWorkOrders), custom-role gated, not open-to-all for v1. Self-review allowed when the role holds the permission (Milos ruling 2026-07-10).</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="12" t="inlineStr">
         <is>
-          <t>C29414</t>
+          <t>C29412</t>
         </is>
       </c>
       <c r="B110" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29412</t>
         </is>
       </c>
       <c r="C110" s="12" t="inlineStr">
         <is>
-          <t>SF-PERM-10</t>
+          <t>SF-PERM-08</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="E110" s="12" t="inlineStr">
         <is>
-          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
+          <t>Verify a user who holds the Mark Reviewed permission can Mark Reviewed a work order they completed</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
@@ -6248,34 +6248,34 @@
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Per-role completion matrix (Complete gate = workOrdersCreateAndEdit) matches roles-matrix-2026-07-13.md exactly: HAS = Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager; LACKS = Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Positive self-review: a role holding woReviewWorkOrders may Mark Reviewed a WO it completed (permission-gated only, no identity block). A role lacking it cannot. Matches matrix + Milos ruling.</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="12" t="inlineStr">
         <is>
-          <t>C29415</t>
+          <t>C29413</t>
         </is>
       </c>
       <c r="B111" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29413</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-01</t>
+          <t>SF-PERM-09</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required mileage is missing</t>
+          <t>Verify a Technician cannot add a vendorless / no-part-number part (lacks See Financial Data)</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -6295,39 +6295,39 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Mileage ON): the completion Details modal shows a Mileage field; leaving it empty and pressing 'Complete Work Order' shows a 'required field' error and completion does not proceed. Settings restored byte-identical.</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Technician lacks seeFinancialData (confirmed live: Tech 6 perms, no seeFinancialData) so cannot add a vendorless / no-part-number part (sell price mandatory, gated by See Financial Data). FE gate holds; BE financial-gate on part-add not re-driven this session.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="12" t="inlineStr">
         <is>
-          <t>C29417</t>
+          <t>C29414</t>
         </is>
       </c>
       <c r="B112" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29414</t>
         </is>
       </c>
       <c r="C112" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-03</t>
+          <t>SF-PERM-10</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
         <is>
-          <t>Validation / Edge</t>
+          <t>Permissions</t>
         </is>
       </c>
       <c r="E112" s="12" t="inlineStr">
         <is>
-          <t>Verify completion is blocked when required engine hours are missing</t>
+          <t>Verify the Complete Work Order action follows the per-role completion permission matrix</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G112" s="14" t="inlineStr">
@@ -6342,24 +6342,24 @@
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Engine Hours ON): the completion Details modal shows an Engine Hours field; empty -&gt; 'required field' error, completion blocked. Same modal as SF-VAL-01 (Mileage + Engine Hours).</t>
+          <t>Wording+VIU 2026-07-13: role expectation re-verified against the fresh live roles matrix (roles-matrix-2026-07-13.md; GET /api/roles/{id} + /api/auth/me/fe-permissions, no system-role drift). Per-role completion matrix (Complete gate = workOrdersCreateAndEdit) matches roles-matrix-2026-07-13.md exactly: HAS = Admin, Service Manager, Senior SA, Service Advisor, Foreman, Parts Manager; LACKS = Technician, Parts Tech, Office, Sales Rep, Time Clock.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="12" t="inlineStr">
         <is>
-          <t>C29418</t>
+          <t>C29415</t>
         </is>
       </c>
       <c r="B113" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29415</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-04</t>
+          <t>SF-VAL-01</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
+          <t>Verify completion is blocked when required mileage is missing</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G113" s="14" t="inlineStr">
@@ -6389,24 +6389,24 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: tech-story modal Next/Continue disabled while the story textarea is empty (Require Tech Story gate) - behavior per prior VIU; tech-story requirement is a Work Orders setting toggle (see SF-SET-15).</t>
+          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Mileage ON): the completion Details modal shows a Mileage field; leaving it empty and pressing 'Complete Work Order' shows a 'required field' error and completion does not proceed. Settings restored byte-identical.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="12" t="inlineStr">
         <is>
-          <t>C29419</t>
+          <t>C29417</t>
         </is>
       </c>
       <c r="B114" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29417</t>
         </is>
       </c>
       <c r="C114" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-05</t>
+          <t>SF-VAL-03</t>
         </is>
       </c>
       <c r="D114" s="12" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="E114" s="12" t="inlineStr">
         <is>
-          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
+          <t>Verify completion is blocked when required engine hours are missing</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G114" s="14" t="inlineStr">
@@ -6436,24 +6436,24 @@
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: required-invoice receive blocked without a vendor invoice number - verified prior drive (FV-val05-noinvoice/withinvoice.png, 2026-07-10). Require Vendor Invoice Number gate.</t>
+          <t>Wording+VIU 2026-07-13 (S2-15783 live, Require Engine Hours ON): the completion Details modal shows an Engine Hours field; empty -&gt; 'required field' error, completion blocked. Same modal as SF-VAL-01 (Mileage + Engine Hours).</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="12" t="inlineStr">
         <is>
-          <t>C29421</t>
+          <t>C29418</t>
         </is>
       </c>
       <c r="B115" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29418</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-07</t>
+          <t>SF-VAL-04</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -6463,7 +6463,7 @@
       </c>
       <c r="E115" s="12" t="inlineStr">
         <is>
-          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+          <t>Verify the tech-story Next/Continue button stays disabled while the story textarea is empty</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
@@ -6483,24 +6483,24 @@
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: Confirm Review disabled until VIN entered in the Mark Reviewed dialog (surfaces when the WO lacks a valid VIN) - same gate as SF-REV-06; Mark Reviewed action confirmed live this run, VIN-required dialog per prior 2026-07-06.</t>
+          <t>Wording+VIU 2026-07-13: tech-story modal Next/Continue disabled while the story textarea is empty (Require Tech Story gate) - behavior per prior VIU; tech-story requirement is a Work Orders setting toggle (see SF-SET-15).</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="12" t="inlineStr">
         <is>
-          <t>C29422</t>
+          <t>C29419</t>
         </is>
       </c>
       <c r="B116" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29419</t>
         </is>
       </c>
       <c r="C116" s="12" t="inlineStr">
         <is>
-          <t>SF-VAL-08</t>
+          <t>SF-VAL-05</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="E116" s="12" t="inlineStr">
         <is>
-          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+          <t>Verify a required-invoice receive is blocked without a vendor invoice number</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G116" s="14" t="inlineStr">
@@ -6530,52 +6530,146 @@
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: re-completing after cancel creates no duplicate POs (idempotent) - verified prior (2026-07-08); consistent with SF-COMP-15/23.</t>
+          <t>Wording+VIU 2026-07-13: required-invoice receive blocked without a vendor invoice number - verified prior drive (FV-val05-noinvoice/withinvoice.png, 2026-07-10). Require Vendor Invoice Number gate.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="12" t="inlineStr">
         <is>
+          <t>C29421</t>
+        </is>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29421</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-07</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="inlineStr">
+        <is>
+          <t>Verify Confirm Review is disabled until a VIN is entered in the Mark Reviewed dialog</t>
+        </is>
+      </c>
+      <c r="F117" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G117" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H117" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: Confirm Review disabled until VIN entered in the Mark Reviewed dialog (surfaces when the WO lacks a valid VIN) - same gate as SF-REV-06; Mark Reviewed action confirmed live this run, VIN-required dialog per prior 2026-07-06.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>C29422</t>
+        </is>
+      </c>
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29422</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>SF-VAL-08</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Validation / Edge</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="inlineStr">
+        <is>
+          <t>Verify re-completing after cancelling does not create duplicate POs</t>
+        </is>
+      </c>
+      <c r="F118" s="12" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H118" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>Wording+VIU 2026-07-13: re-completing after cancel creates no duplicate POs (idempotent) - verified prior (2026-07-08); consistent with SF-COMP-15/23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
           <t>C29424</t>
         </is>
       </c>
-      <c r="B117" s="13" t="inlineStr">
+      <c r="B119" s="13" t="inlineStr">
         <is>
           <t>https://shopview.testrail.io/index.php?/cases/view/29424</t>
         </is>
       </c>
-      <c r="C117" s="12" t="inlineStr">
+      <c r="C119" s="12" t="inlineStr">
         <is>
           <t>SF-VAL-10</t>
         </is>
       </c>
-      <c r="D117" s="12" t="inlineStr">
+      <c r="D119" s="12" t="inlineStr">
         <is>
           <t>Validation / Edge</t>
         </is>
       </c>
-      <c r="E117" s="12" t="inlineStr">
+      <c r="E119" s="12" t="inlineStr">
         <is>
           <t>Verify the same vendor invoice number can be reused across POs (uniqueness relaxed)</t>
         </is>
       </c>
-      <c r="F117" s="12" t="inlineStr">
+      <c r="F119" s="12" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="G117" s="14" t="inlineStr">
-        <is>
-          <t>VIU-Verified</t>
-        </is>
-      </c>
-      <c r="H117" s="12" t="inlineStr">
-        <is>
-          <t>READY (VIU-Verified)</t>
-        </is>
-      </c>
-      <c r="I117" s="12" t="inlineStr">
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>VIU-Verified</t>
+        </is>
+      </c>
+      <c r="H119" s="12" t="inlineStr">
+        <is>
+          <t>READY (VIU-Verified)</t>
+        </is>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
         <is>
           <t>Wording+VIU 2026-07-13: the same vendor invoice number can be reused across POs (uniqueness relaxed) - verified prior (2026-07-10, Story 9 apply-invoice).</t>
         </is>
@@ -6699,6 +6793,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B116" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B119" r:id="rId118"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6710,7 +6806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6821,32 +6917,32 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>C29310</t>
+          <t>C29315</t>
         </is>
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29310</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-21</t>
+          <t>SF-CORE-03</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Core parts — Completion modal</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>Verify on a required-invoice work order an unapproved line disables the Complete Work Order button with a tooltip</t>
+          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
         </is>
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G3" s="15" t="inlineStr">
@@ -6856,39 +6952,39 @@
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
         <is>
-          <t>V2.4 Δ2 wording applied (required-invoice-only disabled Complete button + tooltip; other flows keep the active-CTA + error-message model). VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines OFF, and a WO with a Needs-Approval line; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Verifies special-order cores leave optional-invoice completion unchanged + Complete Without Receiving stays available.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>C29311</t>
+          <t>C29316</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29311</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>SF-COMP-22</t>
+          <t>SF-CORE-04</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Completion — Line approval gate</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
-          <t>Verify a manually unapproved line disables the required-invoice Complete Work Order button with a tooltip even when Auto-approve is ON</t>
+          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
         </is>
       </c>
       <c r="F4" s="12" t="inlineStr">
@@ -6903,44 +6999,44 @@
       </c>
       <c r="H4" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed the specific completion configuration and drive the wizard to Success.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
         </is>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>V2.4 Δ2 wording applied. VIU-Pending: verifying needs Require Vendor Invoice Number ON, Auto-approve Lines ON, and a line manually un-approved after add; not driven this session to avoid flipping shared settings while a tester may be active. Completion surface confirmed live 2026-07-13.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Also needs invoicing to see the 'Cores pending' invoice flag (invoicing not drivable in-harness).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="12" t="inlineStr">
         <is>
-          <t>C29315</t>
+          <t>C29317</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29315</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-03</t>
+          <t>SF-CORE-05</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Completion modal</t>
+          <t>Core parts — Invoice gate</t>
         </is>
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores leave the optional-invoice completion unchanged and Complete Without Receiving stays available</t>
+          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G5" s="15" t="inlineStr">
@@ -6955,24 +7051,24 @@
       </c>
       <c r="I5" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Verifies special-order cores leave optional-invoice completion unchanged + Complete Without Receiving stays available.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Also needs the Create Invoice gate (invoicing not drivable in-harness).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>C29316</t>
+          <t>C29318</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29316</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-04</t>
+          <t>SF-CORE-06</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
@@ -6982,7 +7078,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice shows a 'Cores pending' flag when unresolved special-order cores exist</t>
+          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -7002,34 +7098,34 @@
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Also needs invoicing to see the 'Cores pending' invoice flag (invoicing not drivable in-harness).</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Cancel-at-invoice-gate path needs invoicing (not drivable in-harness).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="12" t="inlineStr">
         <is>
-          <t>C29317</t>
+          <t>C29319</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29317</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-05</t>
+          <t>SF-CORE-07</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Required invoice (Story 4)</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>Verify resolving cores at the Create Invoice gate routes to receive the cored line then lets invoicing proceed</t>
+          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -7049,34 +7145,34 @@
       </c>
       <c r="I7" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Also needs the Create Invoice gate (invoicing not drivable in-harness).</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs the required-invoice receive round-trip with a special-order core.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>C29318</t>
+          <t>C29320</t>
         </is>
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29318</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-06</t>
+          <t>SF-CORE-08</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Invoice gate</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
         <is>
-          <t>Verify cancelling the invoice-gate core resolution leaves the WO completed, un-invoiced and cores-pending</t>
+          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -7096,39 +7192,39 @@
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Cancel-at-invoice-gate path needs invoicing (not drivable in-harness).</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs an unresolved special-order core existing only as a PartRequest + the invoice gate.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="12" t="inlineStr">
         <is>
-          <t>C29319</t>
+          <t>C29321</t>
         </is>
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29319</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-07</t>
+          <t>SF-CORE-09</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Required invoice (Story 4)</t>
+          <t>Core parts — Guardrail</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Verify special-order cores are resolved after the required-invoice Receive round-trip before Complete</t>
+          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -7143,39 +7239,39 @@
       </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs the required-invoice receive round-trip with a special-order core.</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs a part-sale WO and a service WO each with a core to compare auto-resolve vs manual Ok/Not OK.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>C29320</t>
+          <t>C29343</t>
         </is>
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29320</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-08</t>
+          <t>SF-VMIS-06</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>Vendor Missing on WO PO (Story 6)</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>Verify the invoice gate detects an unresolved special-order core that exists only as a PartRequest</t>
+          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -7185,39 +7281,39 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
         </is>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs an unresolved special-order core existing only as a PartRequest + the invoice gate.</t>
+          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. verifying reports mark Vendor-Missing POs as 'needs vendor' needs a vendor-missing PO + the reports surface; not driven this session (needs seeded vendor-missing PO).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>C29321</t>
+          <t>C29359</t>
         </is>
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29321</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>SF-CORE-09</t>
+          <t>SF-BULK-10</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Core parts — Guardrail</t>
+          <t>PO Bulk Receive Page (Story 8)</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>Verify part-sale work orders auto-resolve cores at receive while service work orders require manual Ok/Not OK</t>
+          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -7232,44 +7328,44 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO with core-charge parts, drive the completion Resolve-Cores modal + invoice-gate round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
         </is>
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: VIU-Pending (non-seedable): needs a genuine special-order (vendor-source) core, which is not seedable in-app (only the inventory core P550848 exists; a special-order core requires vendor sourcing). Needs a part-sale WO and a service WO each with a core to compare auto-resolve vs manual Ok/Not OK.</t>
+          <t>Wording+VIU 2026-07-13: needs a genuine cored part on a PO to verify the Ok/Not OK resolution after receive + core-only partial receive. A genuine special-order (vendor-source) core is not seedable in-app (see SF-CORE cluster). Bulk Receive surface confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>C29343</t>
+          <t>C29364</t>
         </is>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29343</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>SF-VMIS-06</t>
+          <t>SF-PNFIX-02</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
-          <t>Vendor Missing on WO PO (Story 6)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>Verify reports mark Vendor Missing POs as 'needs vendor'</t>
+          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -7279,44 +7375,44 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed a WO PO with a vendor-missing part, drive the flag flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
         </is>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: vendor-missing-on-WO-PO behavior per prior VIU (BATCH 7; vendor-missing POs created in prior runs). Bulk Receive vendor grouping confirmed live this run; all current POs have vendors so the flag was not re-surfaced. verifying reports mark Vendor-Missing POs as 'needs vendor' needs a vendor-missing PO + the reports surface; not driven this session (needs seeded vendor-missing PO).</t>
+          <t>Wording+VIU 2026-07-13: entering a NEW part number should create inventory/catalog stock + Part History on receive - blocked by OBS-6 (Part-History surface GET /api/inventory/parts/history returns 500; part-detail page crashes) + needs a vendor-missing/no-PN part to receive.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>C29359</t>
+          <t>C29365</t>
         </is>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29359</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>SF-BULK-10</t>
+          <t>SF-PNFIX-03</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>PO Bulk Receive Page (Story 8)</t>
+          <t>Inline Part-Number Fix (Story 10)</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Verify a cored part's Ok/Not OK resolution becomes available once received, and core-only partial receive is supported</t>
+          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -7326,29 +7422,29 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: fresh sv7301 cookies + seeded data to drive this scenario.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
         </is>
       </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: needs a genuine cored part on a PO to verify the Ok/Not OK resolution after receive + core-only partial receive. A genuine special-order (vendor-source) core is not seedable in-app (see SF-CORE cluster). Bulk Receive surface confirmed live.</t>
+          <t>Wording+VIU 2026-07-13: entering an EXISTING part number should link + update stock/cost/history without overwriting description/category - blocked by OBS-6 (Part-History 500) + needs a no-PN part to receive.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>C29364</t>
+          <t>C29366</t>
         </is>
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29364</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-02</t>
+          <t>SF-PNFIX-04</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -7358,12 +7454,12 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Verify entering a NEW part number creates a new inventory/catalog part with stock and Part History on receive</t>
+          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -7378,24 +7474,24 @@
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: entering a NEW part number should create inventory/catalog stock + Part History on receive - blocked by OBS-6 (Part-History surface GET /api/inventory/parts/history returns 500; part-detail page crashes) + needs a vendor-missing/no-PN part to receive.</t>
+          <t>Wording+VIU 2026-07-13: inline part-number field-locking (sell locks after invoiced/paid) - needs an invoiced/paid WO (not drivable in-harness).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>C29365</t>
+          <t>C29367</t>
         </is>
       </c>
       <c r="B15" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29365</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-03</t>
+          <t>SF-PNFIX-05</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -7405,7 +7501,7 @@
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Verify entering an EXISTING part number links to that item and updates stock/cost/history without overwriting description or category</t>
+          <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -7425,24 +7521,24 @@
       </c>
       <c r="I15" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: entering an EXISTING part number should link + update stock/cost/history without overwriting description/category - blocked by OBS-6 (Part-History 500) + needs a no-PN part to receive.</t>
+          <t>V2.4 Δ3 wording applied. VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08). The invoiced/paid overlay also needs an invoiced WO (not drivable in-harness).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>C29366</t>
+          <t>C29368</t>
         </is>
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29366</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-04</t>
+          <t>SF-PNFIX-06</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -7452,7 +7548,7 @@
       </c>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Verify inline part-number field-locking rules match the receive-screen rules (sell locks after invoiced/paid)</t>
+          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -7472,34 +7568,34 @@
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: inline part-number field-locking (sell locks after invoiced/paid) - needs an invoiced/paid WO (not drivable in-harness).</t>
+          <t>Wording+VIU 2026-07-13: inline part-number save should drive real catalog creation/linking + inventory + Part History - blocked by OBS-6 (Part-History 500).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="12" t="inlineStr">
         <is>
-          <t>C29367</t>
+          <t>C29373</t>
         </is>
       </c>
       <c r="B17" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29367</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-05</t>
+          <t>SF-RCV-05</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received without a part number, a vendor (for vendor-missing) and a cost / sell price, even on an invoiced/paid WO</t>
+          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -7514,44 +7610,44 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
         </is>
       </c>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>V2.4 Δ3 wording applied. VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08). The invoiced/paid overlay also needs an invoiced WO (not drivable in-harness).</t>
+          <t>Wording+VIU 2026-07-13: VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>C29368</t>
+          <t>C29374</t>
         </is>
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29368</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>SF-PNFIX-06</t>
+          <t>SF-RCV-06</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Inline Part-Number Fix (Story 10)</t>
+          <t>Accept Delivery (Story 12)</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Verify the inline part-number save drives real catalog creation/linking, inventory stock and Part History (not just a stored string)</t>
+          <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -7561,29 +7657,29 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the inline part-number fix flow with seeded PO lines.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
         </is>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: inline part-number save should drive real catalog creation/linking + inventory + Part History - blocked by OBS-6 (Part-History 500).</t>
+          <t>V2.4 Δ3 wording applied (S13-R6 part# + S13-R7 cost/sell receive gates). VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>C29373</t>
+          <t>C29375</t>
         </is>
       </c>
       <c r="B19" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29373</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-05</t>
+          <t>SF-RCV-07</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -7593,12 +7689,12 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Verify new vendorless/no-PN WO parts and WO-originated POs appear and are receivable on Accept Delivery, with the vendor-missing group at the top</t>
+          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -7608,39 +7704,39 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering on Accept Delivery — spec contradicts itself.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
         </is>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
+          <t>Wording+VIU 2026-07-13: '+N' vendor indicator + vendor-missing group at top. VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>C29374</t>
+          <t>C29379</t>
         </is>
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29374</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-06</t>
+          <t>SF-VEND-02</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery receive gates: vendor set, part number entered, cost / sell price entered, vendor invoice # captured</t>
+          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -7655,44 +7751,44 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed deliverable POs, drive the Receive / Accept-Delivery flow.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>V2.4 Δ3 wording applied (S13-R6 part# + S13-R7 cost/sell receive gates). VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
+          <t>Wording+VIU 2026-07-13: needs a same-vendor-already-on-PO collision to surface the 'Add to {vendor}?' Merge vs Keep Separate prompt - not seedable without the vendor-missing collision state. Bulk Receive vendor group confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="12" t="inlineStr">
         <is>
-          <t>C29375</t>
+          <t>C29380</t>
         </is>
       </c>
       <c r="B21" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29375</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>SF-RCV-07</t>
+          <t>SF-VEND-03</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Accept Delivery (Story 12)</t>
+          <t>Assign Vendor + Merge (Story 13)</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Verify Accept Delivery shows a '+N' vendor indicator and leads with the vendor-missing group</t>
+          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -7702,29 +7798,29 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q11 — Vendor-missing group ordering (S12-R1 bottom vs S12-R3 top).</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: '+N' vendor indicator + vendor-missing group at top. VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
+          <t>Wording+VIU 2026-07-13: needs two POs for the same WO with a shared vendor to surface the merge-POs prompt - merge-collision state not seedable in-harness.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="inlineStr">
         <is>
-          <t>C29379</t>
+          <t>C29381</t>
         </is>
       </c>
       <c r="B22" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29379</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-02</t>
+          <t>SF-VEND-04</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
@@ -7734,12 +7830,12 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor already on this PO prompts 'Add to {vendor}?' with Merge vs Keep Separate</t>
+          <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -7754,24 +7850,24 @@
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: needs a same-vendor-already-on-PO collision to surface the 'Add to {vendor}?' Merge vs Keep Separate prompt - not seedable without the vendor-missing collision state. Bulk Receive vendor group confirmed live.</t>
+          <t>V2.4 Δ3 wording applied (receive enables only with part# + cost/sell). VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="12" t="inlineStr">
         <is>
-          <t>C29380</t>
+          <t>C29382</t>
         </is>
       </c>
       <c r="B23" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29380</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-03</t>
+          <t>SF-VEND-05</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -7781,7 +7877,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a vendor that is on another PO for the same WO prompts to merge the POs</t>
+          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -7801,24 +7897,24 @@
       </c>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: needs two POs for the same WO with a shared vendor to surface the merge-POs prompt - merge-collision state not seedable in-harness.</t>
+          <t>Wording+VIU 2026-07-13: vendor matched by ID (not name) + merge scoped to same WO + receiving blocked when WO invoiced/paid - the invoiced/paid block needs an invoiced/paid WO (not drivable in-harness).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>C29381</t>
+          <t>C29442</t>
         </is>
       </c>
       <c r="B24" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29381</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29442</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-04</t>
+          <t>SF-VEND-06</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
@@ -7828,12 +7924,12 @@
       </c>
       <c r="E24" s="12" t="inlineStr">
         <is>
-          <t>Verify assigning a different vendor with no collision auto-assigns and clears the QB flag, and Receive enables only once the part number and cost / sell price are also present</t>
+          <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -7843,44 +7939,44 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
         </is>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
-          <t>V2.4 Δ3 wording applied (receive enables only with part# + cost/sell). VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
+          <t>V2.4 Δ3 NEW case (S13-R7 cost/sell receive gate). VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>C29382</t>
+          <t>C29396</t>
         </is>
       </c>
       <c r="B25" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29382</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-05</t>
+          <t>SF-REV-11</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Verify vendor matching is by ID (not name), merge is scoped to the same WO, and receiving is blocked when the WO is invoiced/paid</t>
+          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
@@ -7890,44 +7986,44 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
         </is>
       </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>Wording+VIU 2026-07-13: vendor matched by ID (not name) + merge scoped to same WO + receiving blocked when WO invoiced/paid - the invoiced/paid block needs an invoiced/paid WO (not drivable in-harness).</t>
+          <t>Direct Review-&gt;Complete confirmed live (S2-15823, no separate final Complete). VIU-Pending on the invoicing-block half: verifying invoicing is blocked until the WO is reviewed needs an invoicing drive on a pre-sign-off WO (invoicing not driven in-harness). Not driven this session.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>C29442</t>
+          <t>C29399</t>
         </is>
       </c>
       <c r="B26" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29442</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>SF-VEND-06</t>
+          <t>SF-REV-14</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Assign Vendor + Merge (Story 13)</t>
+          <t>Review ON (Story 16)</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Verify a part cannot be received until a missing cost / sell price is entered</t>
+          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G26" s="15" t="inlineStr">
@@ -7937,44 +8033,44 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: reachable-now · who: QA (needs cookies+seed data) · needs: QA VIU: seed vendor-missing POs, drive Assign-Vendor + merge.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
         </is>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
-          <t>V2.4 Δ3 NEW case (S13-R7 cost/sell receive gate). VIU-Pending: needs a seeded vendor-missing PO on the Bulk Receive / Accept Delivery surface. Every PO available this run had a vendor (vendorMissing:false), so the vendor-missing group and the new receive-time gates were not surfaced. Seeding requires the New Part Request vendor-missing flow (Source=Vendor, free-text part number, no vendor -&gt; complete WO), a multi-step drive not completed this session. General Bulk Receive gates (invoice #, qty, tax) are confirmed (SF-BULK-05/08).</t>
+          <t>VIU-Pending (non-seedable): needs a WO with genuine inventory + special-order cores to verify core resolution before sign-off and the invoicing block until Reviewed AND cores resolved. A genuine special-order (vendor-source) core is not seedable in-app (see SF-CORE cluster). Review flow confirmed live.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>C29396</t>
+          <t>C29404</t>
         </is>
       </c>
       <c r="B27" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29396</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-11</t>
+          <t>SF-UX-04</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>UX Refinements (Story 15)</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
         <is>
-          <t>Verify sign-off completes the work order directly (no separate final Complete) and invoicing is blocked until reviewed</t>
+          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -7984,39 +8080,39 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q8 — Invoicing-blocked-until-reviewed depends on the Reviewed-state ruling (Q8).</t>
+          <t>BLOCKED — MILOS ANSWER · Milos answers Open Question Q10 — Close-vs-cancel confirm modal — design 'still to be added'.</t>
         </is>
       </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>Direct Review-&gt;Complete confirmed live (S2-15823, no separate final Complete). VIU-Pending on the invoicing-block half: verifying invoicing is blocked until the WO is reviewed needs an invoicing drive on a pre-sign-off WO (invoicing not driven in-harness). Not driven this session.</t>
+          <t>VIU-Pending: the close-confirmation dialog (Close = closes modal only; Cancel text-link = closes + returns) needs a completion modal with a discardable in-progress state to trigger it; the labor-only WOs available complete directly without that state. Wording kept build-accurate; needs a part-bearing in-progress completion to drive.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>C29399</t>
+          <t>C29416</t>
         </is>
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29399</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29416</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>SF-REV-14</t>
+          <t>SF-VAL-02</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>Review ON (Story 16)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E28" s="12" t="inlineStr">
         <is>
-          <t>Verify cores are resolved per rules before sign-off and invoicing is blocked until both Reviewed and all cores resolved</t>
+          <t>Verify completion is blocked when a required VIN is missing (non-review No-PO / Optional-invoice flow)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -8031,44 +8127,44 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: enable Require Review and drive the review/sign-off round-trip.</t>
+          <t>BLOCKED — VIU PENDING (QA) · sub-bucket: needs-data · who: QA (needs cookies+seed data) · needs: QA VIU: drive the specific validation/edge scenario with seeded data.</t>
         </is>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
-          <t>VIU-Pending (non-seedable): needs a WO with genuine inventory + special-order cores to verify core resolution before sign-off and the invoicing block until Reviewed AND cores resolved. A genuine special-order (vendor-source) core is not seedable in-app (see SF-CORE cluster). Review flow confirmed live.</t>
+          <t>BUILD FINDING (live 2026-07-13): the completion modal has NO VIN field (only Mileage + Engine Hours), even with Require Review off — broader than V2.4 Δ1. VIN validity surfaces via the 'Valid VIN Required' header chip. VIU-Pending on the hard-block half: confirming a VIN-less WO cannot complete needs a VIN-less asset, which is not seedable (POST /api/vehicles 405). Expected reworded to the observed build behavior + flagged.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>C29404</t>
+          <t>C29420</t>
         </is>
       </c>
       <c r="B29" s="13" t="inlineStr">
         <is>
-          <t>https://shopview.testrail.io/index.php?/cases/view/29404</t>
+          <t>https://shopview.testrail.io/index.php?/cases/view/29420</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>SF-UX-04</t>
+          <t>SF-VAL-06</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>UX Refinements (Story 15)</t>
+          <t>Validation / Edge</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Verify the close-confirmation modal behavior (Close = closes modal only; Cancel = closes modal + returns to previous screen)</t>
+          <t>Verify a vendor-missing part cannot be received without a vendor, a part number, and a cost / sell price</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="G29" s="1